--- a/data/raw_data/feed_profiles_and_composition.xlsx
+++ b/data/raw_data/feed_profiles_and_composition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\treimer\Documents\R-temp-files\climate_risks_to_fed_mariculture\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15AB620-1043-41B8-A22F-996403FA178E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D15D74-3C5D-4EFF-8CDA-C0E2B84919F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7572" yWindow="1344" windowWidth="26880" windowHeight="13908" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11280" yWindow="1044" windowWidth="27396" windowHeight="13908" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="feed_formulations" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="229">
   <si>
     <t>ingredient</t>
   </si>
@@ -446,9 +446,6 @@
     <t>atlantic_salmon</t>
   </si>
   <si>
-    <t>Democratic People's Republic of Korea</t>
-  </si>
-  <si>
     <t>Iran</t>
   </si>
   <si>
@@ -599,9 +596,6 @@
     <t>Aas, T. S. et al. (2022). Utilization of feed resources in the production of Atlantic salmon (Salmo salar) in Norway: An update for 2020. Aquaculture Reports, 26, 101316. https://doi.org/10.1016/j.aqrep.2022.101316</t>
   </si>
   <si>
-    <t>WIP</t>
-  </si>
-  <si>
     <t>rainbow_trout-norway</t>
   </si>
   <si>
@@ -656,9 +650,6 @@
     <t>cellulose</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>Petereit, J., Hoerterer, C., Bischoff-Lang, A. A., Conceição, L. E. C., Pereira, G., Johansen, J., Pastres, R., &amp; Buck, B. H. (2022). Adult European Seabass (Dicentrarchus labrax) Perform Well on Alternative Circular-Economy-Driven Feed Formulations. Sustainability, 14(12), 7279. https://doi.org/10.3390/su14127279</t>
   </si>
   <si>
@@ -743,13 +734,16 @@
     <t>Novriadi, R., Herawati, V. E., Prayitno, S. B., Windarto, S., &amp; Tan, R. (2024). Evaluation of distiller’s dried grains with solubles in diets for Pacific white shrimp, Litopenaeus vannamei, reared under pond conditions. Journal of the World Aquaculture Society, 55(1), 62–76. https://doi.org/10.1111/jwas.13033</t>
   </si>
   <si>
+    <t>wip</t>
+  </si>
+  <si>
+    <t>Reunion</t>
+  </si>
+  <si>
     <t>y</t>
   </si>
   <si>
-    <t>wip</t>
-  </si>
-  <si>
-    <t>Reunion</t>
+    <t>Democratic People’s Republic of Korea</t>
   </si>
 </sst>
 </file>
@@ -1167,7 +1161,7 @@
         <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -1182,7 +1176,7 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -1194,7 +1188,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -1206,7 +1200,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>24</v>
@@ -1218,7 +1212,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>23</v>
@@ -1230,7 +1224,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>25</v>
@@ -1242,7 +1236,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -1353,7 +1347,7 @@
         <v>49</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C16" s="2">
         <v>1.4999999999999999E-2</v>
@@ -1938,7 +1932,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>10</v>
@@ -1950,7 +1944,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>9</v>
@@ -1962,7 +1956,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>1</v>
@@ -1974,7 +1968,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>3</v>
@@ -1986,7 +1980,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>2</v>
@@ -1998,7 +1992,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>21</v>
@@ -2010,7 +2004,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>6</v>
@@ -2022,7 +2016,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>22</v>
@@ -2034,7 +2028,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>23</v>
@@ -2046,7 +2040,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>14</v>
@@ -2058,7 +2052,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>5</v>
@@ -2070,7 +2064,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -2082,10 +2076,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C77" s="2">
         <v>3.7600000000000001E-2</v>
@@ -2094,7 +2088,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>9</v>
@@ -2106,7 +2100,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>1</v>
@@ -2118,7 +2112,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>2</v>
@@ -2130,7 +2124,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>34</v>
@@ -2142,7 +2136,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>24</v>
@@ -2154,7 +2148,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>22</v>
@@ -2166,7 +2160,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>23</v>
@@ -2178,7 +2172,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>12</v>
@@ -2190,7 +2184,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>25</v>
@@ -2202,7 +2196,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>5</v>
@@ -2330,10 +2324,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C96" s="2">
         <v>1.4999999999999999E-2</v>
@@ -2342,10 +2336,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C97" s="2">
         <v>0.13</v>
@@ -2354,7 +2348,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>1</v>
@@ -2366,10 +2360,10 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C99" s="2">
         <v>0.08</v>
@@ -2378,7 +2372,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>28</v>
@@ -2390,7 +2384,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>23</v>
@@ -2402,7 +2396,7 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>12</v>
@@ -2414,10 +2408,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>209</v>
       </c>
       <c r="C103" s="2">
         <v>0.15</v>
@@ -2426,7 +2420,7 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>15</v>
@@ -2453,7 +2447,7 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>46</v>
@@ -2465,7 +2459,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>10</v>
@@ -2477,7 +2471,7 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>9</v>
@@ -2489,7 +2483,7 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>47</v>
@@ -2501,7 +2495,7 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>1</v>
@@ -2511,12 +2505,12 @@
         <v>7.8947368421052627E-2</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>3</v>
@@ -2526,12 +2520,12 @@
         <v>7.1052631578947367E-2</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>2</v>
@@ -2541,12 +2535,12 @@
         <v>3.428571428571428E-2</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>4</v>
@@ -2556,12 +2550,12 @@
         <v>2.571428571428571E-2</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>34</v>
@@ -2573,10 +2567,10 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C117" s="2">
         <v>0.03</v>
@@ -2585,7 +2579,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>22</v>
@@ -2597,7 +2591,7 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>14</v>
@@ -2609,7 +2603,7 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>5</v>
@@ -2621,7 +2615,7 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>15</v>
@@ -2633,7 +2627,7 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>10</v>
@@ -2645,7 +2639,7 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>13</v>
@@ -2657,7 +2651,7 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>17</v>
@@ -2669,7 +2663,7 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>1</v>
@@ -2681,7 +2675,7 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>3</v>
@@ -2693,7 +2687,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>2</v>
@@ -2705,7 +2699,7 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>4</v>
@@ -2717,7 +2711,7 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>16</v>
@@ -2729,7 +2723,7 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>11</v>
@@ -2741,7 +2735,7 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>20</v>
@@ -2753,7 +2747,7 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>18</v>
@@ -2765,7 +2759,7 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>12</v>
@@ -2777,7 +2771,7 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>14</v>
@@ -2789,7 +2783,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>19</v>
@@ -2801,7 +2795,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>5</v>
@@ -2813,7 +2807,7 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>15</v>
@@ -2825,7 +2819,7 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>9</v>
@@ -2837,7 +2831,7 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>47</v>
@@ -2849,7 +2843,7 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>1</v>
@@ -2859,12 +2853,12 @@
         <v>0.15789473684210525</v>
       </c>
       <c r="D140" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>3</v>
@@ -2874,12 +2868,12 @@
         <v>0.14210526315789473</v>
       </c>
       <c r="D141" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>2</v>
@@ -2889,12 +2883,12 @@
         <v>5.1428571428571421E-2</v>
       </c>
       <c r="D142" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>4</v>
@@ -2904,12 +2898,12 @@
         <v>3.8571428571428562E-2</v>
       </c>
       <c r="D143" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>34</v>
@@ -2921,10 +2915,10 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C145" s="2">
         <v>0.04</v>
@@ -2933,7 +2927,7 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>22</v>
@@ -2945,7 +2939,7 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>23</v>
@@ -2957,7 +2951,7 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>12</v>
@@ -2969,7 +2963,7 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>5</v>
@@ -2981,10 +2975,10 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C150" s="2">
         <v>7.1999999999999995E-2</v>
@@ -2993,7 +2987,7 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>1</v>
@@ -3005,7 +2999,7 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>2</v>
@@ -3017,7 +3011,7 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>34</v>
@@ -3030,7 +3024,7 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>23</v>
@@ -3042,7 +3036,7 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>14</v>
@@ -3054,7 +3048,7 @@
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>5</v>
@@ -3066,7 +3060,7 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>1</v>
@@ -3078,7 +3072,7 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>2</v>
@@ -3090,7 +3084,7 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>26</v>
@@ -3102,7 +3096,7 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>8</v>
@@ -3114,7 +3108,7 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>12</v>
@@ -3126,7 +3120,7 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>14</v>
@@ -3138,7 +3132,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>5</v>
@@ -3150,7 +3144,7 @@
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>15</v>
@@ -3172,7 +3166,7 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>23</v>
@@ -3184,7 +3178,7 @@
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>22</v>
@@ -3195,7 +3189,7 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>1</v>
@@ -3206,7 +3200,7 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>25</v>
@@ -3217,7 +3211,7 @@
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>5</v>
@@ -3228,7 +3222,7 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>2</v>
@@ -3239,7 +3233,7 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>34</v>
@@ -3251,7 +3245,7 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>1</v>
@@ -3262,10 +3256,10 @@
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C175">
         <v>0.12</v>
@@ -3273,10 +3267,10 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C176">
         <v>0.1474</v>
@@ -3284,7 +3278,7 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>23</v>
@@ -3295,10 +3289,10 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B178" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="C178">
         <v>1.15E-2</v>
@@ -3306,10 +3300,10 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C179">
         <v>0.02</v>
@@ -3317,7 +3311,7 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>34</v>
@@ -3328,10 +3322,10 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B181" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C181">
         <v>0.05</v>
@@ -3339,7 +3333,7 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B182" t="s">
         <v>1</v>
@@ -3350,7 +3344,7 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B183" t="s">
         <v>3</v>
@@ -3361,7 +3355,7 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B184" t="s">
         <v>34</v>
@@ -3372,7 +3366,7 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B185" t="s">
         <v>23</v>
@@ -3383,7 +3377,7 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B186" t="s">
         <v>12</v>
@@ -3394,7 +3388,7 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B187" t="s">
         <v>5</v>
@@ -3405,7 +3399,7 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B188" t="s">
         <v>1</v>
@@ -3416,7 +3410,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B189" t="s">
         <v>2</v>
@@ -3427,7 +3421,7 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B190" t="s">
         <v>34</v>
@@ -3438,7 +3432,7 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B191" t="s">
         <v>23</v>
@@ -3449,7 +3443,7 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B192" t="s">
         <v>5</v>
@@ -4395,49 +4389,49 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>174</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C2" s="8">
         <v>223</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>94</v>
@@ -4446,7 +4440,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E3" s="11"/>
       <c r="F3" s="8"/>
@@ -4454,7 +4448,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>83</v>
@@ -4463,7 +4457,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="8"/>
@@ -4471,7 +4465,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>57</v>
@@ -4480,7 +4474,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="8"/>
@@ -4491,16 +4485,16 @@
         <v>128</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C6" s="8">
         <v>159</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -4510,13 +4504,13 @@
         <v>128</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" s="8">
         <v>50</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="8"/>
@@ -4533,7 +4527,7 @@
         <v>21</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="8"/>
@@ -4550,13 +4544,13 @@
         <v>1494</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="G9" s="8"/>
     </row>
@@ -4565,20 +4559,20 @@
         <v>128</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>129</v>
+        <v>228</v>
       </c>
       <c r="C10" s="8">
         <v>1</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="8" t="s">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
@@ -4586,20 +4580,18 @@
         <v>128</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C11" s="8">
         <v>863</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>199</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="F11" s="8"/>
       <c r="G11" s="8"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -4607,18 +4599,16 @@
         <v>128</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C12" s="8">
         <v>22</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E12" s="11"/>
-      <c r="F12" s="8" t="s">
-        <v>199</v>
-      </c>
+      <c r="F12" s="8"/>
       <c r="G12" s="8"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -4626,18 +4616,16 @@
         <v>128</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C13" s="8">
         <v>16</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E13" s="11"/>
-      <c r="F13" s="8" t="s">
-        <v>199</v>
-      </c>
+      <c r="F13" s="8"/>
       <c r="G13" s="8"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -4645,18 +4633,16 @@
         <v>128</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C14" s="8">
         <v>9</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E14" s="11"/>
-      <c r="F14" s="8" t="s">
-        <v>199</v>
-      </c>
+      <c r="F14" s="8"/>
       <c r="G14" s="8"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -4664,18 +4650,16 @@
         <v>128</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C15" s="8">
         <v>5</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E15" s="11"/>
-      <c r="F15" s="8" t="s">
-        <v>199</v>
-      </c>
+      <c r="F15" s="8"/>
       <c r="G15" s="8"/>
     </row>
     <row r="16" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
@@ -4683,7 +4667,7 @@
         <v>128</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" s="8">
         <v>212</v>
@@ -4692,7 +4676,7 @@
         <v>127</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
@@ -4702,7 +4686,7 @@
         <v>128</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C17" s="8">
         <v>63</v>
@@ -4770,7 +4754,7 @@
         <v>119</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C21" s="8">
         <v>161</v>
@@ -4785,7 +4769,7 @@
         <v>119</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C22" s="8">
         <v>16</v>
@@ -4860,7 +4844,7 @@
         <v>119</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C27" s="8">
         <v>4</v>
@@ -5166,10 +5150,10 @@
         <v>259</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
@@ -5185,7 +5169,7 @@
         <v>60</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E48" s="11"/>
       <c r="F48" s="8"/>
@@ -5202,7 +5186,7 @@
         <v>34</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E49" s="11"/>
       <c r="F49" s="8"/>
@@ -5213,13 +5197,13 @@
         <v>118</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C50" s="8">
         <v>28</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E50" s="11"/>
       <c r="F50" s="8"/>
@@ -5236,7 +5220,7 @@
         <v>22</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E51" s="11"/>
       <c r="F51" s="8"/>
@@ -5247,13 +5231,13 @@
         <v>118</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C52" s="8">
         <v>19</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E52" s="11"/>
       <c r="F52" s="8"/>
@@ -5270,7 +5254,7 @@
         <v>16</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E53" s="11"/>
       <c r="F53" s="8"/>
@@ -5287,7 +5271,7 @@
         <v>9</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E54" s="11"/>
       <c r="F54" s="8"/>
@@ -5304,7 +5288,7 @@
         <v>4</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="8"/>
@@ -5321,7 +5305,7 @@
         <v>3</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E56" s="11"/>
       <c r="F56" s="8"/>
@@ -5338,7 +5322,7 @@
         <v>2</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="8"/>
@@ -5349,13 +5333,13 @@
         <v>118</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C58" s="8">
         <v>2</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E58" s="11"/>
       <c r="F58" s="8"/>
@@ -5372,7 +5356,7 @@
         <v>2</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E59" s="11"/>
       <c r="F59" s="8"/>
@@ -5389,7 +5373,7 @@
         <v>2</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E60" s="11"/>
       <c r="F60" s="8"/>
@@ -5406,7 +5390,7 @@
         <v>1</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E61" s="11"/>
       <c r="F61" s="8"/>
@@ -5423,7 +5407,7 @@
         <v>1</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E62" s="11"/>
       <c r="F62" s="8"/>
@@ -5440,7 +5424,7 @@
         <v>1</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E63" s="11"/>
       <c r="F63" s="8"/>
@@ -5457,7 +5441,7 @@
         <v>1</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E64" s="11"/>
       <c r="F64" s="8"/>
@@ -5474,7 +5458,7 @@
         <v>1</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E65" s="11"/>
       <c r="F65" s="8"/>
@@ -5491,7 +5475,7 @@
         <v>1</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E66" s="11"/>
       <c r="F66" s="8"/>
@@ -5508,7 +5492,7 @@
         <v>1</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E67" s="11"/>
       <c r="F67" s="8"/>
@@ -5525,7 +5509,7 @@
         <v>1</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E68" s="11"/>
       <c r="F68" s="8"/>
@@ -5542,7 +5526,7 @@
         <v>1</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E69" s="11"/>
       <c r="F69" s="8"/>
@@ -5553,16 +5537,16 @@
         <v>117</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C70" s="8">
         <v>239</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F70" s="8"/>
       <c r="G70" s="8"/>
@@ -5572,13 +5556,13 @@
         <v>117</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C71" s="8">
         <v>4</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E71" s="11"/>
       <c r="F71" s="8"/>
@@ -5595,7 +5579,7 @@
         <v>4</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E72" s="11"/>
       <c r="F72" s="8"/>
@@ -5606,13 +5590,13 @@
         <v>117</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C73" s="8">
         <v>2</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E73" s="11"/>
       <c r="F73" s="8"/>
@@ -5629,7 +5613,7 @@
         <v>1</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="8"/>
@@ -5646,7 +5630,7 @@
         <v>1</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E75" s="11"/>
       <c r="F75" s="8"/>
@@ -5663,7 +5647,7 @@
         <v>1</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E76" s="11"/>
       <c r="F76" s="8"/>
@@ -5680,7 +5664,7 @@
         <v>1</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E77" s="11"/>
       <c r="F77" s="8"/>
@@ -5691,7 +5675,7 @@
         <v>113</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C78" s="8">
         <v>214</v>
@@ -5721,7 +5705,7 @@
         <v>113</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C80" s="8">
         <v>8</v>
@@ -5736,7 +5720,7 @@
         <v>113</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C81" s="8">
         <v>3</v>
@@ -5781,7 +5765,7 @@
         <v>113</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C84" s="8">
         <v>2</v>
@@ -5931,7 +5915,7 @@
         <v>33</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C94" s="8">
         <v>150</v>
@@ -5946,7 +5930,7 @@
         <v>33</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C95" s="8">
         <v>29</v>
@@ -6066,16 +6050,16 @@
         <v>36</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C103" s="8">
         <v>433</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F103" s="8"/>
       <c r="G103" s="8"/>
@@ -6091,7 +6075,7 @@
         <v>214</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E104" s="11"/>
       <c r="F104" s="8"/>
@@ -6108,7 +6092,7 @@
         <v>50</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E105" s="11"/>
       <c r="F105" s="8"/>
@@ -6125,7 +6109,7 @@
         <v>31</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E106" s="11"/>
       <c r="F106" s="8"/>
@@ -6136,13 +6120,13 @@
         <v>36</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C107" s="8">
         <v>6</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E107" s="11"/>
       <c r="F107" s="8"/>
@@ -6159,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E108" s="11"/>
       <c r="F108" s="8"/>
@@ -6176,7 +6160,7 @@
         <v>1</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E109" s="11"/>
       <c r="F109" s="8"/>
@@ -6193,7 +6177,7 @@
         <v>1</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E110" s="11"/>
       <c r="F110" s="8"/>
@@ -6210,7 +6194,7 @@
         <v>1</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E111" s="11"/>
       <c r="F111" s="8"/>
@@ -6227,7 +6211,7 @@
         <v>1</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E112" s="11"/>
       <c r="F112" s="8"/>
@@ -6244,7 +6228,7 @@
         <v>1</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E113" s="11"/>
       <c r="F113" s="8"/>
@@ -6261,7 +6245,7 @@
         <v>1</v>
       </c>
       <c r="D114" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E114" s="11"/>
       <c r="F114" s="8"/>
@@ -6278,7 +6262,7 @@
         <v>1</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E115" s="11"/>
       <c r="F115" s="8"/>
@@ -6295,7 +6279,7 @@
         <v>1</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E116" s="11"/>
       <c r="F116" s="8"/>
@@ -6312,7 +6296,7 @@
         <v>1</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E117" s="11"/>
       <c r="F117" s="8"/>
@@ -6329,7 +6313,7 @@
         <v>1</v>
       </c>
       <c r="D118" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E118" s="11"/>
       <c r="F118" s="8"/>
@@ -6346,7 +6330,7 @@
         <v>1</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E119" s="11"/>
       <c r="F119" s="8"/>
@@ -6357,7 +6341,7 @@
         <v>40</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C120" s="8">
         <v>468</v>
@@ -6372,7 +6356,7 @@
         <v>40</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C121" s="8">
         <v>96</v>
@@ -6387,7 +6371,7 @@
         <v>40</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C122" s="8">
         <v>38</v>
@@ -6417,7 +6401,7 @@
         <v>40</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C124" s="8">
         <v>22</v>
@@ -6432,7 +6416,7 @@
         <v>40</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C125" s="8">
         <v>21</v>
@@ -6462,7 +6446,7 @@
         <v>40</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C127" s="8">
         <v>7</v>
@@ -6477,7 +6461,7 @@
         <v>40</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C128" s="8">
         <v>2</v>
@@ -6702,7 +6686,7 @@
         <v>37</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C143" s="8">
         <v>60</v>
@@ -6762,7 +6746,7 @@
         <v>37</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C147" s="8">
         <v>2</v>
@@ -6822,7 +6806,7 @@
         <v>37</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C151" s="8">
         <v>1</v>
@@ -6942,7 +6926,7 @@
         <v>38</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C159" s="8">
         <v>39</v>
@@ -6957,7 +6941,7 @@
         <v>38</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C160" s="8">
         <v>3</v>
@@ -6982,23 +6966,25 @@
       <c r="F161" s="8"/>
       <c r="G161" s="8"/>
     </row>
-    <row r="162" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A162" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B162" s="8" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C162" s="8">
-        <v>334</v>
+        <v>263</v>
       </c>
       <c r="D162" s="8" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="E162" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="F162" s="8"/>
+        <v>185</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G162" s="8"/>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -7006,36 +6992,35 @@
         <v>93</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>97</v>
+        <v>160</v>
       </c>
       <c r="C163" s="8">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="E163" s="11"/>
-      <c r="F163" s="8"/>
-      <c r="G163" s="8"/>
-    </row>
-    <row r="164" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="F163" s="8" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C164" s="8">
-        <v>263</v>
+        <v>12</v>
       </c>
       <c r="D164" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="E164" s="9" t="s">
-        <v>187</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="E164" s="11"/>
       <c r="F164" s="8" t="s">
-        <v>180</v>
+        <v>227</v>
       </c>
       <c r="G164" s="8"/>
     </row>
@@ -7044,54 +7029,57 @@
         <v>93</v>
       </c>
       <c r="B165" s="8" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="C165" s="8">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E165" s="11"/>
       <c r="F165" s="8" t="s">
-        <v>229</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="G165" s="8"/>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B166" s="8" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="C166" s="8">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D166" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E166" s="11"/>
       <c r="F166" s="8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G166" s="8"/>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>149</v>
+        <v>53</v>
       </c>
       <c r="C167" s="8">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D167" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="E167" s="11"/>
+        <v>180</v>
+      </c>
+      <c r="E167" s="9" t="s">
+        <v>183</v>
+      </c>
       <c r="F167" s="8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G167" s="8"/>
     </row>
@@ -7100,38 +7088,36 @@
         <v>93</v>
       </c>
       <c r="B168" s="8" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="C168" s="8">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D168" s="8" t="s">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="E168" s="11"/>
       <c r="F168" s="8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G168" s="8"/>
     </row>
-    <row r="169" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B169" s="8" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="C169" s="8">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D169" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="E169" s="9" t="s">
-        <v>185</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="E169" s="11"/>
       <c r="F169" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G169" s="8"/>
     </row>
@@ -7140,17 +7126,17 @@
         <v>93</v>
       </c>
       <c r="B170" s="8" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="C170" s="8">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D170" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E170" s="11"/>
       <c r="F170" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G170" s="8"/>
     </row>
@@ -7159,17 +7145,17 @@
         <v>93</v>
       </c>
       <c r="B171" s="8" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C171" s="8">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D171" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E171" s="11"/>
       <c r="F171" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G171" s="8"/>
     </row>
@@ -7178,17 +7164,17 @@
         <v>93</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="C172" s="8">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D172" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E172" s="11"/>
       <c r="F172" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G172" s="8"/>
     </row>
@@ -7197,17 +7183,17 @@
         <v>93</v>
       </c>
       <c r="B173" s="8" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="C173" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E173" s="11"/>
       <c r="F173" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G173" s="8"/>
     </row>
@@ -7216,17 +7202,17 @@
         <v>93</v>
       </c>
       <c r="B174" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C174" s="8">
         <v>1</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E174" s="11"/>
       <c r="F174" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G174" s="8"/>
     </row>
@@ -7235,36 +7221,38 @@
         <v>93</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C175" s="8">
         <v>1</v>
       </c>
       <c r="D175" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E175" s="11"/>
       <c r="F175" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G175" s="8"/>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A176" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="C176" s="8">
-        <v>1</v>
+        <v>334</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="E176" s="11"/>
+        <v>168</v>
+      </c>
+      <c r="E176" s="9" t="s">
+        <v>184</v>
+      </c>
       <c r="F176" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G176" s="8"/>
     </row>
@@ -7273,17 +7261,17 @@
         <v>93</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C177" s="8">
         <v>1</v>
       </c>
       <c r="D177" s="8" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="E177" s="11"/>
       <c r="F177" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G177" s="8"/>
     </row>
@@ -7292,16 +7280,16 @@
         <v>82</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C178" s="8">
         <v>134</v>
       </c>
       <c r="D178" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E178" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F178" s="8"/>
       <c r="G178" s="8"/>
@@ -7311,13 +7299,13 @@
         <v>82</v>
       </c>
       <c r="B179" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C179" s="8">
         <v>76</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E179" s="11"/>
       <c r="F179" s="8"/>
@@ -7334,7 +7322,7 @@
         <v>17</v>
       </c>
       <c r="D180" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E180" s="11"/>
       <c r="F180" s="8"/>
@@ -7345,13 +7333,13 @@
         <v>82</v>
       </c>
       <c r="B181" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C181" s="8">
         <v>2</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E181" s="11"/>
       <c r="F181" s="8"/>
@@ -7368,7 +7356,7 @@
         <v>1</v>
       </c>
       <c r="D182" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E182" s="11"/>
       <c r="F182" s="8"/>
@@ -7385,7 +7373,7 @@
         <v>1</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E183" s="11"/>
       <c r="F183" s="8"/>
@@ -7402,7 +7390,7 @@
         <v>1</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E184" s="11"/>
       <c r="F184" s="8"/>
@@ -7419,7 +7407,7 @@
         <v>1</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E185" s="11"/>
       <c r="F185" s="8"/>
@@ -7436,7 +7424,7 @@
         <v>1</v>
       </c>
       <c r="D186" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E186" s="11"/>
       <c r="F186" s="8"/>
@@ -7453,7 +7441,7 @@
         <v>1</v>
       </c>
       <c r="D187" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E187" s="11"/>
       <c r="F187" s="8"/>
@@ -7470,7 +7458,7 @@
         <v>1</v>
       </c>
       <c r="D188" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E188" s="11"/>
       <c r="F188" s="8"/>
@@ -7487,7 +7475,7 @@
         <v>1</v>
       </c>
       <c r="D189" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E189" s="11"/>
       <c r="F189" s="8"/>
@@ -7504,7 +7492,7 @@
         <v>1</v>
       </c>
       <c r="D190" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E190" s="11"/>
       <c r="F190" s="8"/>
@@ -7521,7 +7509,7 @@
         <v>1</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E191" s="11"/>
       <c r="F191" s="8"/>
@@ -7538,10 +7526,10 @@
         <v>59</v>
       </c>
       <c r="D192" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F192" s="8"/>
       <c r="G192" s="8"/>
@@ -7557,7 +7545,7 @@
         <v>40</v>
       </c>
       <c r="D193" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E193" s="11"/>
       <c r="F193" s="8"/>
@@ -7568,13 +7556,13 @@
         <v>82</v>
       </c>
       <c r="B194" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C194" s="8">
         <v>26</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E194" s="11"/>
       <c r="F194" s="8"/>
@@ -7591,7 +7579,7 @@
         <v>25</v>
       </c>
       <c r="D195" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E195" s="11"/>
       <c r="F195" s="8"/>
@@ -7602,13 +7590,13 @@
         <v>82</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C196" s="8">
         <v>23</v>
       </c>
       <c r="D196" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E196" s="11"/>
       <c r="F196" s="8"/>
@@ -7625,7 +7613,7 @@
         <v>18</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E197" s="11"/>
       <c r="F197" s="8"/>
@@ -7642,7 +7630,7 @@
         <v>14</v>
       </c>
       <c r="D198" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E198" s="11"/>
       <c r="F198" s="8"/>
@@ -7653,13 +7641,13 @@
         <v>82</v>
       </c>
       <c r="B199" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C199" s="8">
         <v>14</v>
       </c>
       <c r="D199" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E199" s="11"/>
       <c r="F199" s="8"/>
@@ -7676,7 +7664,7 @@
         <v>10</v>
       </c>
       <c r="D200" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E200" s="11"/>
       <c r="F200" s="8"/>
@@ -7693,7 +7681,7 @@
         <v>9</v>
       </c>
       <c r="D201" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E201" s="11"/>
       <c r="F201" s="8"/>
@@ -7710,7 +7698,7 @@
         <v>3</v>
       </c>
       <c r="D202" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E202" s="11"/>
       <c r="F202" s="8"/>
@@ -7721,13 +7709,13 @@
         <v>82</v>
       </c>
       <c r="B203" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C203" s="8">
         <v>3</v>
       </c>
       <c r="D203" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E203" s="11"/>
       <c r="F203" s="8"/>
@@ -7744,7 +7732,7 @@
         <v>2</v>
       </c>
       <c r="D204" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E204" s="11"/>
       <c r="F204" s="8"/>
@@ -7761,7 +7749,7 @@
         <v>2</v>
       </c>
       <c r="D205" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E205" s="11"/>
       <c r="F205" s="8"/>
@@ -7778,7 +7766,7 @@
         <v>1</v>
       </c>
       <c r="D206" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E206" s="11"/>
       <c r="F206" s="8"/>
@@ -7795,7 +7783,7 @@
         <v>1</v>
       </c>
       <c r="D207" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E207" s="11"/>
       <c r="F207" s="8"/>
@@ -7812,7 +7800,7 @@
         <v>1</v>
       </c>
       <c r="D208" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E208" s="11"/>
       <c r="F208" s="8"/>
@@ -7829,7 +7817,7 @@
         <v>1</v>
       </c>
       <c r="D209" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E209" s="11"/>
       <c r="F209" s="8"/>
@@ -7840,7 +7828,7 @@
         <v>42</v>
       </c>
       <c r="B210" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C210" s="8">
         <v>542</v>
@@ -7855,7 +7843,7 @@
         <v>42</v>
       </c>
       <c r="B211" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C211" s="8">
         <v>418</v>
@@ -7870,7 +7858,7 @@
         <v>42</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C212" s="8">
         <v>292</v>
@@ -7885,7 +7873,7 @@
         <v>42</v>
       </c>
       <c r="B213" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C213" s="8">
         <v>203</v>
@@ -7930,7 +7918,7 @@
         <v>42</v>
       </c>
       <c r="B216" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C216" s="8">
         <v>96</v>
@@ -7945,7 +7933,7 @@
         <v>42</v>
       </c>
       <c r="B217" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C217" s="8">
         <v>54</v>
@@ -7975,7 +7963,7 @@
         <v>42</v>
       </c>
       <c r="B219" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C219" s="8">
         <v>23</v>
@@ -8140,7 +8128,7 @@
         <v>39</v>
       </c>
       <c r="B230" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C230" s="8">
         <v>92</v>
@@ -8170,7 +8158,7 @@
         <v>39</v>
       </c>
       <c r="B232" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C232" s="8">
         <v>24</v>
@@ -8185,7 +8173,7 @@
         <v>39</v>
       </c>
       <c r="B233" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C233" s="8">
         <v>19</v>
@@ -8215,7 +8203,7 @@
         <v>39</v>
       </c>
       <c r="B235" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C235" s="8">
         <v>10</v>
@@ -8290,16 +8278,16 @@
         <v>41</v>
       </c>
       <c r="B240" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C240" s="8">
         <v>1183</v>
       </c>
       <c r="D240" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E240" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F240" s="8"/>
       <c r="G240" s="8"/>
@@ -8315,7 +8303,7 @@
         <v>14</v>
       </c>
       <c r="D241" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E241" s="11"/>
       <c r="F241" s="8"/>
@@ -8326,13 +8314,13 @@
         <v>41</v>
       </c>
       <c r="B242" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C242" s="8">
         <v>13</v>
       </c>
       <c r="D242" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E242" s="11"/>
       <c r="F242" s="8"/>
@@ -8349,7 +8337,7 @@
         <v>13</v>
       </c>
       <c r="D243" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E243" s="11"/>
       <c r="F243" s="8"/>
@@ -8360,13 +8348,13 @@
         <v>41</v>
       </c>
       <c r="B244" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C244" s="8">
         <v>4</v>
       </c>
       <c r="D244" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E244" s="11"/>
       <c r="F244" s="8"/>
@@ -8383,7 +8371,7 @@
         <v>3</v>
       </c>
       <c r="D245" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E245" s="11"/>
       <c r="F245" s="8"/>
@@ -8394,16 +8382,16 @@
         <v>41</v>
       </c>
       <c r="B246" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C246" s="8">
         <v>1308</v>
       </c>
       <c r="D246" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E246" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F246" s="8"/>
       <c r="G246" s="8"/>
@@ -8419,7 +8407,7 @@
         <v>260</v>
       </c>
       <c r="D247" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E247" s="11"/>
       <c r="F247" s="8"/>
@@ -8430,13 +8418,13 @@
         <v>41</v>
       </c>
       <c r="B248" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C248" s="8">
         <v>179</v>
       </c>
       <c r="D248" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E248" s="11"/>
       <c r="F248" s="8"/>
@@ -8447,13 +8435,13 @@
         <v>41</v>
       </c>
       <c r="B249" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C249" s="8">
         <v>73</v>
       </c>
       <c r="D249" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E249" s="11"/>
       <c r="F249" s="8"/>
@@ -8470,7 +8458,7 @@
         <v>72</v>
       </c>
       <c r="D250" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E250" s="11"/>
       <c r="F250" s="8"/>
@@ -8481,13 +8469,13 @@
         <v>41</v>
       </c>
       <c r="B251" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C251" s="8">
         <v>57</v>
       </c>
       <c r="D251" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E251" s="11"/>
       <c r="F251" s="8"/>
@@ -8498,13 +8486,13 @@
         <v>41</v>
       </c>
       <c r="B252" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C252" s="8">
         <v>39</v>
       </c>
       <c r="D252" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E252" s="11"/>
       <c r="F252" s="8"/>
@@ -8515,13 +8503,13 @@
         <v>41</v>
       </c>
       <c r="B253" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C253" s="8">
         <v>37</v>
       </c>
       <c r="D253" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E253" s="11"/>
       <c r="F253" s="8"/>
@@ -8532,13 +8520,13 @@
         <v>41</v>
       </c>
       <c r="B254" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C254" s="8">
         <v>36</v>
       </c>
       <c r="D254" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E254" s="11"/>
       <c r="F254" s="8"/>
@@ -8549,13 +8537,13 @@
         <v>41</v>
       </c>
       <c r="B255" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C255" s="8">
         <v>14</v>
       </c>
       <c r="D255" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E255" s="11"/>
       <c r="F255" s="8"/>
@@ -8572,7 +8560,7 @@
         <v>13</v>
       </c>
       <c r="D256" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E256" s="11"/>
       <c r="F256" s="8"/>
@@ -8583,13 +8571,13 @@
         <v>41</v>
       </c>
       <c r="B257" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C257" s="8">
         <v>12</v>
       </c>
       <c r="D257" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E257" s="11"/>
       <c r="F257" s="8"/>
@@ -8600,13 +8588,13 @@
         <v>41</v>
       </c>
       <c r="B258" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C258" s="8">
         <v>11</v>
       </c>
       <c r="D258" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E258" s="11"/>
       <c r="F258" s="8"/>
@@ -8623,7 +8611,7 @@
         <v>9</v>
       </c>
       <c r="D259" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E259" s="11"/>
       <c r="F259" s="8"/>
@@ -8634,13 +8622,13 @@
         <v>41</v>
       </c>
       <c r="B260" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C260" s="8">
         <v>5</v>
       </c>
       <c r="D260" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E260" s="11"/>
       <c r="F260" s="8"/>
@@ -8651,13 +8639,13 @@
         <v>41</v>
       </c>
       <c r="B261" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C261" s="8">
         <v>3</v>
       </c>
       <c r="D261" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E261" s="11"/>
       <c r="F261" s="8"/>
@@ -8674,7 +8662,7 @@
         <v>2</v>
       </c>
       <c r="D262" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E262" s="11"/>
       <c r="F262" s="8"/>
@@ -8691,7 +8679,7 @@
         <v>2</v>
       </c>
       <c r="D263" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E263" s="11"/>
       <c r="F263" s="8"/>
@@ -8708,7 +8696,7 @@
         <v>1</v>
       </c>
       <c r="D264" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E264" s="11"/>
       <c r="F264" s="8"/>
@@ -8725,7 +8713,7 @@
         <v>1</v>
       </c>
       <c r="D265" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E265" s="11"/>
       <c r="F265" s="8"/>
@@ -8742,7 +8730,7 @@
         <v>1</v>
       </c>
       <c r="D266" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E266" s="11"/>
       <c r="F266" s="8"/>
@@ -8759,7 +8747,7 @@
         <v>1</v>
       </c>
       <c r="D267" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E267" s="11"/>
       <c r="F267" s="8"/>
@@ -8776,7 +8764,7 @@
         <v>1</v>
       </c>
       <c r="D268" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E268" s="11"/>
       <c r="F268" s="8"/>
@@ -8793,7 +8781,7 @@
         <v>1</v>
       </c>
       <c r="D269" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E269" s="11"/>
       <c r="F269" s="8"/>
@@ -8810,7 +8798,7 @@
         <v>1</v>
       </c>
       <c r="D270" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E270" s="11"/>
       <c r="F270" s="8"/>
@@ -8827,7 +8815,7 @@
         <v>1</v>
       </c>
       <c r="D271" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E271" s="11"/>
       <c r="F271" s="8"/>
@@ -8844,7 +8832,7 @@
         <v>1</v>
       </c>
       <c r="D272" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E272" s="11"/>
       <c r="F272" s="8"/>
@@ -8861,7 +8849,7 @@
         <v>1</v>
       </c>
       <c r="D273" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E273" s="11"/>
       <c r="F273" s="8"/>
@@ -8878,7 +8866,7 @@
         <v>1</v>
       </c>
       <c r="D274" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E274" s="11"/>
       <c r="F274" s="8"/>
@@ -8895,7 +8883,7 @@
         <v>1</v>
       </c>
       <c r="D275" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E275" s="11"/>
       <c r="F275" s="8"/>
@@ -8912,7 +8900,7 @@
         <v>1</v>
       </c>
       <c r="D276" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E276" s="11"/>
       <c r="F276" s="8"/>
@@ -8929,7 +8917,7 @@
         <v>1</v>
       </c>
       <c r="D277" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E277" s="11"/>
       <c r="F277" s="8"/>
@@ -8946,7 +8934,7 @@
         <v>1</v>
       </c>
       <c r="D278" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E278" s="11"/>
       <c r="F278" s="8"/>
@@ -8957,16 +8945,16 @@
         <v>41</v>
       </c>
       <c r="B279" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C279" s="8">
         <v>795</v>
       </c>
       <c r="D279" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E279" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F279" s="8"/>
       <c r="G279" s="8"/>
@@ -8976,13 +8964,13 @@
         <v>41</v>
       </c>
       <c r="B280" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C280" s="8">
         <v>205</v>
       </c>
       <c r="D280" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E280" s="11"/>
       <c r="F280" s="8"/>
@@ -8999,7 +8987,7 @@
         <v>117</v>
       </c>
       <c r="D281" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E281" s="11"/>
       <c r="F281" s="8"/>
@@ -9016,7 +9004,7 @@
         <v>90</v>
       </c>
       <c r="D282" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E282" s="11"/>
       <c r="F282" s="8"/>
@@ -9027,13 +9015,13 @@
         <v>41</v>
       </c>
       <c r="B283" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C283" s="8">
         <v>7</v>
       </c>
       <c r="D283" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E283" s="11"/>
       <c r="F283" s="8"/>
@@ -9050,7 +9038,7 @@
         <v>5</v>
       </c>
       <c r="D284" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E284" s="11"/>
       <c r="F284" s="8"/>
@@ -9061,13 +9049,13 @@
         <v>41</v>
       </c>
       <c r="B285" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C285" s="8">
         <v>3</v>
       </c>
       <c r="D285" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E285" s="11"/>
       <c r="F285" s="8"/>
@@ -9084,7 +9072,7 @@
         <v>1</v>
       </c>
       <c r="D286" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E286" s="11"/>
       <c r="F286" s="8"/>
@@ -9101,7 +9089,7 @@
         <v>1</v>
       </c>
       <c r="D287" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E287" s="11"/>
       <c r="F287" s="8"/>
@@ -9118,7 +9106,7 @@
         <v>1</v>
       </c>
       <c r="D288" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E288" s="11"/>
       <c r="F288" s="8"/>
@@ -9135,7 +9123,7 @@
         <v>1</v>
       </c>
       <c r="D289" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E289" s="11"/>
       <c r="F289" s="8"/>
@@ -9146,16 +9134,16 @@
         <v>41</v>
       </c>
       <c r="B290" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C290" s="8">
         <v>520</v>
       </c>
       <c r="D290" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E290" s="9" t="s">
         <v>224</v>
-      </c>
-      <c r="E290" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="F290" s="8"/>
       <c r="G290" s="8"/>
@@ -9165,13 +9153,13 @@
         <v>41</v>
       </c>
       <c r="B291" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C291" s="8">
         <v>455</v>
       </c>
       <c r="D291" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E291" s="11"/>
       <c r="F291" s="8"/>
@@ -9182,13 +9170,13 @@
         <v>41</v>
       </c>
       <c r="B292" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C292" s="8">
         <v>404</v>
       </c>
       <c r="D292" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E292" s="11"/>
       <c r="F292" s="8"/>
@@ -9199,13 +9187,13 @@
         <v>41</v>
       </c>
       <c r="B293" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C293" s="8">
         <v>94</v>
       </c>
       <c r="D293" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E293" s="11"/>
       <c r="F293" s="8"/>
@@ -9222,7 +9210,7 @@
         <v>32</v>
       </c>
       <c r="D294" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E294" s="11"/>
       <c r="F294" s="8"/>
@@ -9233,13 +9221,13 @@
         <v>41</v>
       </c>
       <c r="B295" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C295" s="8">
         <v>9</v>
       </c>
       <c r="D295" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E295" s="11"/>
       <c r="F295" s="8"/>
@@ -9256,7 +9244,7 @@
         <v>3</v>
       </c>
       <c r="D296" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E296" s="11"/>
       <c r="F296" s="8"/>
@@ -9273,7 +9261,7 @@
         <v>1</v>
       </c>
       <c r="D297" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E297" s="11"/>
       <c r="F297" s="8"/>
@@ -9290,7 +9278,7 @@
         <v>1</v>
       </c>
       <c r="D298" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E298" s="11"/>
       <c r="F298" s="8"/>
@@ -9307,7 +9295,7 @@
         <v>1</v>
       </c>
       <c r="D299" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E299" s="11"/>
       <c r="F299" s="8"/>
@@ -9324,7 +9312,7 @@
         <v>1</v>
       </c>
       <c r="D300" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E300" s="11"/>
       <c r="F300" s="8"/>
@@ -9336,7 +9324,7 @@
       <sortCondition ref="A1:A300"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="G2 F5:G5 F2:F300">
+  <conditionalFormatting sqref="G2 F2:F300 F5:G5">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"Y"</formula>
     </cfRule>

--- a/data/raw_data/feed_profiles_and_composition.xlsx
+++ b/data/raw_data/feed_profiles_and_composition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\treimer\Documents\R-temp-files\climate_risks_to_fed_mariculture\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D15D74-3C5D-4EFF-8CDA-C0E2B84919F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D739D3E0-B9EB-47D4-926C-02C62C89A482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11280" yWindow="1044" windowWidth="27396" windowHeight="13908" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="0" windowWidth="21900" windowHeight="16656" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="feed_formulations" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="229">
   <si>
     <t>ingredient</t>
   </si>
@@ -7252,7 +7252,7 @@
         <v>184</v>
       </c>
       <c r="F176" s="8" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G176" s="8"/>
     </row>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="E177" s="11"/>
       <c r="F177" s="8" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G177" s="8"/>
     </row>
@@ -7291,7 +7291,9 @@
       <c r="E178" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="F178" s="8"/>
+      <c r="F178" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G178" s="8"/>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -7308,7 +7310,9 @@
         <v>193</v>
       </c>
       <c r="E179" s="11"/>
-      <c r="F179" s="8"/>
+      <c r="F179" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G179" s="8"/>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -7325,7 +7329,9 @@
         <v>193</v>
       </c>
       <c r="E180" s="11"/>
-      <c r="F180" s="8"/>
+      <c r="F180" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G180" s="8"/>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -7342,7 +7348,9 @@
         <v>193</v>
       </c>
       <c r="E181" s="11"/>
-      <c r="F181" s="8"/>
+      <c r="F181" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G181" s="8"/>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -7359,7 +7367,9 @@
         <v>193</v>
       </c>
       <c r="E182" s="11"/>
-      <c r="F182" s="8"/>
+      <c r="F182" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G182" s="8"/>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -7376,7 +7386,9 @@
         <v>193</v>
       </c>
       <c r="E183" s="11"/>
-      <c r="F183" s="8"/>
+      <c r="F183" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G183" s="8"/>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -7393,7 +7405,9 @@
         <v>193</v>
       </c>
       <c r="E184" s="11"/>
-      <c r="F184" s="8"/>
+      <c r="F184" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G184" s="8"/>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -7410,7 +7424,9 @@
         <v>193</v>
       </c>
       <c r="E185" s="11"/>
-      <c r="F185" s="8"/>
+      <c r="F185" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G185" s="8"/>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -7427,7 +7443,9 @@
         <v>193</v>
       </c>
       <c r="E186" s="11"/>
-      <c r="F186" s="8"/>
+      <c r="F186" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G186" s="8"/>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -7444,7 +7462,9 @@
         <v>193</v>
       </c>
       <c r="E187" s="11"/>
-      <c r="F187" s="8"/>
+      <c r="F187" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G187" s="8"/>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -7461,7 +7481,9 @@
         <v>193</v>
       </c>
       <c r="E188" s="11"/>
-      <c r="F188" s="8"/>
+      <c r="F188" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G188" s="8"/>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -7478,7 +7500,9 @@
         <v>193</v>
       </c>
       <c r="E189" s="11"/>
-      <c r="F189" s="8"/>
+      <c r="F189" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G189" s="8"/>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -7495,7 +7519,9 @@
         <v>193</v>
       </c>
       <c r="E190" s="11"/>
-      <c r="F190" s="8"/>
+      <c r="F190" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G190" s="8"/>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -7512,7 +7538,9 @@
         <v>193</v>
       </c>
       <c r="E191" s="11"/>
-      <c r="F191" s="8"/>
+      <c r="F191" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G191" s="8"/>
     </row>
     <row r="192" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
@@ -9324,7 +9352,7 @@
       <sortCondition ref="A1:A300"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="G2 F2:F300 F5:G5">
+  <conditionalFormatting sqref="G2 F5:G5 F2:F300">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"Y"</formula>
     </cfRule>

--- a/data/raw_data/feed_profiles_and_composition.xlsx
+++ b/data/raw_data/feed_profiles_and_composition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\treimer\Documents\R-temp-files\climate_risks_to_fed_mariculture\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D739D3E0-B9EB-47D4-926C-02C62C89A482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE24ADC3-867E-4C70-99C6-804B1D444301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="0" windowWidth="21900" windowHeight="16656" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24" yWindow="1236" windowWidth="20136" windowHeight="13908" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="feed_formulations" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="228">
   <si>
     <t>ingredient</t>
   </si>
@@ -713,9 +713,6 @@
     <t>cassava-meal</t>
   </si>
   <si>
-    <t>corn-flour</t>
-  </si>
-  <si>
     <t>palm-oil</t>
   </si>
   <si>
@@ -750,10 +747,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -829,6 +827,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -853,11 +857,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -878,10 +883,13 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{B7894CC1-4EE1-4A7D-B74F-624174892FC0}"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
@@ -1150,7 +1158,7 @@
     <col min="7" max="7" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>31</v>
       </c>
@@ -1174,7 +1182,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>200</v>
       </c>
@@ -1186,7 +1194,7 @@
       </c>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>200</v>
       </c>
@@ -1198,7 +1206,7 @@
       </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>200</v>
       </c>
@@ -1210,7 +1218,7 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>200</v>
       </c>
@@ -1222,7 +1230,7 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>200</v>
       </c>
@@ -1234,7 +1242,7 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>200</v>
       </c>
@@ -1246,7 +1254,7 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>49</v>
       </c>
@@ -1258,7 +1266,7 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>49</v>
       </c>
@@ -1270,7 +1278,7 @@
       </c>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>49</v>
       </c>
@@ -1282,7 +1290,7 @@
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>49</v>
       </c>
@@ -1294,7 +1302,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>49</v>
       </c>
@@ -1306,7 +1314,7 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
@@ -1318,7 +1326,7 @@
       </c>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>49</v>
       </c>
@@ -1330,7 +1338,7 @@
       </c>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>49</v>
       </c>
@@ -1342,7 +1350,7 @@
       </c>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>49</v>
       </c>
@@ -1354,7 +1362,7 @@
       </c>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>49</v>
       </c>
@@ -1366,7 +1374,7 @@
       </c>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>49</v>
       </c>
@@ -1378,7 +1386,7 @@
       </c>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>49</v>
       </c>
@@ -1390,7 +1398,7 @@
       </c>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>49</v>
       </c>
@@ -1402,7 +1410,7 @@
       </c>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>49</v>
       </c>
@@ -1414,7 +1422,7 @@
       </c>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>44</v>
       </c>
@@ -1426,7 +1434,7 @@
       </c>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>44</v>
       </c>
@@ -1438,7 +1446,7 @@
       </c>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>44</v>
       </c>
@@ -1450,7 +1458,7 @@
       </c>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>44</v>
       </c>
@@ -1462,7 +1470,7 @@
       </c>
       <c r="D25" s="2"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>44</v>
       </c>
@@ -1474,7 +1482,7 @@
       </c>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>44</v>
       </c>
@@ -1486,7 +1494,7 @@
       </c>
       <c r="D27" s="2"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
@@ -1498,7 +1506,7 @@
       </c>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>44</v>
       </c>
@@ -1510,7 +1518,7 @@
       </c>
       <c r="D29" s="2"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>44</v>
       </c>
@@ -1522,7 +1530,7 @@
       </c>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>44</v>
       </c>
@@ -1534,7 +1542,7 @@
       </c>
       <c r="D31" s="2"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>44</v>
       </c>
@@ -1546,7 +1554,7 @@
       </c>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>44</v>
       </c>
@@ -1558,7 +1566,7 @@
       </c>
       <c r="D33" s="2"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>44</v>
       </c>
@@ -1570,7 +1578,7 @@
       </c>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>44</v>
       </c>
@@ -1582,7 +1590,7 @@
       </c>
       <c r="D35" s="2"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>43</v>
       </c>
@@ -1594,7 +1602,7 @@
       </c>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>43</v>
       </c>
@@ -1606,7 +1614,7 @@
       </c>
       <c r="D37" s="2"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>43</v>
       </c>
@@ -1618,7 +1626,7 @@
       </c>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>43</v>
       </c>
@@ -1630,7 +1638,7 @@
       </c>
       <c r="D39" s="2"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>43</v>
       </c>
@@ -1642,7 +1650,7 @@
       </c>
       <c r="D40" s="2"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>43</v>
       </c>
@@ -1654,7 +1662,7 @@
       </c>
       <c r="D41" s="2"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>43</v>
       </c>
@@ -1666,7 +1674,7 @@
       </c>
       <c r="D42" s="2"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>43</v>
       </c>
@@ -1678,7 +1686,7 @@
       </c>
       <c r="D43" s="2"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>43</v>
       </c>
@@ -1690,7 +1698,7 @@
       </c>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>43</v>
       </c>
@@ -1702,7 +1710,7 @@
       </c>
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>43</v>
       </c>
@@ -1714,7 +1722,7 @@
       </c>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>43</v>
       </c>
@@ -1726,7 +1734,7 @@
       </c>
       <c r="D47" s="2"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>43</v>
       </c>
@@ -1738,7 +1746,7 @@
       </c>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>43</v>
       </c>
@@ -1750,7 +1758,7 @@
       </c>
       <c r="D49" s="2"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>43</v>
       </c>
@@ -1762,7 +1770,7 @@
       </c>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>43</v>
       </c>
@@ -1774,7 +1782,7 @@
       </c>
       <c r="D51" s="2"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>43</v>
       </c>
@@ -1786,7 +1794,7 @@
       </c>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>48</v>
       </c>
@@ -1798,7 +1806,7 @@
       </c>
       <c r="D53" s="2"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>48</v>
       </c>
@@ -1810,7 +1818,7 @@
       </c>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>48</v>
       </c>
@@ -1822,7 +1830,7 @@
       </c>
       <c r="D55" s="2"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>48</v>
       </c>
@@ -1834,7 +1842,7 @@
       </c>
       <c r="D56" s="2"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>48</v>
       </c>
@@ -1846,7 +1854,7 @@
       </c>
       <c r="D57" s="2"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>48</v>
       </c>
@@ -1858,7 +1866,7 @@
       </c>
       <c r="D58" s="2"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>48</v>
       </c>
@@ -1870,7 +1878,7 @@
       </c>
       <c r="D59" s="2"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>48</v>
       </c>
@@ -1882,7 +1890,7 @@
       </c>
       <c r="D60" s="2"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>48</v>
       </c>
@@ -1894,7 +1902,7 @@
       </c>
       <c r="D61" s="2"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>48</v>
       </c>
@@ -1906,7 +1914,7 @@
       </c>
       <c r="D62" s="2"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>48</v>
       </c>
@@ -1918,7 +1926,7 @@
       </c>
       <c r="D63" s="2"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>48</v>
       </c>
@@ -1930,7 +1938,7 @@
       </c>
       <c r="D64" s="2"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>198</v>
       </c>
@@ -1942,7 +1950,7 @@
       </c>
       <c r="D65" s="2"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>198</v>
       </c>
@@ -1954,7 +1962,7 @@
       </c>
       <c r="D66" s="2"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>198</v>
       </c>
@@ -1966,7 +1974,7 @@
       </c>
       <c r="D67" s="3"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>198</v>
       </c>
@@ -1978,7 +1986,7 @@
       </c>
       <c r="D68" s="2"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>198</v>
       </c>
@@ -1990,7 +1998,7 @@
       </c>
       <c r="D69" s="2"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>198</v>
       </c>
@@ -2002,7 +2010,7 @@
       </c>
       <c r="D70" s="2"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>198</v>
       </c>
@@ -2014,7 +2022,7 @@
       </c>
       <c r="D71" s="2"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>198</v>
       </c>
@@ -2026,7 +2034,7 @@
       </c>
       <c r="D72" s="2"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>198</v>
       </c>
@@ -2038,7 +2046,7 @@
       </c>
       <c r="D73" s="2"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>198</v>
       </c>
@@ -2050,7 +2058,7 @@
       </c>
       <c r="D74" s="2"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>198</v>
       </c>
@@ -2062,7 +2070,7 @@
       </c>
       <c r="D75" s="2"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>198</v>
       </c>
@@ -2074,7 +2082,7 @@
       </c>
       <c r="D76" s="2"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>210</v>
       </c>
@@ -2086,7 +2094,7 @@
       </c>
       <c r="D77" s="3"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>210</v>
       </c>
@@ -2098,7 +2106,7 @@
       </c>
       <c r="D78" s="3"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>210</v>
       </c>
@@ -2110,7 +2118,7 @@
       </c>
       <c r="D79" s="3"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>210</v>
       </c>
@@ -2122,7 +2130,7 @@
       </c>
       <c r="D80" s="3"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>210</v>
       </c>
@@ -2134,7 +2142,7 @@
       </c>
       <c r="D81" s="3"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>210</v>
       </c>
@@ -2146,7 +2154,7 @@
       </c>
       <c r="D82" s="3"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>210</v>
       </c>
@@ -2158,7 +2166,7 @@
       </c>
       <c r="D83" s="3"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>210</v>
       </c>
@@ -2170,7 +2178,7 @@
       </c>
       <c r="D84" s="3"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>210</v>
       </c>
@@ -2182,7 +2190,7 @@
       </c>
       <c r="D85" s="3"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>210</v>
       </c>
@@ -2194,7 +2202,7 @@
       </c>
       <c r="D86" s="3"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>210</v>
       </c>
@@ -2206,7 +2214,7 @@
       </c>
       <c r="D87" s="3"/>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>30</v>
       </c>
@@ -2220,7 +2228,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>33</v>
       </c>
@@ -2235,7 +2243,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>33</v>
       </c>
@@ -2250,7 +2258,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>33</v>
       </c>
@@ -2265,7 +2273,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>33</v>
       </c>
@@ -2280,7 +2288,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>33</v>
       </c>
@@ -2295,7 +2303,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>33</v>
       </c>
@@ -2310,7 +2318,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>29</v>
       </c>
@@ -2322,7 +2330,7 @@
       </c>
       <c r="D95" s="2"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>203</v>
       </c>
@@ -2334,7 +2342,7 @@
       </c>
       <c r="D96" s="3"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>203</v>
       </c>
@@ -2346,7 +2354,7 @@
       </c>
       <c r="D97" s="3"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>203</v>
       </c>
@@ -2358,7 +2366,7 @@
       </c>
       <c r="D98" s="3"/>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>203</v>
       </c>
@@ -2370,7 +2378,7 @@
       </c>
       <c r="D99" s="3"/>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>203</v>
       </c>
@@ -2382,7 +2390,7 @@
       </c>
       <c r="D100" s="3"/>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>203</v>
       </c>
@@ -2394,7 +2402,7 @@
       </c>
       <c r="D101" s="3"/>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>203</v>
       </c>
@@ -2406,7 +2414,7 @@
       </c>
       <c r="D102" s="3"/>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>203</v>
       </c>
@@ -2418,7 +2426,7 @@
       </c>
       <c r="D103" s="3"/>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>203</v>
       </c>
@@ -2430,22 +2438,22 @@
       </c>
       <c r="D104" s="3"/>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>181</v>
       </c>
@@ -2457,7 +2465,7 @@
       </c>
       <c r="D108" s="3"/>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>181</v>
       </c>
@@ -2469,7 +2477,7 @@
       </c>
       <c r="D109" s="3"/>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>181</v>
       </c>
@@ -2481,7 +2489,7 @@
       </c>
       <c r="D110" s="3"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>181</v>
       </c>
@@ -2493,7 +2501,7 @@
       </c>
       <c r="D111" s="3"/>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>181</v>
       </c>
@@ -2508,7 +2516,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>181</v>
       </c>
@@ -2523,7 +2531,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>181</v>
       </c>
@@ -2538,7 +2546,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>181</v>
       </c>
@@ -2553,7 +2561,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>181</v>
       </c>
@@ -2565,7 +2573,7 @@
       </c>
       <c r="D116" s="3"/>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>181</v>
       </c>
@@ -2577,7 +2585,7 @@
       </c>
       <c r="D117" s="3"/>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>181</v>
       </c>
@@ -2589,7 +2597,7 @@
       </c>
       <c r="D118" s="3"/>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>181</v>
       </c>
@@ -2601,7 +2609,7 @@
       </c>
       <c r="D119" s="3"/>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>181</v>
       </c>
@@ -2613,7 +2621,7 @@
       </c>
       <c r="D120" s="3"/>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>181</v>
       </c>
@@ -2625,7 +2633,7 @@
       </c>
       <c r="D121" s="3"/>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>179</v>
       </c>
@@ -2637,7 +2645,7 @@
       </c>
       <c r="D122" s="3"/>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>179</v>
       </c>
@@ -2649,7 +2657,7 @@
       </c>
       <c r="D123" s="3"/>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>179</v>
       </c>
@@ -2661,7 +2669,7 @@
       </c>
       <c r="D124" s="3"/>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>179</v>
       </c>
@@ -2673,7 +2681,7 @@
       </c>
       <c r="D125" s="3"/>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>179</v>
       </c>
@@ -2685,7 +2693,7 @@
       </c>
       <c r="D126" s="3"/>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>179</v>
       </c>
@@ -2697,7 +2705,7 @@
       </c>
       <c r="D127" s="3"/>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>179</v>
       </c>
@@ -2709,7 +2717,7 @@
       </c>
       <c r="D128" s="3"/>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>179</v>
       </c>
@@ -2721,7 +2729,7 @@
       </c>
       <c r="D129" s="3"/>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>179</v>
       </c>
@@ -2733,7 +2741,7 @@
       </c>
       <c r="D130" s="3"/>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>179</v>
       </c>
@@ -2745,7 +2753,7 @@
       </c>
       <c r="D131" s="3"/>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>179</v>
       </c>
@@ -2757,7 +2765,7 @@
       </c>
       <c r="D132" s="3"/>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>179</v>
       </c>
@@ -2769,7 +2777,7 @@
       </c>
       <c r="D133" s="3"/>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>179</v>
       </c>
@@ -2781,7 +2789,7 @@
       </c>
       <c r="D134" s="3"/>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>179</v>
       </c>
@@ -2793,7 +2801,7 @@
       </c>
       <c r="D135" s="3"/>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>179</v>
       </c>
@@ -2805,7 +2813,7 @@
       </c>
       <c r="D136" s="3"/>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>179</v>
       </c>
@@ -2817,7 +2825,7 @@
       </c>
       <c r="D137" s="3"/>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>182</v>
       </c>
@@ -2829,7 +2837,7 @@
       </c>
       <c r="D138" s="3"/>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>182</v>
       </c>
@@ -2841,7 +2849,7 @@
       </c>
       <c r="D139" s="3"/>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>182</v>
       </c>
@@ -2856,7 +2864,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>182</v>
       </c>
@@ -2871,7 +2879,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>182</v>
       </c>
@@ -2886,7 +2894,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>182</v>
       </c>
@@ -2901,7 +2909,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>182</v>
       </c>
@@ -2913,7 +2921,7 @@
       </c>
       <c r="D144" s="3"/>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>182</v>
       </c>
@@ -2925,7 +2933,7 @@
       </c>
       <c r="D145" s="3"/>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>182</v>
       </c>
@@ -2937,7 +2945,7 @@
       </c>
       <c r="D146" s="3"/>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>182</v>
       </c>
@@ -2949,7 +2957,7 @@
       </c>
       <c r="D147" s="3"/>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>182</v>
       </c>
@@ -2961,7 +2969,7 @@
       </c>
       <c r="D148" s="3"/>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>182</v>
       </c>
@@ -2973,7 +2981,7 @@
       </c>
       <c r="D149" s="3"/>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>195</v>
       </c>
@@ -2985,7 +2993,7 @@
       </c>
       <c r="D150" s="2"/>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>195</v>
       </c>
@@ -2997,7 +3005,7 @@
       </c>
       <c r="D151" s="2"/>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>195</v>
       </c>
@@ -3009,7 +3017,7 @@
       </c>
       <c r="D152" s="2"/>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>195</v>
       </c>
@@ -3022,7 +3030,7 @@
       </c>
       <c r="D153" s="2"/>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>195</v>
       </c>
@@ -3034,7 +3042,7 @@
       </c>
       <c r="D154" s="2"/>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>195</v>
       </c>
@@ -3046,7 +3054,7 @@
       </c>
       <c r="D155" s="2"/>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>195</v>
       </c>
@@ -3058,7 +3066,7 @@
       </c>
       <c r="D156" s="2"/>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>191</v>
       </c>
@@ -3070,7 +3078,7 @@
       </c>
       <c r="D157" s="3"/>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>191</v>
       </c>
@@ -3082,7 +3090,7 @@
       </c>
       <c r="D158" s="2"/>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>191</v>
       </c>
@@ -3094,7 +3102,7 @@
       </c>
       <c r="D159" s="2"/>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>191</v>
       </c>
@@ -3106,7 +3114,7 @@
       </c>
       <c r="D160" s="2"/>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>191</v>
       </c>
@@ -3118,7 +3126,7 @@
       </c>
       <c r="D161" s="2"/>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>191</v>
       </c>
@@ -3130,7 +3138,7 @@
       </c>
       <c r="D162" s="2"/>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>191</v>
       </c>
@@ -3142,7 +3150,7 @@
       </c>
       <c r="D163" s="2"/>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>191</v>
       </c>
@@ -3154,1212 +3162,1211 @@
       </c>
       <c r="D164" s="2"/>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B167" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B167" t="s">
+        <v>196</v>
+      </c>
+      <c r="C167" s="14">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B168" t="s">
+        <v>1</v>
+      </c>
+      <c r="C168" s="14">
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A169" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B169" t="s">
+        <v>3</v>
+      </c>
+      <c r="C169" s="14">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B170" t="s">
+        <v>34</v>
+      </c>
+      <c r="C170" s="14">
+        <v>2.9999999999999805E-2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B171" t="s">
         <v>23</v>
       </c>
-      <c r="C167" s="2">
+      <c r="C171" s="14">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A172" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B172" t="s">
+        <v>12</v>
+      </c>
+      <c r="C172" s="14">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B173" t="s">
+        <v>5</v>
+      </c>
+      <c r="C173" s="14">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A174" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B174" t="s">
+        <v>1</v>
+      </c>
+      <c r="C174" s="14">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A175" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B175" t="s">
+        <v>2</v>
+      </c>
+      <c r="C175" s="14">
+        <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A176" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B176" t="s">
+        <v>34</v>
+      </c>
+      <c r="C176" s="14">
+        <v>5.5999999999998273E-3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B177" t="s">
+        <v>23</v>
+      </c>
+      <c r="C177" s="14">
+        <v>0.17500000000000002</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B178" t="s">
+        <v>5</v>
+      </c>
+      <c r="C178" s="14">
+        <v>0.45140000000000002</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C179" s="14">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C180" s="14">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A181" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C181" s="14">
+        <v>0.1474</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C182" s="14">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A183" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C183" s="14">
+        <v>3.1000000000000028E-2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A184" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C184" s="14">
+        <v>1.15E-2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A185" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C185" s="14">
+        <v>0.47010000000000002</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A186" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C186" s="15">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A187" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C187" s="15">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A188" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C188" s="14">
+        <v>9.2999999999999972E-2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A189" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C189" s="15">
+        <v>0.20300000000000001</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A190" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C190" s="15">
         <f>0.2+0.015</f>
         <v>0.21500000000000002</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A168" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C168" s="2">
-        <v>0.20300000000000001</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A169" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C169" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A170" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B170" s="2" t="s">
+    <row r="191" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A191" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B191" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C170" s="2">
+      <c r="C191" s="15">
         <v>0.06</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A171" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B171" s="2" t="s">
+    <row r="192" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A192" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B192" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C171" s="2">
+      <c r="C192" s="15">
         <v>0.31900000000000001</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A172" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C172" s="2">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A173" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C173">
-        <f>1-SUM(C167:C172)</f>
-        <v>9.2999999999999972E-2</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A174" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C174">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A175" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C175">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A176" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C176">
-        <v>0.1474</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C177">
-        <v>0.47010000000000002</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="C178">
-        <v>1.15E-2</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C179">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C180">
-        <v>3.1000000000000028E-2</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B181" t="s">
-        <v>196</v>
-      </c>
-      <c r="C181">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B182" t="s">
-        <v>1</v>
-      </c>
-      <c r="C182">
-        <v>0.56000000000000005</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B183" t="s">
-        <v>3</v>
-      </c>
-      <c r="C183">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B184" t="s">
-        <v>34</v>
-      </c>
-      <c r="C184">
-        <v>2.9999999999999805E-2</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B185" t="s">
-        <v>23</v>
-      </c>
-      <c r="C185">
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B186" t="s">
-        <v>12</v>
-      </c>
-      <c r="C186">
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B187" t="s">
-        <v>5</v>
-      </c>
-      <c r="C187">
-        <v>0.28000000000000003</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B188" t="s">
-        <v>1</v>
-      </c>
-      <c r="C188">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B189" t="s">
-        <v>2</v>
-      </c>
-      <c r="C189">
-        <v>2.8000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B190" t="s">
-        <v>34</v>
-      </c>
-      <c r="C190">
-        <v>5.5999999999998273E-3</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B191" t="s">
-        <v>23</v>
-      </c>
-      <c r="C191">
-        <v>0.17500000000000002</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B192" t="s">
-        <v>5</v>
-      </c>
-      <c r="C192">
-        <v>0.45140000000000002</v>
-      </c>
-    </row>
-    <row r="193" x14ac:dyDescent="0.25"/>
-    <row r="194" x14ac:dyDescent="0.25"/>
-    <row r="195" x14ac:dyDescent="0.25"/>
-    <row r="196" x14ac:dyDescent="0.25"/>
-    <row r="197" x14ac:dyDescent="0.25"/>
-    <row r="198" x14ac:dyDescent="0.25"/>
-    <row r="199" x14ac:dyDescent="0.25"/>
-    <row r="200" x14ac:dyDescent="0.25"/>
-    <row r="201" x14ac:dyDescent="0.25"/>
-    <row r="202" x14ac:dyDescent="0.25"/>
-    <row r="203" x14ac:dyDescent="0.25"/>
-    <row r="204" x14ac:dyDescent="0.25"/>
-    <row r="205" x14ac:dyDescent="0.25"/>
-    <row r="206" x14ac:dyDescent="0.25"/>
-    <row r="207" x14ac:dyDescent="0.25"/>
-    <row r="208" x14ac:dyDescent="0.25"/>
-    <row r="209" x14ac:dyDescent="0.25"/>
-    <row r="210" x14ac:dyDescent="0.25"/>
-    <row r="211" x14ac:dyDescent="0.25"/>
-    <row r="212" x14ac:dyDescent="0.25"/>
-    <row r="213" x14ac:dyDescent="0.25"/>
-    <row r="214" x14ac:dyDescent="0.25"/>
-    <row r="215" x14ac:dyDescent="0.25"/>
-    <row r="216" x14ac:dyDescent="0.25"/>
-    <row r="217" x14ac:dyDescent="0.25"/>
-    <row r="218" x14ac:dyDescent="0.25"/>
-    <row r="219" x14ac:dyDescent="0.25"/>
-    <row r="220" x14ac:dyDescent="0.25"/>
-    <row r="221" x14ac:dyDescent="0.25"/>
-    <row r="222" x14ac:dyDescent="0.25"/>
-    <row r="223" x14ac:dyDescent="0.25"/>
-    <row r="224" x14ac:dyDescent="0.25"/>
-    <row r="225" x14ac:dyDescent="0.25"/>
-    <row r="226" x14ac:dyDescent="0.25"/>
-    <row r="227" x14ac:dyDescent="0.25"/>
-    <row r="228" x14ac:dyDescent="0.25"/>
-    <row r="229" x14ac:dyDescent="0.25"/>
-    <row r="230" x14ac:dyDescent="0.25"/>
-    <row r="231" x14ac:dyDescent="0.25"/>
-    <row r="232" x14ac:dyDescent="0.25"/>
-    <row r="233" x14ac:dyDescent="0.25"/>
-    <row r="234" x14ac:dyDescent="0.25"/>
-    <row r="235" x14ac:dyDescent="0.25"/>
-    <row r="236" x14ac:dyDescent="0.25"/>
-    <row r="237" x14ac:dyDescent="0.25"/>
-    <row r="238" x14ac:dyDescent="0.25"/>
-    <row r="239" x14ac:dyDescent="0.25"/>
-    <row r="240" x14ac:dyDescent="0.25"/>
-    <row r="241" x14ac:dyDescent="0.25"/>
-    <row r="242" x14ac:dyDescent="0.25"/>
-    <row r="243" x14ac:dyDescent="0.25"/>
-    <row r="244" x14ac:dyDescent="0.25"/>
-    <row r="245" x14ac:dyDescent="0.25"/>
-    <row r="246" x14ac:dyDescent="0.25"/>
-    <row r="247" x14ac:dyDescent="0.25"/>
-    <row r="248" x14ac:dyDescent="0.25"/>
-    <row r="249" x14ac:dyDescent="0.25"/>
-    <row r="250" x14ac:dyDescent="0.25"/>
-    <row r="251" x14ac:dyDescent="0.25"/>
-    <row r="252" x14ac:dyDescent="0.25"/>
-    <row r="253" x14ac:dyDescent="0.25"/>
-    <row r="254" x14ac:dyDescent="0.25"/>
-    <row r="255" x14ac:dyDescent="0.25"/>
-    <row r="256" x14ac:dyDescent="0.25"/>
-    <row r="257" x14ac:dyDescent="0.25"/>
-    <row r="258" x14ac:dyDescent="0.25"/>
-    <row r="259" x14ac:dyDescent="0.25"/>
-    <row r="260" x14ac:dyDescent="0.25"/>
-    <row r="261" x14ac:dyDescent="0.25"/>
-    <row r="262" x14ac:dyDescent="0.25"/>
-    <row r="263" x14ac:dyDescent="0.25"/>
-    <row r="264" x14ac:dyDescent="0.25"/>
-    <row r="265" x14ac:dyDescent="0.25"/>
-    <row r="266" x14ac:dyDescent="0.25"/>
-    <row r="267" x14ac:dyDescent="0.25"/>
-    <row r="268" x14ac:dyDescent="0.25"/>
-    <row r="269" x14ac:dyDescent="0.25"/>
-    <row r="270" x14ac:dyDescent="0.25"/>
-    <row r="271" x14ac:dyDescent="0.25"/>
-    <row r="272" x14ac:dyDescent="0.25"/>
-    <row r="273" x14ac:dyDescent="0.25"/>
-    <row r="274" x14ac:dyDescent="0.25"/>
-    <row r="275" x14ac:dyDescent="0.25"/>
-    <row r="276" x14ac:dyDescent="0.25"/>
-    <row r="277" x14ac:dyDescent="0.25"/>
-    <row r="278" x14ac:dyDescent="0.25"/>
-    <row r="279" x14ac:dyDescent="0.25"/>
-    <row r="280" x14ac:dyDescent="0.25"/>
-    <row r="281" x14ac:dyDescent="0.25"/>
-    <row r="282" x14ac:dyDescent="0.25"/>
-    <row r="283" x14ac:dyDescent="0.25"/>
-    <row r="284" x14ac:dyDescent="0.25"/>
-    <row r="285" x14ac:dyDescent="0.25"/>
-    <row r="286" x14ac:dyDescent="0.25"/>
-    <row r="287" x14ac:dyDescent="0.25"/>
-    <row r="288" x14ac:dyDescent="0.25"/>
-    <row r="289" x14ac:dyDescent="0.25"/>
-    <row r="290" x14ac:dyDescent="0.25"/>
-    <row r="291" x14ac:dyDescent="0.25"/>
-    <row r="292" x14ac:dyDescent="0.25"/>
-    <row r="293" x14ac:dyDescent="0.25"/>
-    <row r="294" x14ac:dyDescent="0.25"/>
-    <row r="295" x14ac:dyDescent="0.25"/>
-    <row r="296" x14ac:dyDescent="0.25"/>
-    <row r="297" x14ac:dyDescent="0.25"/>
-    <row r="298" x14ac:dyDescent="0.25"/>
-    <row r="299" x14ac:dyDescent="0.25"/>
-    <row r="300" x14ac:dyDescent="0.25"/>
-    <row r="301" x14ac:dyDescent="0.25"/>
-    <row r="302" x14ac:dyDescent="0.25"/>
-    <row r="303" x14ac:dyDescent="0.25"/>
-    <row r="304" x14ac:dyDescent="0.25"/>
-    <row r="305" x14ac:dyDescent="0.25"/>
-    <row r="306" x14ac:dyDescent="0.25"/>
-    <row r="307" x14ac:dyDescent="0.25"/>
-    <row r="308" x14ac:dyDescent="0.25"/>
-    <row r="309" x14ac:dyDescent="0.25"/>
-    <row r="310" x14ac:dyDescent="0.25"/>
-    <row r="311" x14ac:dyDescent="0.25"/>
-    <row r="312" x14ac:dyDescent="0.25"/>
-    <row r="313" x14ac:dyDescent="0.25"/>
-    <row r="314" x14ac:dyDescent="0.25"/>
-    <row r="315" x14ac:dyDescent="0.25"/>
-    <row r="316" x14ac:dyDescent="0.25"/>
-    <row r="317" x14ac:dyDescent="0.25"/>
-    <row r="318" x14ac:dyDescent="0.25"/>
-    <row r="319" x14ac:dyDescent="0.25"/>
-    <row r="320" x14ac:dyDescent="0.25"/>
-    <row r="321" x14ac:dyDescent="0.25"/>
-    <row r="322" x14ac:dyDescent="0.25"/>
-    <row r="323" x14ac:dyDescent="0.25"/>
-    <row r="324" x14ac:dyDescent="0.25"/>
-    <row r="325" x14ac:dyDescent="0.25"/>
-    <row r="326" x14ac:dyDescent="0.25"/>
-    <row r="327" x14ac:dyDescent="0.25"/>
-    <row r="328" x14ac:dyDescent="0.25"/>
-    <row r="329" x14ac:dyDescent="0.25"/>
-    <row r="330" x14ac:dyDescent="0.25"/>
-    <row r="331" x14ac:dyDescent="0.25"/>
-    <row r="332" x14ac:dyDescent="0.25"/>
-    <row r="333" x14ac:dyDescent="0.25"/>
-    <row r="334" x14ac:dyDescent="0.25"/>
-    <row r="335" x14ac:dyDescent="0.25"/>
-    <row r="336" x14ac:dyDescent="0.25"/>
-    <row r="337" x14ac:dyDescent="0.25"/>
-    <row r="338" x14ac:dyDescent="0.25"/>
-    <row r="339" x14ac:dyDescent="0.25"/>
-    <row r="340" x14ac:dyDescent="0.25"/>
-    <row r="341" x14ac:dyDescent="0.25"/>
-    <row r="342" x14ac:dyDescent="0.25"/>
-    <row r="343" x14ac:dyDescent="0.25"/>
-    <row r="344" x14ac:dyDescent="0.25"/>
-    <row r="345" x14ac:dyDescent="0.25"/>
-    <row r="346" x14ac:dyDescent="0.25"/>
-    <row r="347" x14ac:dyDescent="0.25"/>
-    <row r="348" x14ac:dyDescent="0.25"/>
-    <row r="349" x14ac:dyDescent="0.25"/>
-    <row r="350" x14ac:dyDescent="0.25"/>
-    <row r="351" x14ac:dyDescent="0.25"/>
-    <row r="352" x14ac:dyDescent="0.25"/>
-    <row r="353" x14ac:dyDescent="0.25"/>
-    <row r="354" x14ac:dyDescent="0.25"/>
-    <row r="355" x14ac:dyDescent="0.25"/>
-    <row r="356" x14ac:dyDescent="0.25"/>
-    <row r="357" x14ac:dyDescent="0.25"/>
-    <row r="358" x14ac:dyDescent="0.25"/>
-    <row r="359" x14ac:dyDescent="0.25"/>
-    <row r="360" x14ac:dyDescent="0.25"/>
-    <row r="361" x14ac:dyDescent="0.25"/>
-    <row r="362" x14ac:dyDescent="0.25"/>
-    <row r="363" x14ac:dyDescent="0.25"/>
-    <row r="364" x14ac:dyDescent="0.25"/>
-    <row r="365" x14ac:dyDescent="0.25"/>
-    <row r="366" x14ac:dyDescent="0.25"/>
-    <row r="367" x14ac:dyDescent="0.25"/>
-    <row r="368" x14ac:dyDescent="0.25"/>
-    <row r="369" x14ac:dyDescent="0.25"/>
-    <row r="370" x14ac:dyDescent="0.25"/>
-    <row r="371" x14ac:dyDescent="0.25"/>
-    <row r="372" x14ac:dyDescent="0.25"/>
-    <row r="373" x14ac:dyDescent="0.25"/>
-    <row r="374" x14ac:dyDescent="0.25"/>
-    <row r="375" x14ac:dyDescent="0.25"/>
-    <row r="376" x14ac:dyDescent="0.25"/>
-    <row r="377" x14ac:dyDescent="0.25"/>
-    <row r="378" x14ac:dyDescent="0.25"/>
-    <row r="379" x14ac:dyDescent="0.25"/>
-    <row r="380" x14ac:dyDescent="0.25"/>
-    <row r="381" x14ac:dyDescent="0.25"/>
-    <row r="382" x14ac:dyDescent="0.25"/>
-    <row r="383" x14ac:dyDescent="0.25"/>
-    <row r="384" x14ac:dyDescent="0.25"/>
-    <row r="385" x14ac:dyDescent="0.25"/>
-    <row r="386" x14ac:dyDescent="0.25"/>
-    <row r="387" x14ac:dyDescent="0.25"/>
-    <row r="388" x14ac:dyDescent="0.25"/>
-    <row r="389" x14ac:dyDescent="0.25"/>
-    <row r="390" x14ac:dyDescent="0.25"/>
-    <row r="391" x14ac:dyDescent="0.25"/>
-    <row r="392" x14ac:dyDescent="0.25"/>
-    <row r="393" x14ac:dyDescent="0.25"/>
-    <row r="394" x14ac:dyDescent="0.25"/>
-    <row r="395" x14ac:dyDescent="0.25"/>
-    <row r="396" x14ac:dyDescent="0.25"/>
-    <row r="397" x14ac:dyDescent="0.25"/>
-    <row r="398" x14ac:dyDescent="0.25"/>
-    <row r="399" x14ac:dyDescent="0.25"/>
-    <row r="400" x14ac:dyDescent="0.25"/>
-    <row r="401" x14ac:dyDescent="0.25"/>
-    <row r="402" x14ac:dyDescent="0.25"/>
-    <row r="403" x14ac:dyDescent="0.25"/>
-    <row r="404" x14ac:dyDescent="0.25"/>
-    <row r="405" x14ac:dyDescent="0.25"/>
-    <row r="406" x14ac:dyDescent="0.25"/>
-    <row r="407" x14ac:dyDescent="0.25"/>
-    <row r="408" x14ac:dyDescent="0.25"/>
-    <row r="409" x14ac:dyDescent="0.25"/>
-    <row r="410" x14ac:dyDescent="0.25"/>
-    <row r="411" x14ac:dyDescent="0.25"/>
-    <row r="412" x14ac:dyDescent="0.25"/>
-    <row r="413" x14ac:dyDescent="0.25"/>
-    <row r="414" x14ac:dyDescent="0.25"/>
-    <row r="415" x14ac:dyDescent="0.25"/>
-    <row r="416" x14ac:dyDescent="0.25"/>
-    <row r="417" x14ac:dyDescent="0.25"/>
-    <row r="418" x14ac:dyDescent="0.25"/>
-    <row r="419" x14ac:dyDescent="0.25"/>
-    <row r="420" x14ac:dyDescent="0.25"/>
-    <row r="421" x14ac:dyDescent="0.25"/>
-    <row r="422" x14ac:dyDescent="0.25"/>
-    <row r="423" x14ac:dyDescent="0.25"/>
-    <row r="424" x14ac:dyDescent="0.25"/>
-    <row r="425" x14ac:dyDescent="0.25"/>
-    <row r="426" x14ac:dyDescent="0.25"/>
-    <row r="427" x14ac:dyDescent="0.25"/>
-    <row r="428" x14ac:dyDescent="0.25"/>
-    <row r="429" x14ac:dyDescent="0.25"/>
-    <row r="430" x14ac:dyDescent="0.25"/>
-    <row r="431" x14ac:dyDescent="0.25"/>
-    <row r="432" x14ac:dyDescent="0.25"/>
-    <row r="433" x14ac:dyDescent="0.25"/>
-    <row r="434" x14ac:dyDescent="0.25"/>
-    <row r="435" x14ac:dyDescent="0.25"/>
-    <row r="436" x14ac:dyDescent="0.25"/>
-    <row r="437" x14ac:dyDescent="0.25"/>
-    <row r="438" x14ac:dyDescent="0.25"/>
-    <row r="439" x14ac:dyDescent="0.25"/>
-    <row r="440" x14ac:dyDescent="0.25"/>
-    <row r="441" x14ac:dyDescent="0.25"/>
-    <row r="442" x14ac:dyDescent="0.25"/>
-    <row r="443" x14ac:dyDescent="0.25"/>
-    <row r="444" x14ac:dyDescent="0.25"/>
-    <row r="445" x14ac:dyDescent="0.25"/>
-    <row r="446" x14ac:dyDescent="0.25"/>
-    <row r="447" x14ac:dyDescent="0.25"/>
-    <row r="448" x14ac:dyDescent="0.25"/>
-    <row r="449" x14ac:dyDescent="0.25"/>
-    <row r="450" x14ac:dyDescent="0.25"/>
-    <row r="451" x14ac:dyDescent="0.25"/>
-    <row r="452" x14ac:dyDescent="0.25"/>
-    <row r="453" x14ac:dyDescent="0.25"/>
-    <row r="454" x14ac:dyDescent="0.25"/>
-    <row r="455" x14ac:dyDescent="0.25"/>
-    <row r="456" x14ac:dyDescent="0.25"/>
-    <row r="457" x14ac:dyDescent="0.25"/>
-    <row r="458" x14ac:dyDescent="0.25"/>
-    <row r="459" x14ac:dyDescent="0.25"/>
-    <row r="460" x14ac:dyDescent="0.25"/>
-    <row r="461" x14ac:dyDescent="0.25"/>
-    <row r="462" x14ac:dyDescent="0.25"/>
-    <row r="463" x14ac:dyDescent="0.25"/>
-    <row r="464" x14ac:dyDescent="0.25"/>
-    <row r="465" x14ac:dyDescent="0.25"/>
-    <row r="466" x14ac:dyDescent="0.25"/>
-    <row r="467" x14ac:dyDescent="0.25"/>
-    <row r="468" x14ac:dyDescent="0.25"/>
-    <row r="469" x14ac:dyDescent="0.25"/>
-    <row r="470" x14ac:dyDescent="0.25"/>
-    <row r="471" x14ac:dyDescent="0.25"/>
-    <row r="472" x14ac:dyDescent="0.25"/>
-    <row r="473" x14ac:dyDescent="0.25"/>
-    <row r="474" x14ac:dyDescent="0.25"/>
-    <row r="475" x14ac:dyDescent="0.25"/>
-    <row r="476" x14ac:dyDescent="0.25"/>
-    <row r="477" x14ac:dyDescent="0.25"/>
-    <row r="478" x14ac:dyDescent="0.25"/>
-    <row r="479" x14ac:dyDescent="0.25"/>
-    <row r="480" x14ac:dyDescent="0.25"/>
-    <row r="481" x14ac:dyDescent="0.25"/>
-    <row r="482" x14ac:dyDescent="0.25"/>
-    <row r="483" x14ac:dyDescent="0.25"/>
-    <row r="484" x14ac:dyDescent="0.25"/>
-    <row r="485" x14ac:dyDescent="0.25"/>
-    <row r="486" x14ac:dyDescent="0.25"/>
-    <row r="487" x14ac:dyDescent="0.25"/>
-    <row r="488" x14ac:dyDescent="0.25"/>
-    <row r="489" x14ac:dyDescent="0.25"/>
-    <row r="490" x14ac:dyDescent="0.25"/>
-    <row r="491" x14ac:dyDescent="0.25"/>
-    <row r="492" x14ac:dyDescent="0.25"/>
-    <row r="493" x14ac:dyDescent="0.25"/>
-    <row r="494" x14ac:dyDescent="0.25"/>
-    <row r="495" x14ac:dyDescent="0.25"/>
-    <row r="496" x14ac:dyDescent="0.25"/>
-    <row r="497" x14ac:dyDescent="0.25"/>
-    <row r="498" x14ac:dyDescent="0.25"/>
-    <row r="499" x14ac:dyDescent="0.25"/>
-    <row r="500" x14ac:dyDescent="0.25"/>
-    <row r="501" x14ac:dyDescent="0.25"/>
-    <row r="502" x14ac:dyDescent="0.25"/>
-    <row r="503" x14ac:dyDescent="0.25"/>
-    <row r="504" x14ac:dyDescent="0.25"/>
-    <row r="505" x14ac:dyDescent="0.25"/>
-    <row r="506" x14ac:dyDescent="0.25"/>
-    <row r="507" x14ac:dyDescent="0.25"/>
-    <row r="508" x14ac:dyDescent="0.25"/>
-    <row r="509" x14ac:dyDescent="0.25"/>
-    <row r="510" x14ac:dyDescent="0.25"/>
-    <row r="511" x14ac:dyDescent="0.25"/>
-    <row r="512" x14ac:dyDescent="0.25"/>
-    <row r="513" x14ac:dyDescent="0.25"/>
-    <row r="514" x14ac:dyDescent="0.25"/>
-    <row r="515" x14ac:dyDescent="0.25"/>
-    <row r="516" x14ac:dyDescent="0.25"/>
-    <row r="517" x14ac:dyDescent="0.25"/>
-    <row r="518" x14ac:dyDescent="0.25"/>
-    <row r="519" x14ac:dyDescent="0.25"/>
-    <row r="520" x14ac:dyDescent="0.25"/>
-    <row r="521" x14ac:dyDescent="0.25"/>
-    <row r="522" x14ac:dyDescent="0.25"/>
-    <row r="523" x14ac:dyDescent="0.25"/>
-    <row r="524" x14ac:dyDescent="0.25"/>
-    <row r="525" x14ac:dyDescent="0.25"/>
-    <row r="526" x14ac:dyDescent="0.25"/>
-    <row r="527" x14ac:dyDescent="0.25"/>
-    <row r="528" x14ac:dyDescent="0.25"/>
-    <row r="529" x14ac:dyDescent="0.25"/>
-    <row r="530" x14ac:dyDescent="0.25"/>
-    <row r="531" x14ac:dyDescent="0.25"/>
-    <row r="532" x14ac:dyDescent="0.25"/>
-    <row r="533" x14ac:dyDescent="0.25"/>
-    <row r="534" x14ac:dyDescent="0.25"/>
-    <row r="535" x14ac:dyDescent="0.25"/>
-    <row r="536" x14ac:dyDescent="0.25"/>
-    <row r="537" x14ac:dyDescent="0.25"/>
-    <row r="538" x14ac:dyDescent="0.25"/>
-    <row r="539" x14ac:dyDescent="0.25"/>
-    <row r="540" x14ac:dyDescent="0.25"/>
-    <row r="541" x14ac:dyDescent="0.25"/>
-    <row r="542" x14ac:dyDescent="0.25"/>
-    <row r="543" x14ac:dyDescent="0.25"/>
-    <row r="544" x14ac:dyDescent="0.25"/>
-    <row r="545" x14ac:dyDescent="0.25"/>
-    <row r="546" x14ac:dyDescent="0.25"/>
-    <row r="547" x14ac:dyDescent="0.25"/>
-    <row r="548" x14ac:dyDescent="0.25"/>
-    <row r="549" x14ac:dyDescent="0.25"/>
-    <row r="550" x14ac:dyDescent="0.25"/>
-    <row r="551" x14ac:dyDescent="0.25"/>
-    <row r="552" x14ac:dyDescent="0.25"/>
-    <row r="553" x14ac:dyDescent="0.25"/>
-    <row r="554" x14ac:dyDescent="0.25"/>
-    <row r="555" x14ac:dyDescent="0.25"/>
-    <row r="556" x14ac:dyDescent="0.25"/>
-    <row r="557" x14ac:dyDescent="0.25"/>
-    <row r="558" x14ac:dyDescent="0.25"/>
-    <row r="559" x14ac:dyDescent="0.25"/>
-    <row r="560" x14ac:dyDescent="0.25"/>
-    <row r="561" x14ac:dyDescent="0.25"/>
-    <row r="562" x14ac:dyDescent="0.25"/>
-    <row r="563" x14ac:dyDescent="0.25"/>
-    <row r="564" x14ac:dyDescent="0.25"/>
-    <row r="565" x14ac:dyDescent="0.25"/>
-    <row r="566" x14ac:dyDescent="0.25"/>
-    <row r="567" x14ac:dyDescent="0.25"/>
-    <row r="568" x14ac:dyDescent="0.25"/>
-    <row r="569" x14ac:dyDescent="0.25"/>
-    <row r="570" x14ac:dyDescent="0.25"/>
-    <row r="571" x14ac:dyDescent="0.25"/>
-    <row r="572" x14ac:dyDescent="0.25"/>
-    <row r="573" x14ac:dyDescent="0.25"/>
-    <row r="574" x14ac:dyDescent="0.25"/>
-    <row r="575" x14ac:dyDescent="0.25"/>
-    <row r="576" x14ac:dyDescent="0.25"/>
-    <row r="577" x14ac:dyDescent="0.25"/>
-    <row r="578" x14ac:dyDescent="0.25"/>
-    <row r="579" x14ac:dyDescent="0.25"/>
-    <row r="580" x14ac:dyDescent="0.25"/>
-    <row r="581" x14ac:dyDescent="0.25"/>
-    <row r="582" x14ac:dyDescent="0.25"/>
-    <row r="583" x14ac:dyDescent="0.25"/>
-    <row r="584" x14ac:dyDescent="0.25"/>
-    <row r="585" x14ac:dyDescent="0.25"/>
-    <row r="586" x14ac:dyDescent="0.25"/>
-    <row r="587" x14ac:dyDescent="0.25"/>
-    <row r="588" x14ac:dyDescent="0.25"/>
-    <row r="589" x14ac:dyDescent="0.25"/>
-    <row r="590" x14ac:dyDescent="0.25"/>
-    <row r="591" x14ac:dyDescent="0.25"/>
-    <row r="592" x14ac:dyDescent="0.25"/>
-    <row r="593" x14ac:dyDescent="0.25"/>
-    <row r="594" x14ac:dyDescent="0.25"/>
-    <row r="595" x14ac:dyDescent="0.25"/>
-    <row r="596" x14ac:dyDescent="0.25"/>
-    <row r="597" x14ac:dyDescent="0.25"/>
-    <row r="598" x14ac:dyDescent="0.25"/>
-    <row r="599" x14ac:dyDescent="0.25"/>
-    <row r="600" x14ac:dyDescent="0.25"/>
-    <row r="601" x14ac:dyDescent="0.25"/>
-    <row r="602" x14ac:dyDescent="0.25"/>
-    <row r="603" x14ac:dyDescent="0.25"/>
-    <row r="604" x14ac:dyDescent="0.25"/>
-    <row r="605" x14ac:dyDescent="0.25"/>
-    <row r="606" x14ac:dyDescent="0.25"/>
-    <row r="607" x14ac:dyDescent="0.25"/>
-    <row r="608" x14ac:dyDescent="0.25"/>
-    <row r="609" x14ac:dyDescent="0.25"/>
-    <row r="610" x14ac:dyDescent="0.25"/>
-    <row r="611" x14ac:dyDescent="0.25"/>
-    <row r="612" x14ac:dyDescent="0.25"/>
-    <row r="613" x14ac:dyDescent="0.25"/>
-    <row r="614" x14ac:dyDescent="0.25"/>
-    <row r="615" x14ac:dyDescent="0.25"/>
-    <row r="616" x14ac:dyDescent="0.25"/>
-    <row r="617" x14ac:dyDescent="0.25"/>
-    <row r="618" x14ac:dyDescent="0.25"/>
-    <row r="619" x14ac:dyDescent="0.25"/>
-    <row r="620" x14ac:dyDescent="0.25"/>
-    <row r="621" x14ac:dyDescent="0.25"/>
-    <row r="622" x14ac:dyDescent="0.25"/>
-    <row r="623" x14ac:dyDescent="0.25"/>
-    <row r="624" x14ac:dyDescent="0.25"/>
-    <row r="625" x14ac:dyDescent="0.25"/>
-    <row r="626" x14ac:dyDescent="0.25"/>
-    <row r="627" x14ac:dyDescent="0.25"/>
-    <row r="628" x14ac:dyDescent="0.25"/>
-    <row r="629" x14ac:dyDescent="0.25"/>
-    <row r="630" x14ac:dyDescent="0.25"/>
-    <row r="631" x14ac:dyDescent="0.25"/>
-    <row r="632" x14ac:dyDescent="0.25"/>
-    <row r="633" x14ac:dyDescent="0.25"/>
-    <row r="634" x14ac:dyDescent="0.25"/>
-    <row r="635" x14ac:dyDescent="0.25"/>
-    <row r="636" x14ac:dyDescent="0.25"/>
-    <row r="637" x14ac:dyDescent="0.25"/>
-    <row r="638" x14ac:dyDescent="0.25"/>
-    <row r="639" x14ac:dyDescent="0.25"/>
-    <row r="640" x14ac:dyDescent="0.25"/>
-    <row r="641" x14ac:dyDescent="0.25"/>
-    <row r="642" x14ac:dyDescent="0.25"/>
-    <row r="643" x14ac:dyDescent="0.25"/>
-    <row r="644" x14ac:dyDescent="0.25"/>
-    <row r="645" x14ac:dyDescent="0.25"/>
-    <row r="646" x14ac:dyDescent="0.25"/>
-    <row r="647" x14ac:dyDescent="0.25"/>
-    <row r="648" x14ac:dyDescent="0.25"/>
-    <row r="649" x14ac:dyDescent="0.25"/>
-    <row r="650" x14ac:dyDescent="0.25"/>
-    <row r="651" x14ac:dyDescent="0.25"/>
-    <row r="652" x14ac:dyDescent="0.25"/>
-    <row r="653" x14ac:dyDescent="0.25"/>
-    <row r="654" x14ac:dyDescent="0.25"/>
-    <row r="655" x14ac:dyDescent="0.25"/>
-    <row r="656" x14ac:dyDescent="0.25"/>
-    <row r="657" x14ac:dyDescent="0.25"/>
-    <row r="658" x14ac:dyDescent="0.25"/>
-    <row r="659" x14ac:dyDescent="0.25"/>
-    <row r="660" x14ac:dyDescent="0.25"/>
-    <row r="661" x14ac:dyDescent="0.25"/>
-    <row r="662" x14ac:dyDescent="0.25"/>
-    <row r="663" x14ac:dyDescent="0.25"/>
-    <row r="664" x14ac:dyDescent="0.25"/>
-    <row r="665" x14ac:dyDescent="0.25"/>
-    <row r="666" x14ac:dyDescent="0.25"/>
-    <row r="667" x14ac:dyDescent="0.25"/>
-    <row r="668" x14ac:dyDescent="0.25"/>
-    <row r="669" x14ac:dyDescent="0.25"/>
-    <row r="670" x14ac:dyDescent="0.25"/>
-    <row r="671" x14ac:dyDescent="0.25"/>
-    <row r="672" x14ac:dyDescent="0.25"/>
-    <row r="673" x14ac:dyDescent="0.25"/>
-    <row r="674" x14ac:dyDescent="0.25"/>
-    <row r="675" x14ac:dyDescent="0.25"/>
-    <row r="676" x14ac:dyDescent="0.25"/>
-    <row r="677" x14ac:dyDescent="0.25"/>
-    <row r="678" x14ac:dyDescent="0.25"/>
-    <row r="679" x14ac:dyDescent="0.25"/>
-    <row r="680" x14ac:dyDescent="0.25"/>
-    <row r="681" x14ac:dyDescent="0.25"/>
-    <row r="682" x14ac:dyDescent="0.25"/>
-    <row r="683" x14ac:dyDescent="0.25"/>
-    <row r="684" x14ac:dyDescent="0.25"/>
-    <row r="685" x14ac:dyDescent="0.25"/>
-    <row r="686" x14ac:dyDescent="0.25"/>
-    <row r="687" x14ac:dyDescent="0.25"/>
-    <row r="688" x14ac:dyDescent="0.25"/>
-    <row r="689" x14ac:dyDescent="0.25"/>
-    <row r="690" x14ac:dyDescent="0.25"/>
-    <row r="691" x14ac:dyDescent="0.25"/>
-    <row r="692" x14ac:dyDescent="0.25"/>
-    <row r="693" x14ac:dyDescent="0.25"/>
-    <row r="694" x14ac:dyDescent="0.25"/>
-    <row r="695" x14ac:dyDescent="0.25"/>
-    <row r="696" x14ac:dyDescent="0.25"/>
-    <row r="697" x14ac:dyDescent="0.25"/>
-    <row r="698" x14ac:dyDescent="0.25"/>
-    <row r="699" x14ac:dyDescent="0.25"/>
-    <row r="700" x14ac:dyDescent="0.25"/>
-    <row r="701" x14ac:dyDescent="0.25"/>
-    <row r="702" x14ac:dyDescent="0.25"/>
-    <row r="703" x14ac:dyDescent="0.25"/>
-    <row r="704" x14ac:dyDescent="0.25"/>
-    <row r="705" x14ac:dyDescent="0.25"/>
-    <row r="706" x14ac:dyDescent="0.25"/>
-    <row r="707" x14ac:dyDescent="0.25"/>
-    <row r="708" x14ac:dyDescent="0.25"/>
-    <row r="709" x14ac:dyDescent="0.25"/>
-    <row r="710" x14ac:dyDescent="0.25"/>
-    <row r="711" x14ac:dyDescent="0.25"/>
-    <row r="712" x14ac:dyDescent="0.25"/>
-    <row r="713" x14ac:dyDescent="0.25"/>
-    <row r="714" x14ac:dyDescent="0.25"/>
-    <row r="715" x14ac:dyDescent="0.25"/>
-    <row r="716" x14ac:dyDescent="0.25"/>
-    <row r="717" x14ac:dyDescent="0.25"/>
-    <row r="718" x14ac:dyDescent="0.25"/>
-    <row r="719" x14ac:dyDescent="0.25"/>
-    <row r="720" x14ac:dyDescent="0.25"/>
-    <row r="721" x14ac:dyDescent="0.25"/>
-    <row r="722" x14ac:dyDescent="0.25"/>
-    <row r="723" x14ac:dyDescent="0.25"/>
-    <row r="724" x14ac:dyDescent="0.25"/>
-    <row r="725" x14ac:dyDescent="0.25"/>
-    <row r="726" x14ac:dyDescent="0.25"/>
-    <row r="727" x14ac:dyDescent="0.25"/>
-    <row r="728" x14ac:dyDescent="0.25"/>
-    <row r="729" x14ac:dyDescent="0.25"/>
-    <row r="730" x14ac:dyDescent="0.25"/>
-    <row r="731" x14ac:dyDescent="0.25"/>
-    <row r="732" x14ac:dyDescent="0.25"/>
-    <row r="733" x14ac:dyDescent="0.25"/>
-    <row r="734" x14ac:dyDescent="0.25"/>
-    <row r="735" x14ac:dyDescent="0.25"/>
-    <row r="736" x14ac:dyDescent="0.25"/>
-    <row r="737" x14ac:dyDescent="0.25"/>
-    <row r="738" x14ac:dyDescent="0.25"/>
-    <row r="739" x14ac:dyDescent="0.25"/>
-    <row r="740" x14ac:dyDescent="0.25"/>
-    <row r="741" x14ac:dyDescent="0.25"/>
-    <row r="742" x14ac:dyDescent="0.25"/>
-    <row r="743" x14ac:dyDescent="0.25"/>
-    <row r="744" x14ac:dyDescent="0.25"/>
-    <row r="745" x14ac:dyDescent="0.25"/>
-    <row r="746" x14ac:dyDescent="0.25"/>
-    <row r="747" x14ac:dyDescent="0.25"/>
-    <row r="748" x14ac:dyDescent="0.25"/>
-    <row r="749" x14ac:dyDescent="0.25"/>
-    <row r="750" x14ac:dyDescent="0.25"/>
-    <row r="751" x14ac:dyDescent="0.25"/>
-    <row r="752" x14ac:dyDescent="0.25"/>
-    <row r="753" x14ac:dyDescent="0.25"/>
-    <row r="754" x14ac:dyDescent="0.25"/>
-    <row r="755" x14ac:dyDescent="0.25"/>
-    <row r="756" x14ac:dyDescent="0.25"/>
-    <row r="757" x14ac:dyDescent="0.25"/>
-    <row r="758" x14ac:dyDescent="0.25"/>
-    <row r="759" x14ac:dyDescent="0.25"/>
-    <row r="760" x14ac:dyDescent="0.25"/>
-    <row r="761" x14ac:dyDescent="0.25"/>
-    <row r="762" x14ac:dyDescent="0.25"/>
-    <row r="763" x14ac:dyDescent="0.25"/>
-    <row r="764" x14ac:dyDescent="0.25"/>
-    <row r="765" x14ac:dyDescent="0.25"/>
-    <row r="766" x14ac:dyDescent="0.25"/>
-    <row r="767" x14ac:dyDescent="0.25"/>
-    <row r="768" x14ac:dyDescent="0.25"/>
-    <row r="769" x14ac:dyDescent="0.25"/>
-    <row r="770" x14ac:dyDescent="0.25"/>
-    <row r="771" x14ac:dyDescent="0.25"/>
-    <row r="772" x14ac:dyDescent="0.25"/>
-    <row r="773" x14ac:dyDescent="0.25"/>
-    <row r="774" x14ac:dyDescent="0.25"/>
-    <row r="775" x14ac:dyDescent="0.25"/>
-    <row r="776" x14ac:dyDescent="0.25"/>
-    <row r="777" x14ac:dyDescent="0.25"/>
-    <row r="778" x14ac:dyDescent="0.25"/>
-    <row r="779" x14ac:dyDescent="0.25"/>
-    <row r="780" x14ac:dyDescent="0.25"/>
-    <row r="781" x14ac:dyDescent="0.25"/>
-    <row r="782" x14ac:dyDescent="0.25"/>
-    <row r="783" x14ac:dyDescent="0.25"/>
-    <row r="784" x14ac:dyDescent="0.25"/>
-    <row r="785" x14ac:dyDescent="0.25"/>
-    <row r="786" x14ac:dyDescent="0.25"/>
-    <row r="787" x14ac:dyDescent="0.25"/>
-    <row r="788" x14ac:dyDescent="0.25"/>
-    <row r="789" x14ac:dyDescent="0.25"/>
-    <row r="790" x14ac:dyDescent="0.25"/>
-    <row r="791" x14ac:dyDescent="0.25"/>
-    <row r="792" x14ac:dyDescent="0.25"/>
-    <row r="793" x14ac:dyDescent="0.25"/>
-    <row r="794" x14ac:dyDescent="0.25"/>
-    <row r="795" x14ac:dyDescent="0.25"/>
-    <row r="796" x14ac:dyDescent="0.25"/>
-    <row r="797" x14ac:dyDescent="0.25"/>
-    <row r="798" x14ac:dyDescent="0.25"/>
-    <row r="799" x14ac:dyDescent="0.25"/>
-    <row r="800" x14ac:dyDescent="0.25"/>
-    <row r="801" x14ac:dyDescent="0.25"/>
-    <row r="802" x14ac:dyDescent="0.25"/>
-    <row r="803" x14ac:dyDescent="0.25"/>
-    <row r="804" x14ac:dyDescent="0.25"/>
-    <row r="805" x14ac:dyDescent="0.25"/>
-    <row r="806" x14ac:dyDescent="0.25"/>
-    <row r="807" x14ac:dyDescent="0.25"/>
-    <row r="808" x14ac:dyDescent="0.25"/>
-    <row r="809" x14ac:dyDescent="0.25"/>
-    <row r="810" x14ac:dyDescent="0.25"/>
-    <row r="811" x14ac:dyDescent="0.25"/>
-    <row r="812" x14ac:dyDescent="0.25"/>
-    <row r="813" x14ac:dyDescent="0.25"/>
-    <row r="814" x14ac:dyDescent="0.25"/>
-    <row r="815" x14ac:dyDescent="0.25"/>
-    <row r="816" x14ac:dyDescent="0.25"/>
-    <row r="817" x14ac:dyDescent="0.25"/>
-    <row r="818" x14ac:dyDescent="0.25"/>
-    <row r="819" x14ac:dyDescent="0.25"/>
-    <row r="820" x14ac:dyDescent="0.25"/>
-    <row r="821" x14ac:dyDescent="0.25"/>
-    <row r="822" x14ac:dyDescent="0.25"/>
-    <row r="823" x14ac:dyDescent="0.25"/>
-    <row r="824" x14ac:dyDescent="0.25"/>
-    <row r="825" x14ac:dyDescent="0.25"/>
-    <row r="826" x14ac:dyDescent="0.25"/>
-    <row r="827" x14ac:dyDescent="0.25"/>
-    <row r="828" x14ac:dyDescent="0.25"/>
-    <row r="829" x14ac:dyDescent="0.25"/>
-    <row r="830" x14ac:dyDescent="0.25"/>
-    <row r="831" x14ac:dyDescent="0.25"/>
-    <row r="832" x14ac:dyDescent="0.25"/>
-    <row r="833" x14ac:dyDescent="0.25"/>
-    <row r="834" x14ac:dyDescent="0.25"/>
-    <row r="835" x14ac:dyDescent="0.25"/>
-    <row r="836" x14ac:dyDescent="0.25"/>
-    <row r="837" x14ac:dyDescent="0.25"/>
-    <row r="838" x14ac:dyDescent="0.25"/>
-    <row r="839" x14ac:dyDescent="0.25"/>
-    <row r="840" x14ac:dyDescent="0.25"/>
-    <row r="841" x14ac:dyDescent="0.25"/>
-    <row r="842" x14ac:dyDescent="0.25"/>
-    <row r="843" x14ac:dyDescent="0.25"/>
-    <row r="844" x14ac:dyDescent="0.25"/>
-    <row r="845" x14ac:dyDescent="0.25"/>
-    <row r="846" x14ac:dyDescent="0.25"/>
-    <row r="847" x14ac:dyDescent="0.25"/>
-    <row r="848" x14ac:dyDescent="0.25"/>
-    <row r="849" x14ac:dyDescent="0.25"/>
-    <row r="850" x14ac:dyDescent="0.25"/>
-    <row r="851" x14ac:dyDescent="0.25"/>
-    <row r="852" x14ac:dyDescent="0.25"/>
-    <row r="853" x14ac:dyDescent="0.25"/>
-    <row r="854" x14ac:dyDescent="0.25"/>
-    <row r="855" x14ac:dyDescent="0.25"/>
-    <row r="856" x14ac:dyDescent="0.25"/>
-    <row r="857" x14ac:dyDescent="0.25"/>
-    <row r="858" x14ac:dyDescent="0.25"/>
-    <row r="859" x14ac:dyDescent="0.25"/>
-    <row r="860" x14ac:dyDescent="0.25"/>
-    <row r="861" x14ac:dyDescent="0.25"/>
-    <row r="862" x14ac:dyDescent="0.25"/>
-    <row r="863" x14ac:dyDescent="0.25"/>
-    <row r="864" x14ac:dyDescent="0.25"/>
-    <row r="865" x14ac:dyDescent="0.25"/>
-    <row r="866" x14ac:dyDescent="0.25"/>
-    <row r="867" x14ac:dyDescent="0.25"/>
-    <row r="868" x14ac:dyDescent="0.25"/>
-    <row r="869" x14ac:dyDescent="0.25"/>
-    <row r="870" x14ac:dyDescent="0.25"/>
-    <row r="871" x14ac:dyDescent="0.25"/>
-    <row r="872" x14ac:dyDescent="0.25"/>
-    <row r="873" x14ac:dyDescent="0.25"/>
-    <row r="874" x14ac:dyDescent="0.25"/>
-    <row r="875" x14ac:dyDescent="0.25"/>
-    <row r="876" x14ac:dyDescent="0.25"/>
-    <row r="877" x14ac:dyDescent="0.25"/>
-    <row r="878" x14ac:dyDescent="0.25"/>
-    <row r="879" x14ac:dyDescent="0.25"/>
-    <row r="880" x14ac:dyDescent="0.25"/>
-    <row r="881" x14ac:dyDescent="0.25"/>
-    <row r="882" x14ac:dyDescent="0.25"/>
-    <row r="883" x14ac:dyDescent="0.25"/>
-    <row r="884" x14ac:dyDescent="0.25"/>
-    <row r="885" x14ac:dyDescent="0.25"/>
-    <row r="886" x14ac:dyDescent="0.25"/>
-    <row r="887" x14ac:dyDescent="0.25"/>
-    <row r="888" x14ac:dyDescent="0.25"/>
-    <row r="889" x14ac:dyDescent="0.25"/>
-    <row r="890" x14ac:dyDescent="0.25"/>
-    <row r="891" x14ac:dyDescent="0.25"/>
-    <row r="892" x14ac:dyDescent="0.25"/>
-    <row r="893" x14ac:dyDescent="0.25"/>
-    <row r="894" x14ac:dyDescent="0.25"/>
-    <row r="895" x14ac:dyDescent="0.25"/>
-    <row r="896" x14ac:dyDescent="0.25"/>
-    <row r="897" x14ac:dyDescent="0.25"/>
-    <row r="898" x14ac:dyDescent="0.25"/>
-    <row r="899" x14ac:dyDescent="0.25"/>
-    <row r="900" x14ac:dyDescent="0.25"/>
-    <row r="901" x14ac:dyDescent="0.25"/>
-    <row r="902" x14ac:dyDescent="0.25"/>
-    <row r="903" x14ac:dyDescent="0.25"/>
-    <row r="904" x14ac:dyDescent="0.25"/>
-    <row r="905" x14ac:dyDescent="0.25"/>
-    <row r="906" x14ac:dyDescent="0.25"/>
-    <row r="907" x14ac:dyDescent="0.25"/>
-    <row r="908" x14ac:dyDescent="0.25"/>
-    <row r="909" x14ac:dyDescent="0.25"/>
-    <row r="910" x14ac:dyDescent="0.25"/>
-    <row r="911" x14ac:dyDescent="0.25"/>
-    <row r="912" x14ac:dyDescent="0.25"/>
-    <row r="913" x14ac:dyDescent="0.25"/>
-    <row r="914" x14ac:dyDescent="0.25"/>
-    <row r="915" x14ac:dyDescent="0.25"/>
-    <row r="916" x14ac:dyDescent="0.25"/>
-    <row r="917" x14ac:dyDescent="0.25"/>
-    <row r="918" x14ac:dyDescent="0.25"/>
-    <row r="919" x14ac:dyDescent="0.25"/>
-    <row r="920" x14ac:dyDescent="0.25"/>
-    <row r="921" x14ac:dyDescent="0.25"/>
-    <row r="922" x14ac:dyDescent="0.25"/>
-    <row r="923" x14ac:dyDescent="0.25"/>
-    <row r="924" x14ac:dyDescent="0.25"/>
-    <row r="925" x14ac:dyDescent="0.25"/>
-    <row r="926" x14ac:dyDescent="0.25"/>
-    <row r="927" x14ac:dyDescent="0.25"/>
-    <row r="928" x14ac:dyDescent="0.25"/>
-    <row r="929" x14ac:dyDescent="0.25"/>
-    <row r="930" x14ac:dyDescent="0.25"/>
-    <row r="931" x14ac:dyDescent="0.25"/>
-    <row r="932" x14ac:dyDescent="0.25"/>
-    <row r="933" x14ac:dyDescent="0.25"/>
-    <row r="934" x14ac:dyDescent="0.25"/>
-    <row r="935" x14ac:dyDescent="0.25"/>
-    <row r="936" x14ac:dyDescent="0.25"/>
-    <row r="937" x14ac:dyDescent="0.25"/>
-    <row r="938" x14ac:dyDescent="0.25"/>
-    <row r="939" x14ac:dyDescent="0.25"/>
-    <row r="940" x14ac:dyDescent="0.25"/>
-    <row r="941" x14ac:dyDescent="0.25"/>
-    <row r="942" x14ac:dyDescent="0.25"/>
-    <row r="943" x14ac:dyDescent="0.25"/>
-    <row r="944" x14ac:dyDescent="0.25"/>
-    <row r="945" x14ac:dyDescent="0.25"/>
-    <row r="946" x14ac:dyDescent="0.25"/>
-    <row r="947" x14ac:dyDescent="0.25"/>
-    <row r="948" x14ac:dyDescent="0.25"/>
-    <row r="949" x14ac:dyDescent="0.25"/>
-    <row r="950" x14ac:dyDescent="0.25"/>
-    <row r="951" x14ac:dyDescent="0.25"/>
-    <row r="952" x14ac:dyDescent="0.25"/>
-    <row r="953" x14ac:dyDescent="0.25"/>
-    <row r="954" x14ac:dyDescent="0.25"/>
-    <row r="955" x14ac:dyDescent="0.25"/>
-    <row r="956" x14ac:dyDescent="0.25"/>
-    <row r="957" x14ac:dyDescent="0.25"/>
-    <row r="958" x14ac:dyDescent="0.25"/>
-    <row r="959" x14ac:dyDescent="0.25"/>
-    <row r="960" x14ac:dyDescent="0.25"/>
-    <row r="961" x14ac:dyDescent="0.25"/>
-    <row r="962" x14ac:dyDescent="0.25"/>
-    <row r="963" x14ac:dyDescent="0.25"/>
-    <row r="964" x14ac:dyDescent="0.25"/>
-    <row r="965" x14ac:dyDescent="0.25"/>
-    <row r="966" x14ac:dyDescent="0.25"/>
-    <row r="967" x14ac:dyDescent="0.25"/>
-    <row r="968" x14ac:dyDescent="0.25"/>
-    <row r="969" x14ac:dyDescent="0.25"/>
-    <row r="970" x14ac:dyDescent="0.25"/>
-    <row r="971" x14ac:dyDescent="0.25"/>
-    <row r="972" x14ac:dyDescent="0.25"/>
-    <row r="973" x14ac:dyDescent="0.25"/>
-    <row r="974" x14ac:dyDescent="0.25"/>
-    <row r="975" x14ac:dyDescent="0.25"/>
-    <row r="976" x14ac:dyDescent="0.25"/>
-    <row r="977" x14ac:dyDescent="0.25"/>
-    <row r="978" x14ac:dyDescent="0.25"/>
-    <row r="979" x14ac:dyDescent="0.25"/>
-    <row r="980" x14ac:dyDescent="0.25"/>
-    <row r="981" x14ac:dyDescent="0.25"/>
-    <row r="982" x14ac:dyDescent="0.25"/>
-    <row r="983" x14ac:dyDescent="0.25"/>
-    <row r="984" x14ac:dyDescent="0.25"/>
-    <row r="985" x14ac:dyDescent="0.25"/>
-    <row r="986" x14ac:dyDescent="0.25"/>
-    <row r="987" x14ac:dyDescent="0.25"/>
-    <row r="988" x14ac:dyDescent="0.25"/>
-    <row r="989" x14ac:dyDescent="0.25"/>
-    <row r="990" x14ac:dyDescent="0.25"/>
-    <row r="991" x14ac:dyDescent="0.25"/>
-    <row r="992" x14ac:dyDescent="0.25"/>
-    <row r="993" x14ac:dyDescent="0.25"/>
-    <row r="994" x14ac:dyDescent="0.25"/>
-    <row r="995" x14ac:dyDescent="0.25"/>
-    <row r="996" x14ac:dyDescent="0.25"/>
-    <row r="997" x14ac:dyDescent="0.25"/>
-    <row r="998" x14ac:dyDescent="0.25"/>
-    <row r="999" x14ac:dyDescent="0.25"/>
-    <row r="1000" x14ac:dyDescent="0.25"/>
-    <row r="1001" x14ac:dyDescent="0.25"/>
-    <row r="1002" x14ac:dyDescent="0.25"/>
-    <row r="1003" x14ac:dyDescent="0.25"/>
-    <row r="1004" x14ac:dyDescent="0.25"/>
-    <row r="1005" x14ac:dyDescent="0.25"/>
-    <row r="1006" x14ac:dyDescent="0.25"/>
-    <row r="1007" x14ac:dyDescent="0.25"/>
-    <row r="1008" x14ac:dyDescent="0.25"/>
-    <row r="1009" x14ac:dyDescent="0.25"/>
-    <row r="1010" x14ac:dyDescent="0.25"/>
-    <row r="1011" x14ac:dyDescent="0.25"/>
-    <row r="1012" x14ac:dyDescent="0.25"/>
-    <row r="1013" x14ac:dyDescent="0.25"/>
-    <row r="1014" x14ac:dyDescent="0.25"/>
-    <row r="1015" x14ac:dyDescent="0.25"/>
-    <row r="1016" x14ac:dyDescent="0.25"/>
-    <row r="1017" x14ac:dyDescent="0.25"/>
-    <row r="1018" x14ac:dyDescent="0.25"/>
-    <row r="1019" x14ac:dyDescent="0.25"/>
-    <row r="1020" x14ac:dyDescent="0.25"/>
-    <row r="1021" x14ac:dyDescent="0.25"/>
-    <row r="1022" x14ac:dyDescent="0.25"/>
-    <row r="1023" x14ac:dyDescent="0.25"/>
-    <row r="1024" x14ac:dyDescent="0.25"/>
-    <row r="1025" x14ac:dyDescent="0.25"/>
-    <row r="1026" x14ac:dyDescent="0.25"/>
-    <row r="1027" x14ac:dyDescent="0.25"/>
-    <row r="1028" x14ac:dyDescent="0.25"/>
-    <row r="1029" x14ac:dyDescent="0.25"/>
-    <row r="1030" x14ac:dyDescent="0.25"/>
-    <row r="1031" x14ac:dyDescent="0.25"/>
-    <row r="1032" x14ac:dyDescent="0.25"/>
-    <row r="1033" x14ac:dyDescent="0.25"/>
-    <row r="1034" x14ac:dyDescent="0.25"/>
-    <row r="1035" x14ac:dyDescent="0.25"/>
-    <row r="1036" x14ac:dyDescent="0.25"/>
-    <row r="1037" x14ac:dyDescent="0.25"/>
-    <row r="1038" x14ac:dyDescent="0.25"/>
-    <row r="1039" x14ac:dyDescent="0.25"/>
-    <row r="1040" x14ac:dyDescent="0.25"/>
-    <row r="1041" x14ac:dyDescent="0.25"/>
-    <row r="1042" x14ac:dyDescent="0.25"/>
-    <row r="1043" x14ac:dyDescent="0.25"/>
-    <row r="1044" x14ac:dyDescent="0.25"/>
-    <row r="1045" x14ac:dyDescent="0.25"/>
-    <row r="1046" x14ac:dyDescent="0.25"/>
-    <row r="1047" x14ac:dyDescent="0.25"/>
-    <row r="1048" x14ac:dyDescent="0.25"/>
-    <row r="1049" x14ac:dyDescent="0.25"/>
-    <row r="1050" x14ac:dyDescent="0.25"/>
-    <row r="1051" x14ac:dyDescent="0.25"/>
-    <row r="1052" x14ac:dyDescent="0.25"/>
-    <row r="1053" x14ac:dyDescent="0.25"/>
-    <row r="1054" x14ac:dyDescent="0.25"/>
-    <row r="1055" x14ac:dyDescent="0.25"/>
-    <row r="1056" x14ac:dyDescent="0.25"/>
-    <row r="1057" x14ac:dyDescent="0.25"/>
-    <row r="1058" x14ac:dyDescent="0.25"/>
-    <row r="1059" x14ac:dyDescent="0.25"/>
-    <row r="1060" x14ac:dyDescent="0.25"/>
-    <row r="1061" x14ac:dyDescent="0.25"/>
-    <row r="1062" x14ac:dyDescent="0.25"/>
-    <row r="1063" x14ac:dyDescent="0.25"/>
-    <row r="1064" x14ac:dyDescent="0.25"/>
-    <row r="1065" x14ac:dyDescent="0.25"/>
-    <row r="1066" x14ac:dyDescent="0.25"/>
-    <row r="1067" x14ac:dyDescent="0.25"/>
-    <row r="1068" x14ac:dyDescent="0.25"/>
-    <row r="1069" x14ac:dyDescent="0.25"/>
-    <row r="1070" x14ac:dyDescent="0.25"/>
-    <row r="1071" x14ac:dyDescent="0.25"/>
-    <row r="1072" x14ac:dyDescent="0.25"/>
-    <row r="1073" x14ac:dyDescent="0.25"/>
-    <row r="1074" x14ac:dyDescent="0.25"/>
-    <row r="1075" x14ac:dyDescent="0.25"/>
-    <row r="1076" x14ac:dyDescent="0.25"/>
-    <row r="1077" x14ac:dyDescent="0.25"/>
-    <row r="1078" x14ac:dyDescent="0.25"/>
-    <row r="1079" x14ac:dyDescent="0.25"/>
-    <row r="1080" x14ac:dyDescent="0.25"/>
-    <row r="1081" x14ac:dyDescent="0.25"/>
-    <row r="1082" x14ac:dyDescent="0.25"/>
-    <row r="1083" x14ac:dyDescent="0.25"/>
-    <row r="1084" x14ac:dyDescent="0.25"/>
-    <row r="1085" x14ac:dyDescent="0.25"/>
-    <row r="1086" x14ac:dyDescent="0.25"/>
-    <row r="1087" x14ac:dyDescent="0.25"/>
-    <row r="1088" x14ac:dyDescent="0.25"/>
-    <row r="1089" x14ac:dyDescent="0.25"/>
-    <row r="1090" x14ac:dyDescent="0.25"/>
-    <row r="1091" x14ac:dyDescent="0.25"/>
-    <row r="1092" x14ac:dyDescent="0.25"/>
-    <row r="1093" x14ac:dyDescent="0.25"/>
-    <row r="1094" x14ac:dyDescent="0.25"/>
-    <row r="1095" x14ac:dyDescent="0.25"/>
-    <row r="1096" x14ac:dyDescent="0.25"/>
-    <row r="1097" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1001" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1002" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1003" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1004" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1005" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1006" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1007" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1008" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1009" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1010" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1011" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1012" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1013" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1014" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1015" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1016" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1017" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1018" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1019" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1020" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1021" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1022" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1023" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1024" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1025" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1026" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1027" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1028" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1029" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1030" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1031" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1032" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1033" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1034" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1035" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1036" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1037" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1038" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1039" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1040" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1041" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1042" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1043" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1044" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1045" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1046" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1047" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1048" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1049" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1050" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1051" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1052" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1053" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1054" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1055" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1056" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1057" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1058" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1059" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1060" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1061" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1062" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1063" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1064" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1065" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1066" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1067" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1068" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1069" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1070" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1071" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1072" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1073" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1074" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1075" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1076" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1077" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1078" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1079" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1080" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1081" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1082" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1083" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1084" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1085" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1086" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1087" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1088" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1089" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1090" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1091" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1092" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1093" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1094" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1095" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1096" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1097" ht="13.2" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:D192" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D192">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A167:D192">
       <sortCondition ref="A1:A192"/>
     </sortState>
   </autoFilter>
@@ -4374,6 +4381,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A162FC-7907-44C7-A909-E8E1323EC5F6}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G300"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4410,7 +4418,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>199</v>
       </c>
@@ -4429,7 +4437,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>199</v>
       </c>
@@ -4446,7 +4454,7 @@
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>199</v>
       </c>
@@ -4463,7 +4471,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>199</v>
       </c>
@@ -4480,7 +4488,7 @@
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>128</v>
       </c>
@@ -4499,7 +4507,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>128</v>
       </c>
@@ -4516,7 +4524,7 @@
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>128</v>
       </c>
@@ -4533,7 +4541,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>128</v>
       </c>
@@ -4550,16 +4558,16 @@
         <v>176</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>128</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C10" s="8">
         <v>1</v>
@@ -4569,13 +4577,13 @@
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>128</v>
       </c>
@@ -4594,7 +4602,7 @@
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>128</v>
       </c>
@@ -4611,7 +4619,7 @@
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>128</v>
       </c>
@@ -4628,7 +4636,7 @@
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>128</v>
       </c>
@@ -4645,7 +4653,7 @@
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>128</v>
       </c>
@@ -4662,7 +4670,7 @@
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>128</v>
       </c>
@@ -4681,7 +4689,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>128</v>
       </c>
@@ -4698,7 +4706,7 @@
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>128</v>
       </c>
@@ -4715,7 +4723,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>128</v>
       </c>
@@ -4732,7 +4740,7 @@
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>128</v>
       </c>
@@ -4749,7 +4757,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>119</v>
       </c>
@@ -4764,7 +4772,7 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>119</v>
       </c>
@@ -4779,7 +4787,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>119</v>
       </c>
@@ -4794,7 +4802,7 @@
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>119</v>
       </c>
@@ -4809,7 +4817,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>119</v>
       </c>
@@ -4824,7 +4832,7 @@
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>119</v>
       </c>
@@ -4839,7 +4847,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>119</v>
       </c>
@@ -4854,7 +4862,7 @@
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>119</v>
       </c>
@@ -4869,7 +4877,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>119</v>
       </c>
@@ -4884,7 +4892,7 @@
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>119</v>
       </c>
@@ -4899,7 +4907,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>119</v>
       </c>
@@ -4914,7 +4922,7 @@
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>119</v>
       </c>
@@ -4929,7 +4937,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>119</v>
       </c>
@@ -4944,7 +4952,7 @@
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>119</v>
       </c>
@@ -4959,7 +4967,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>119</v>
       </c>
@@ -4974,7 +4982,7 @@
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>119</v>
       </c>
@@ -4989,7 +4997,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="8"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>119</v>
       </c>
@@ -5004,7 +5012,7 @@
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>119</v>
       </c>
@@ -5019,7 +5027,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>119</v>
       </c>
@@ -5034,7 +5042,7 @@
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>119</v>
       </c>
@@ -5049,7 +5057,7 @@
       <c r="F40" s="8"/>
       <c r="G40" s="8"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>119</v>
       </c>
@@ -5064,7 +5072,7 @@
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>119</v>
       </c>
@@ -5079,7 +5087,7 @@
       <c r="F42" s="8"/>
       <c r="G42" s="8"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>119</v>
       </c>
@@ -5094,7 +5102,7 @@
       <c r="F43" s="8"/>
       <c r="G43" s="8"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
         <v>119</v>
       </c>
@@ -5109,7 +5117,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>119</v>
       </c>
@@ -5124,7 +5132,7 @@
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>119</v>
       </c>
@@ -5139,7 +5147,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
     </row>
-    <row r="47" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>118</v>
       </c>
@@ -5158,7 +5166,7 @@
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>118</v>
       </c>
@@ -5175,7 +5183,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
         <v>118</v>
       </c>
@@ -5192,7 +5200,7 @@
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
         <v>118</v>
       </c>
@@ -5209,7 +5217,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="8"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
         <v>118</v>
       </c>
@@ -5226,7 +5234,7 @@
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
         <v>118</v>
       </c>
@@ -5243,7 +5251,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="8"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
         <v>118</v>
       </c>
@@ -5260,7 +5268,7 @@
       <c r="F53" s="8"/>
       <c r="G53" s="8"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
         <v>118</v>
       </c>
@@ -5277,7 +5285,7 @@
       <c r="F54" s="8"/>
       <c r="G54" s="8"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
         <v>118</v>
       </c>
@@ -5294,7 +5302,7 @@
       <c r="F55" s="8"/>
       <c r="G55" s="8"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>118</v>
       </c>
@@ -5311,7 +5319,7 @@
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
         <v>118</v>
       </c>
@@ -5328,7 +5336,7 @@
       <c r="F57" s="8"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
         <v>118</v>
       </c>
@@ -5345,7 +5353,7 @@
       <c r="F58" s="8"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
         <v>118</v>
       </c>
@@ -5362,7 +5370,7 @@
       <c r="F59" s="8"/>
       <c r="G59" s="8"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
         <v>118</v>
       </c>
@@ -5379,7 +5387,7 @@
       <c r="F60" s="8"/>
       <c r="G60" s="8"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
         <v>118</v>
       </c>
@@ -5396,7 +5404,7 @@
       <c r="F61" s="8"/>
       <c r="G61" s="8"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
         <v>118</v>
       </c>
@@ -5413,7 +5421,7 @@
       <c r="F62" s="8"/>
       <c r="G62" s="8"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
         <v>118</v>
       </c>
@@ -5430,7 +5438,7 @@
       <c r="F63" s="8"/>
       <c r="G63" s="8"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
         <v>118</v>
       </c>
@@ -5447,7 +5455,7 @@
       <c r="F64" s="8"/>
       <c r="G64" s="8"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>118</v>
       </c>
@@ -5464,7 +5472,7 @@
       <c r="F65" s="8"/>
       <c r="G65" s="8"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
         <v>118</v>
       </c>
@@ -5481,7 +5489,7 @@
       <c r="F66" s="8"/>
       <c r="G66" s="8"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
         <v>118</v>
       </c>
@@ -5498,7 +5506,7 @@
       <c r="F67" s="8"/>
       <c r="G67" s="8"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
         <v>118</v>
       </c>
@@ -5515,7 +5523,7 @@
       <c r="F68" s="8"/>
       <c r="G68" s="8"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
         <v>118</v>
       </c>
@@ -5532,7 +5540,7 @@
       <c r="F69" s="8"/>
       <c r="G69" s="8"/>
     </row>
-    <row r="70" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
         <v>117</v>
       </c>
@@ -5551,7 +5559,7 @@
       <c r="F70" s="8"/>
       <c r="G70" s="8"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
         <v>117</v>
       </c>
@@ -5568,7 +5576,7 @@
       <c r="F71" s="8"/>
       <c r="G71" s="8"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
         <v>117</v>
       </c>
@@ -5585,7 +5593,7 @@
       <c r="F72" s="8"/>
       <c r="G72" s="8"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
         <v>117</v>
       </c>
@@ -5602,7 +5610,7 @@
       <c r="F73" s="8"/>
       <c r="G73" s="8"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
         <v>117</v>
       </c>
@@ -5619,7 +5627,7 @@
       <c r="F74" s="8"/>
       <c r="G74" s="8"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
         <v>117</v>
       </c>
@@ -5636,7 +5644,7 @@
       <c r="F75" s="8"/>
       <c r="G75" s="8"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
         <v>117</v>
       </c>
@@ -5653,7 +5661,7 @@
       <c r="F76" s="8"/>
       <c r="G76" s="8"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
         <v>117</v>
       </c>
@@ -5670,7 +5678,7 @@
       <c r="F77" s="8"/>
       <c r="G77" s="8"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="8" t="s">
         <v>113</v>
       </c>
@@ -5685,7 +5693,7 @@
       <c r="F78" s="8"/>
       <c r="G78" s="8"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
         <v>113</v>
       </c>
@@ -5700,7 +5708,7 @@
       <c r="F79" s="8"/>
       <c r="G79" s="8"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="8" t="s">
         <v>113</v>
       </c>
@@ -5715,7 +5723,7 @@
       <c r="F80" s="8"/>
       <c r="G80" s="8"/>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
         <v>113</v>
       </c>
@@ -5730,7 +5738,7 @@
       <c r="F81" s="8"/>
       <c r="G81" s="8"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
         <v>113</v>
       </c>
@@ -5745,7 +5753,7 @@
       <c r="F82" s="8"/>
       <c r="G82" s="8"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
         <v>113</v>
       </c>
@@ -5760,7 +5768,7 @@
       <c r="F83" s="8"/>
       <c r="G83" s="8"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="8" t="s">
         <v>113</v>
       </c>
@@ -5775,7 +5783,7 @@
       <c r="F84" s="8"/>
       <c r="G84" s="8"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
         <v>113</v>
       </c>
@@ -5790,7 +5798,7 @@
       <c r="F85" s="8"/>
       <c r="G85" s="8"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="8" t="s">
         <v>113</v>
       </c>
@@ -5805,7 +5813,7 @@
       <c r="F86" s="8"/>
       <c r="G86" s="8"/>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
         <v>113</v>
       </c>
@@ -5820,7 +5828,7 @@
       <c r="F87" s="8"/>
       <c r="G87" s="8"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="8" t="s">
         <v>113</v>
       </c>
@@ -5835,7 +5843,7 @@
       <c r="F88" s="8"/>
       <c r="G88" s="8"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
         <v>113</v>
       </c>
@@ -5850,7 +5858,7 @@
       <c r="F89" s="8"/>
       <c r="G89" s="8"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="8" t="s">
         <v>113</v>
       </c>
@@ -5865,7 +5873,7 @@
       <c r="F90" s="8"/>
       <c r="G90" s="8"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
         <v>113</v>
       </c>
@@ -5880,7 +5888,7 @@
       <c r="F91" s="8"/>
       <c r="G91" s="8"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
         <v>113</v>
       </c>
@@ -5895,7 +5903,7 @@
       <c r="F92" s="8"/>
       <c r="G92" s="8"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
         <v>113</v>
       </c>
@@ -5910,7 +5918,7 @@
       <c r="F93" s="8"/>
       <c r="G93" s="8"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="8" t="s">
         <v>33</v>
       </c>
@@ -5925,7 +5933,7 @@
       <c r="F94" s="8"/>
       <c r="G94" s="8"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
         <v>33</v>
       </c>
@@ -5940,7 +5948,7 @@
       <c r="F95" s="8"/>
       <c r="G95" s="8"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="8" t="s">
         <v>33</v>
       </c>
@@ -5955,7 +5963,7 @@
       <c r="F96" s="8"/>
       <c r="G96" s="8"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
         <v>33</v>
       </c>
@@ -5970,7 +5978,7 @@
       <c r="F97" s="8"/>
       <c r="G97" s="8"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="8" t="s">
         <v>33</v>
       </c>
@@ -5985,7 +5993,7 @@
       <c r="F98" s="8"/>
       <c r="G98" s="8"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
         <v>33</v>
       </c>
@@ -6000,7 +6008,7 @@
       <c r="F99" s="8"/>
       <c r="G99" s="8"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="8" t="s">
         <v>33</v>
       </c>
@@ -6015,7 +6023,7 @@
       <c r="F100" s="8"/>
       <c r="G100" s="8"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
         <v>33</v>
       </c>
@@ -6030,7 +6038,7 @@
       <c r="F101" s="8"/>
       <c r="G101" s="8"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="8" t="s">
         <v>33</v>
       </c>
@@ -6045,7 +6053,7 @@
       <c r="F102" s="8"/>
       <c r="G102" s="8"/>
     </row>
-    <row r="103" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" ht="66" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
         <v>36</v>
       </c>
@@ -6064,7 +6072,7 @@
       <c r="F103" s="8"/>
       <c r="G103" s="8"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="8" t="s">
         <v>36</v>
       </c>
@@ -6081,7 +6089,7 @@
       <c r="F104" s="8"/>
       <c r="G104" s="8"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
         <v>36</v>
       </c>
@@ -6098,7 +6106,7 @@
       <c r="F105" s="8"/>
       <c r="G105" s="8"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="8" t="s">
         <v>36</v>
       </c>
@@ -6115,7 +6123,7 @@
       <c r="F106" s="8"/>
       <c r="G106" s="8"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
         <v>36</v>
       </c>
@@ -6132,7 +6140,7 @@
       <c r="F107" s="8"/>
       <c r="G107" s="8"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="8" t="s">
         <v>36</v>
       </c>
@@ -6149,7 +6157,7 @@
       <c r="F108" s="8"/>
       <c r="G108" s="8"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
         <v>36</v>
       </c>
@@ -6166,7 +6174,7 @@
       <c r="F109" s="8"/>
       <c r="G109" s="8"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="8" t="s">
         <v>36</v>
       </c>
@@ -6183,7 +6191,7 @@
       <c r="F110" s="8"/>
       <c r="G110" s="8"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
         <v>36</v>
       </c>
@@ -6200,7 +6208,7 @@
       <c r="F111" s="8"/>
       <c r="G111" s="8"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="8" t="s">
         <v>36</v>
       </c>
@@ -6217,7 +6225,7 @@
       <c r="F112" s="8"/>
       <c r="G112" s="8"/>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
         <v>36</v>
       </c>
@@ -6234,7 +6242,7 @@
       <c r="F113" s="8"/>
       <c r="G113" s="8"/>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
         <v>36</v>
       </c>
@@ -6251,7 +6259,7 @@
       <c r="F114" s="8"/>
       <c r="G114" s="8"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
         <v>36</v>
       </c>
@@ -6268,7 +6276,7 @@
       <c r="F115" s="8"/>
       <c r="G115" s="8"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="8" t="s">
         <v>36</v>
       </c>
@@ -6285,7 +6293,7 @@
       <c r="F116" s="8"/>
       <c r="G116" s="8"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
         <v>36</v>
       </c>
@@ -6302,7 +6310,7 @@
       <c r="F117" s="8"/>
       <c r="G117" s="8"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="8" t="s">
         <v>36</v>
       </c>
@@ -6319,7 +6327,7 @@
       <c r="F118" s="8"/>
       <c r="G118" s="8"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
         <v>36</v>
       </c>
@@ -6336,7 +6344,7 @@
       <c r="F119" s="8"/>
       <c r="G119" s="8"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="8" t="s">
         <v>40</v>
       </c>
@@ -6351,7 +6359,7 @@
       <c r="F120" s="8"/>
       <c r="G120" s="8"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
         <v>40</v>
       </c>
@@ -6366,7 +6374,7 @@
       <c r="F121" s="8"/>
       <c r="G121" s="8"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="8" t="s">
         <v>40</v>
       </c>
@@ -6381,7 +6389,7 @@
       <c r="F122" s="8"/>
       <c r="G122" s="8"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
         <v>40</v>
       </c>
@@ -6396,7 +6404,7 @@
       <c r="F123" s="8"/>
       <c r="G123" s="8"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="8" t="s">
         <v>40</v>
       </c>
@@ -6411,7 +6419,7 @@
       <c r="F124" s="8"/>
       <c r="G124" s="8"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
         <v>40</v>
       </c>
@@ -6426,7 +6434,7 @@
       <c r="F125" s="8"/>
       <c r="G125" s="8"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="8" t="s">
         <v>40</v>
       </c>
@@ -6441,7 +6449,7 @@
       <c r="F126" s="8"/>
       <c r="G126" s="8"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
         <v>40</v>
       </c>
@@ -6456,7 +6464,7 @@
       <c r="F127" s="8"/>
       <c r="G127" s="8"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="8" t="s">
         <v>40</v>
       </c>
@@ -6471,7 +6479,7 @@
       <c r="F128" s="8"/>
       <c r="G128" s="8"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
         <v>40</v>
       </c>
@@ -6486,7 +6494,7 @@
       <c r="F129" s="8"/>
       <c r="G129" s="8"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="8" t="s">
         <v>40</v>
       </c>
@@ -6501,7 +6509,7 @@
       <c r="F130" s="8"/>
       <c r="G130" s="8"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
         <v>40</v>
       </c>
@@ -6516,7 +6524,7 @@
       <c r="F131" s="8"/>
       <c r="G131" s="8"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="8" t="s">
         <v>40</v>
       </c>
@@ -6531,7 +6539,7 @@
       <c r="F132" s="8"/>
       <c r="G132" s="8"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
         <v>40</v>
       </c>
@@ -6546,7 +6554,7 @@
       <c r="F133" s="8"/>
       <c r="G133" s="8"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="8" t="s">
         <v>40</v>
       </c>
@@ -6561,7 +6569,7 @@
       <c r="F134" s="8"/>
       <c r="G134" s="8"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
         <v>40</v>
       </c>
@@ -6576,7 +6584,7 @@
       <c r="F135" s="8"/>
       <c r="G135" s="8"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="8" t="s">
         <v>40</v>
       </c>
@@ -6591,7 +6599,7 @@
       <c r="F136" s="8"/>
       <c r="G136" s="8"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
         <v>40</v>
       </c>
@@ -6606,7 +6614,7 @@
       <c r="F137" s="8"/>
       <c r="G137" s="8"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
         <v>40</v>
       </c>
@@ -6621,7 +6629,7 @@
       <c r="F138" s="8"/>
       <c r="G138" s="8"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
         <v>40</v>
       </c>
@@ -6636,7 +6644,7 @@
       <c r="F139" s="8"/>
       <c r="G139" s="8"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="8" t="s">
         <v>40</v>
       </c>
@@ -6651,7 +6659,7 @@
       <c r="F140" s="8"/>
       <c r="G140" s="8"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
         <v>40</v>
       </c>
@@ -6666,7 +6674,7 @@
       <c r="F141" s="8"/>
       <c r="G141" s="8"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="8" t="s">
         <v>40</v>
       </c>
@@ -6681,7 +6689,7 @@
       <c r="F142" s="8"/>
       <c r="G142" s="8"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
         <v>37</v>
       </c>
@@ -6696,7 +6704,7 @@
       <c r="F143" s="8"/>
       <c r="G143" s="8"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="8" t="s">
         <v>37</v>
       </c>
@@ -6711,7 +6719,7 @@
       <c r="F144" s="8"/>
       <c r="G144" s="8"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
         <v>37</v>
       </c>
@@ -6726,7 +6734,7 @@
       <c r="F145" s="8"/>
       <c r="G145" s="8"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="8" t="s">
         <v>37</v>
       </c>
@@ -6741,7 +6749,7 @@
       <c r="F146" s="8"/>
       <c r="G146" s="8"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
         <v>37</v>
       </c>
@@ -6756,7 +6764,7 @@
       <c r="F147" s="8"/>
       <c r="G147" s="8"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
         <v>37</v>
       </c>
@@ -6771,7 +6779,7 @@
       <c r="F148" s="8"/>
       <c r="G148" s="8"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
         <v>37</v>
       </c>
@@ -6786,7 +6794,7 @@
       <c r="F149" s="8"/>
       <c r="G149" s="8"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="8" t="s">
         <v>37</v>
       </c>
@@ -6801,12 +6809,12 @@
       <c r="F150" s="8"/>
       <c r="G150" s="8"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C151" s="8">
         <v>1</v>
@@ -6816,7 +6824,7 @@
       <c r="F151" s="8"/>
       <c r="G151" s="8"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="8" t="s">
         <v>37</v>
       </c>
@@ -6831,7 +6839,7 @@
       <c r="F152" s="8"/>
       <c r="G152" s="8"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
         <v>37</v>
       </c>
@@ -6846,7 +6854,7 @@
       <c r="F153" s="8"/>
       <c r="G153" s="8"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="8" t="s">
         <v>37</v>
       </c>
@@ -6861,7 +6869,7 @@
       <c r="F154" s="8"/>
       <c r="G154" s="8"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
         <v>37</v>
       </c>
@@ -6876,7 +6884,7 @@
       <c r="F155" s="8"/>
       <c r="G155" s="8"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="8" t="s">
         <v>37</v>
       </c>
@@ -6891,7 +6899,7 @@
       <c r="F156" s="8"/>
       <c r="G156" s="8"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
         <v>37</v>
       </c>
@@ -6906,7 +6914,7 @@
       <c r="F157" s="8"/>
       <c r="G157" s="8"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="8" t="s">
         <v>38</v>
       </c>
@@ -6921,7 +6929,7 @@
       <c r="F158" s="8"/>
       <c r="G158" s="8"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
         <v>38</v>
       </c>
@@ -6936,7 +6944,7 @@
       <c r="F159" s="8"/>
       <c r="G159" s="8"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="8" t="s">
         <v>38</v>
       </c>
@@ -6951,7 +6959,7 @@
       <c r="F160" s="8"/>
       <c r="G160" s="8"/>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
         <v>38</v>
       </c>
@@ -6966,7 +6974,7 @@
       <c r="F161" s="8"/>
       <c r="G161" s="8"/>
     </row>
-    <row r="162" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="8" t="s">
         <v>93</v>
       </c>
@@ -6983,11 +6991,11 @@
         <v>185</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G162" s="8"/>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
         <v>93</v>
       </c>
@@ -7002,10 +7010,10 @@
       </c>
       <c r="E163" s="11"/>
       <c r="F163" s="8" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="8" t="s">
         <v>93</v>
       </c>
@@ -7020,11 +7028,11 @@
       </c>
       <c r="E164" s="11"/>
       <c r="F164" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G164" s="8"/>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
         <v>93</v>
       </c>
@@ -7039,11 +7047,11 @@
       </c>
       <c r="E165" s="11"/>
       <c r="F165" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G165" s="8"/>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="8" t="s">
         <v>93</v>
       </c>
@@ -7058,11 +7066,11 @@
       </c>
       <c r="E166" s="11"/>
       <c r="F166" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G166" s="8"/>
     </row>
-    <row r="167" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
         <v>93</v>
       </c>
@@ -7079,11 +7087,11 @@
         <v>183</v>
       </c>
       <c r="F167" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G167" s="8"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="8" t="s">
         <v>93</v>
       </c>
@@ -7098,11 +7106,11 @@
       </c>
       <c r="E168" s="11"/>
       <c r="F168" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G168" s="8"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
         <v>93</v>
       </c>
@@ -7117,11 +7125,11 @@
       </c>
       <c r="E169" s="11"/>
       <c r="F169" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G169" s="8"/>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
         <v>93</v>
       </c>
@@ -7136,11 +7144,11 @@
       </c>
       <c r="E170" s="11"/>
       <c r="F170" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G170" s="8"/>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
         <v>93</v>
       </c>
@@ -7155,11 +7163,11 @@
       </c>
       <c r="E171" s="11"/>
       <c r="F171" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G171" s="8"/>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="8" t="s">
         <v>93</v>
       </c>
@@ -7174,11 +7182,11 @@
       </c>
       <c r="E172" s="11"/>
       <c r="F172" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G172" s="8"/>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
         <v>93</v>
       </c>
@@ -7193,11 +7201,11 @@
       </c>
       <c r="E173" s="11"/>
       <c r="F173" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G173" s="8"/>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="8" t="s">
         <v>93</v>
       </c>
@@ -7212,11 +7220,11 @@
       </c>
       <c r="E174" s="11"/>
       <c r="F174" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G174" s="8"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
         <v>93</v>
       </c>
@@ -7231,11 +7239,11 @@
       </c>
       <c r="E175" s="11"/>
       <c r="F175" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G175" s="8"/>
     </row>
-    <row r="176" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="8" t="s">
         <v>93</v>
       </c>
@@ -7252,11 +7260,11 @@
         <v>184</v>
       </c>
       <c r="F176" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G176" s="8"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
         <v>93</v>
       </c>
@@ -7271,11 +7279,11 @@
       </c>
       <c r="E177" s="11"/>
       <c r="F177" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G177" s="8"/>
     </row>
-    <row r="178" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="8" t="s">
         <v>82</v>
       </c>
@@ -7292,11 +7300,11 @@
         <v>194</v>
       </c>
       <c r="F178" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G178" s="8"/>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
         <v>82</v>
       </c>
@@ -7311,11 +7319,11 @@
       </c>
       <c r="E179" s="11"/>
       <c r="F179" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G179" s="8"/>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="8" t="s">
         <v>82</v>
       </c>
@@ -7330,11 +7338,11 @@
       </c>
       <c r="E180" s="11"/>
       <c r="F180" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G180" s="8"/>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
         <v>82</v>
       </c>
@@ -7349,11 +7357,11 @@
       </c>
       <c r="E181" s="11"/>
       <c r="F181" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G181" s="8"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="8" t="s">
         <v>82</v>
       </c>
@@ -7368,11 +7376,11 @@
       </c>
       <c r="E182" s="11"/>
       <c r="F182" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G182" s="8"/>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
         <v>82</v>
       </c>
@@ -7387,11 +7395,11 @@
       </c>
       <c r="E183" s="11"/>
       <c r="F183" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G183" s="8"/>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="8" t="s">
         <v>82</v>
       </c>
@@ -7406,11 +7414,11 @@
       </c>
       <c r="E184" s="11"/>
       <c r="F184" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G184" s="8"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
         <v>82</v>
       </c>
@@ -7425,11 +7433,11 @@
       </c>
       <c r="E185" s="11"/>
       <c r="F185" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G185" s="8"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="8" t="s">
         <v>82</v>
       </c>
@@ -7444,11 +7452,11 @@
       </c>
       <c r="E186" s="11"/>
       <c r="F186" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G186" s="8"/>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
         <v>82</v>
       </c>
@@ -7463,11 +7471,11 @@
       </c>
       <c r="E187" s="11"/>
       <c r="F187" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G187" s="8"/>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="8" t="s">
         <v>82</v>
       </c>
@@ -7482,11 +7490,11 @@
       </c>
       <c r="E188" s="11"/>
       <c r="F188" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G188" s="8"/>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
         <v>82</v>
       </c>
@@ -7501,11 +7509,11 @@
       </c>
       <c r="E189" s="11"/>
       <c r="F189" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G189" s="8"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="8" t="s">
         <v>82</v>
       </c>
@@ -7520,11 +7528,11 @@
       </c>
       <c r="E190" s="11"/>
       <c r="F190" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G190" s="8"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
         <v>82</v>
       </c>
@@ -7539,11 +7547,11 @@
       </c>
       <c r="E191" s="11"/>
       <c r="F191" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G191" s="8"/>
     </row>
-    <row r="192" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
         <v>82</v>
       </c>
@@ -7562,7 +7570,7 @@
       <c r="F192" s="8"/>
       <c r="G192" s="8"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
         <v>82</v>
       </c>
@@ -7579,7 +7587,7 @@
       <c r="F193" s="8"/>
       <c r="G193" s="8"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="8" t="s">
         <v>82</v>
       </c>
@@ -7596,7 +7604,7 @@
       <c r="F194" s="8"/>
       <c r="G194" s="8"/>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
         <v>82</v>
       </c>
@@ -7613,7 +7621,7 @@
       <c r="F195" s="8"/>
       <c r="G195" s="8"/>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="8" t="s">
         <v>82</v>
       </c>
@@ -7630,7 +7638,7 @@
       <c r="F196" s="8"/>
       <c r="G196" s="8"/>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
         <v>82</v>
       </c>
@@ -7647,7 +7655,7 @@
       <c r="F197" s="8"/>
       <c r="G197" s="8"/>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="8" t="s">
         <v>82</v>
       </c>
@@ -7664,7 +7672,7 @@
       <c r="F198" s="8"/>
       <c r="G198" s="8"/>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
         <v>82</v>
       </c>
@@ -7681,7 +7689,7 @@
       <c r="F199" s="8"/>
       <c r="G199" s="8"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="8" t="s">
         <v>82</v>
       </c>
@@ -7698,7 +7706,7 @@
       <c r="F200" s="8"/>
       <c r="G200" s="8"/>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
         <v>82</v>
       </c>
@@ -7715,7 +7723,7 @@
       <c r="F201" s="8"/>
       <c r="G201" s="8"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="8" t="s">
         <v>82</v>
       </c>
@@ -7732,7 +7740,7 @@
       <c r="F202" s="8"/>
       <c r="G202" s="8"/>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
         <v>82</v>
       </c>
@@ -7749,7 +7757,7 @@
       <c r="F203" s="8"/>
       <c r="G203" s="8"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="8" t="s">
         <v>82</v>
       </c>
@@ -7766,7 +7774,7 @@
       <c r="F204" s="8"/>
       <c r="G204" s="8"/>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
         <v>82</v>
       </c>
@@ -7783,7 +7791,7 @@
       <c r="F205" s="8"/>
       <c r="G205" s="8"/>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="8" t="s">
         <v>82</v>
       </c>
@@ -7800,7 +7808,7 @@
       <c r="F206" s="8"/>
       <c r="G206" s="8"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
         <v>82</v>
       </c>
@@ -7817,7 +7825,7 @@
       <c r="F207" s="8"/>
       <c r="G207" s="8"/>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="8" t="s">
         <v>82</v>
       </c>
@@ -7834,7 +7842,7 @@
       <c r="F208" s="8"/>
       <c r="G208" s="8"/>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
         <v>82</v>
       </c>
@@ -7851,7 +7859,7 @@
       <c r="F209" s="8"/>
       <c r="G209" s="8"/>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="8" t="s">
         <v>42</v>
       </c>
@@ -7866,7 +7874,7 @@
       <c r="F210" s="8"/>
       <c r="G210" s="8"/>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
         <v>42</v>
       </c>
@@ -7881,7 +7889,7 @@
       <c r="F211" s="8"/>
       <c r="G211" s="8"/>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="8" t="s">
         <v>42</v>
       </c>
@@ -7896,7 +7904,7 @@
       <c r="F212" s="8"/>
       <c r="G212" s="8"/>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
         <v>42</v>
       </c>
@@ -7911,7 +7919,7 @@
       <c r="F213" s="8"/>
       <c r="G213" s="8"/>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="8" t="s">
         <v>42</v>
       </c>
@@ -7926,7 +7934,7 @@
       <c r="F214" s="8"/>
       <c r="G214" s="8"/>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
         <v>42</v>
       </c>
@@ -7941,7 +7949,7 @@
       <c r="F215" s="8"/>
       <c r="G215" s="8"/>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="8" t="s">
         <v>42</v>
       </c>
@@ -7956,7 +7964,7 @@
       <c r="F216" s="8"/>
       <c r="G216" s="8"/>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
         <v>42</v>
       </c>
@@ -7971,7 +7979,7 @@
       <c r="F217" s="8"/>
       <c r="G217" s="8"/>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="8" t="s">
         <v>42</v>
       </c>
@@ -7986,7 +7994,7 @@
       <c r="F218" s="8"/>
       <c r="G218" s="8"/>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
         <v>42</v>
       </c>
@@ -8001,7 +8009,7 @@
       <c r="F219" s="8"/>
       <c r="G219" s="8"/>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="8" t="s">
         <v>42</v>
       </c>
@@ -8016,7 +8024,7 @@
       <c r="F220" s="8"/>
       <c r="G220" s="8"/>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
         <v>42</v>
       </c>
@@ -8031,7 +8039,7 @@
       <c r="F221" s="8"/>
       <c r="G221" s="8"/>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="8" t="s">
         <v>42</v>
       </c>
@@ -8046,7 +8054,7 @@
       <c r="F222" s="8"/>
       <c r="G222" s="8"/>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
         <v>42</v>
       </c>
@@ -8061,7 +8069,7 @@
       <c r="F223" s="8"/>
       <c r="G223" s="8"/>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="8" t="s">
         <v>42</v>
       </c>
@@ -8076,7 +8084,7 @@
       <c r="F224" s="8"/>
       <c r="G224" s="8"/>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
         <v>42</v>
       </c>
@@ -8091,7 +8099,7 @@
       <c r="F225" s="8"/>
       <c r="G225" s="8"/>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="8" t="s">
         <v>42</v>
       </c>
@@ -8106,7 +8114,7 @@
       <c r="F226" s="8"/>
       <c r="G226" s="8"/>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
         <v>42</v>
       </c>
@@ -8121,7 +8129,7 @@
       <c r="F227" s="8"/>
       <c r="G227" s="8"/>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="8" t="s">
         <v>42</v>
       </c>
@@ -8136,7 +8144,7 @@
       <c r="F228" s="8"/>
       <c r="G228" s="8"/>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
         <v>42</v>
       </c>
@@ -8151,7 +8159,7 @@
       <c r="F229" s="8"/>
       <c r="G229" s="8"/>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="8" t="s">
         <v>39</v>
       </c>
@@ -8166,7 +8174,7 @@
       <c r="F230" s="8"/>
       <c r="G230" s="8"/>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
         <v>39</v>
       </c>
@@ -8181,7 +8189,7 @@
       <c r="F231" s="8"/>
       <c r="G231" s="8"/>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="8" t="s">
         <v>39</v>
       </c>
@@ -8196,7 +8204,7 @@
       <c r="F232" s="8"/>
       <c r="G232" s="8"/>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
         <v>39</v>
       </c>
@@ -8211,7 +8219,7 @@
       <c r="F233" s="8"/>
       <c r="G233" s="8"/>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="8" t="s">
         <v>39</v>
       </c>
@@ -8226,7 +8234,7 @@
       <c r="F234" s="8"/>
       <c r="G234" s="8"/>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
         <v>39</v>
       </c>
@@ -8241,7 +8249,7 @@
       <c r="F235" s="8"/>
       <c r="G235" s="8"/>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="8" t="s">
         <v>39</v>
       </c>
@@ -8256,7 +8264,7 @@
       <c r="F236" s="8"/>
       <c r="G236" s="8"/>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
         <v>39</v>
       </c>
@@ -8271,7 +8279,7 @@
       <c r="F237" s="8"/>
       <c r="G237" s="8"/>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="8" t="s">
         <v>39</v>
       </c>
@@ -8286,7 +8294,7 @@
       <c r="F238" s="8"/>
       <c r="G238" s="8"/>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
         <v>39</v>
       </c>
@@ -8979,10 +8987,10 @@
         <v>795</v>
       </c>
       <c r="D279" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E279" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F279" s="8"/>
       <c r="G279" s="8"/>
@@ -8998,7 +9006,7 @@
         <v>205</v>
       </c>
       <c r="D280" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E280" s="11"/>
       <c r="F280" s="8"/>
@@ -9015,7 +9023,7 @@
         <v>117</v>
       </c>
       <c r="D281" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E281" s="11"/>
       <c r="F281" s="8"/>
@@ -9032,7 +9040,7 @@
         <v>90</v>
       </c>
       <c r="D282" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E282" s="11"/>
       <c r="F282" s="8"/>
@@ -9049,7 +9057,7 @@
         <v>7</v>
       </c>
       <c r="D283" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E283" s="11"/>
       <c r="F283" s="8"/>
@@ -9066,7 +9074,7 @@
         <v>5</v>
       </c>
       <c r="D284" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E284" s="11"/>
       <c r="F284" s="8"/>
@@ -9083,7 +9091,7 @@
         <v>3</v>
       </c>
       <c r="D285" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E285" s="11"/>
       <c r="F285" s="8"/>
@@ -9100,7 +9108,7 @@
         <v>1</v>
       </c>
       <c r="D286" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E286" s="11"/>
       <c r="F286" s="8"/>
@@ -9117,7 +9125,7 @@
         <v>1</v>
       </c>
       <c r="D287" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E287" s="11"/>
       <c r="F287" s="8"/>
@@ -9134,7 +9142,7 @@
         <v>1</v>
       </c>
       <c r="D288" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E288" s="11"/>
       <c r="F288" s="8"/>
@@ -9151,7 +9159,7 @@
         <v>1</v>
       </c>
       <c r="D289" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E289" s="11"/>
       <c r="F289" s="8"/>
@@ -9168,10 +9176,10 @@
         <v>520</v>
       </c>
       <c r="D290" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E290" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F290" s="8"/>
       <c r="G290" s="8"/>
@@ -9187,7 +9195,7 @@
         <v>455</v>
       </c>
       <c r="D291" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E291" s="11"/>
       <c r="F291" s="8"/>
@@ -9204,7 +9212,7 @@
         <v>404</v>
       </c>
       <c r="D292" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E292" s="11"/>
       <c r="F292" s="8"/>
@@ -9221,7 +9229,7 @@
         <v>94</v>
       </c>
       <c r="D293" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E293" s="11"/>
       <c r="F293" s="8"/>
@@ -9238,7 +9246,7 @@
         <v>32</v>
       </c>
       <c r="D294" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E294" s="11"/>
       <c r="F294" s="8"/>
@@ -9255,7 +9263,7 @@
         <v>9</v>
       </c>
       <c r="D295" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E295" s="11"/>
       <c r="F295" s="8"/>
@@ -9272,7 +9280,7 @@
         <v>3</v>
       </c>
       <c r="D296" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E296" s="11"/>
       <c r="F296" s="8"/>
@@ -9289,7 +9297,7 @@
         <v>1</v>
       </c>
       <c r="D297" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E297" s="11"/>
       <c r="F297" s="8"/>
@@ -9306,7 +9314,7 @@
         <v>1</v>
       </c>
       <c r="D298" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E298" s="11"/>
       <c r="F298" s="8"/>
@@ -9323,7 +9331,7 @@
         <v>1</v>
       </c>
       <c r="D299" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E299" s="11"/>
       <c r="F299" s="8"/>
@@ -9340,7 +9348,7 @@
         <v>1</v>
       </c>
       <c r="D300" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E300" s="11"/>
       <c r="F300" s="8"/>
@@ -9348,11 +9356,16 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G300" xr:uid="{38A162FC-7907-44C7-A909-E8E1323EC5F6}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="whiteleg_shrimp"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G300">
       <sortCondition ref="A1:A300"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="G2 F5:G5 F2:F300">
+  <conditionalFormatting sqref="G2 F2:F300 F5:G5">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"Y"</formula>
     </cfRule>

--- a/data/raw_data/feed_profiles_and_composition.xlsx
+++ b/data/raw_data/feed_profiles_and_composition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\treimer\Documents\R-temp-files\climate_risks_to_fed_mariculture\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE24ADC3-867E-4C70-99C6-804B1D444301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21EC04E6-4D6D-47D8-9A7E-C69B42F88450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24" yWindow="1236" windowWidth="20136" windowHeight="13908" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5268" yWindow="0" windowWidth="25236" windowHeight="16656" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="feed_formulations" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="228">
   <si>
     <t>ingredient</t>
   </si>
@@ -4558,7 +4558,7 @@
         <v>176</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G9" s="8"/>
     </row>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>177</v>
@@ -4599,7 +4599,9 @@
       <c r="E11" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="F11" s="8"/>
+      <c r="F11" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G11" s="8"/>
     </row>
     <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -4616,7 +4618,9 @@
         <v>142</v>
       </c>
       <c r="E12" s="11"/>
-      <c r="F12" s="8"/>
+      <c r="F12" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G12" s="8"/>
     </row>
     <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -4633,7 +4637,9 @@
         <v>142</v>
       </c>
       <c r="E13" s="11"/>
-      <c r="F13" s="8"/>
+      <c r="F13" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G13" s="8"/>
     </row>
     <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -4650,7 +4656,9 @@
         <v>142</v>
       </c>
       <c r="E14" s="11"/>
-      <c r="F14" s="8"/>
+      <c r="F14" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G14" s="8"/>
     </row>
     <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -4667,7 +4675,9 @@
         <v>142</v>
       </c>
       <c r="E15" s="11"/>
-      <c r="F15" s="8"/>
+      <c r="F15" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G15" s="8"/>
     </row>
     <row r="16" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
@@ -7283,7 +7293,7 @@
       </c>
       <c r="G177" s="8"/>
     </row>
-    <row r="178" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A178" s="8" t="s">
         <v>82</v>
       </c>
@@ -7304,7 +7314,7 @@
       </c>
       <c r="G178" s="8"/>
     </row>
-    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
         <v>82</v>
       </c>
@@ -7323,7 +7333,7 @@
       </c>
       <c r="G179" s="8"/>
     </row>
-    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="8" t="s">
         <v>82</v>
       </c>
@@ -7342,7 +7352,7 @@
       </c>
       <c r="G180" s="8"/>
     </row>
-    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
         <v>82</v>
       </c>
@@ -7361,7 +7371,7 @@
       </c>
       <c r="G181" s="8"/>
     </row>
-    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="8" t="s">
         <v>82</v>
       </c>
@@ -7380,7 +7390,7 @@
       </c>
       <c r="G182" s="8"/>
     </row>
-    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
         <v>82</v>
       </c>
@@ -7399,7 +7409,7 @@
       </c>
       <c r="G183" s="8"/>
     </row>
-    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="8" t="s">
         <v>82</v>
       </c>
@@ -7418,7 +7428,7 @@
       </c>
       <c r="G184" s="8"/>
     </row>
-    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
         <v>82</v>
       </c>
@@ -7437,7 +7447,7 @@
       </c>
       <c r="G185" s="8"/>
     </row>
-    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="8" t="s">
         <v>82</v>
       </c>
@@ -7456,7 +7466,7 @@
       </c>
       <c r="G186" s="8"/>
     </row>
-    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
         <v>82</v>
       </c>
@@ -7475,7 +7485,7 @@
       </c>
       <c r="G187" s="8"/>
     </row>
-    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="8" t="s">
         <v>82</v>
       </c>
@@ -7494,7 +7504,7 @@
       </c>
       <c r="G188" s="8"/>
     </row>
-    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
         <v>82</v>
       </c>
@@ -7513,7 +7523,7 @@
       </c>
       <c r="G189" s="8"/>
     </row>
-    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="8" t="s">
         <v>82</v>
       </c>
@@ -7532,7 +7542,7 @@
       </c>
       <c r="G190" s="8"/>
     </row>
-    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
         <v>82</v>
       </c>
@@ -7551,7 +7561,7 @@
       </c>
       <c r="G191" s="8"/>
     </row>
-    <row r="192" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
         <v>82</v>
       </c>
@@ -7570,7 +7580,7 @@
       <c r="F192" s="8"/>
       <c r="G192" s="8"/>
     </row>
-    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
         <v>82</v>
       </c>
@@ -7587,7 +7597,7 @@
       <c r="F193" s="8"/>
       <c r="G193" s="8"/>
     </row>
-    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="8" t="s">
         <v>82</v>
       </c>
@@ -7604,7 +7614,7 @@
       <c r="F194" s="8"/>
       <c r="G194" s="8"/>
     </row>
-    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
         <v>82</v>
       </c>
@@ -7621,7 +7631,7 @@
       <c r="F195" s="8"/>
       <c r="G195" s="8"/>
     </row>
-    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="8" t="s">
         <v>82</v>
       </c>
@@ -7638,7 +7648,7 @@
       <c r="F196" s="8"/>
       <c r="G196" s="8"/>
     </row>
-    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
         <v>82</v>
       </c>
@@ -7655,7 +7665,7 @@
       <c r="F197" s="8"/>
       <c r="G197" s="8"/>
     </row>
-    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="8" t="s">
         <v>82</v>
       </c>
@@ -7672,7 +7682,7 @@
       <c r="F198" s="8"/>
       <c r="G198" s="8"/>
     </row>
-    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
         <v>82</v>
       </c>
@@ -7689,7 +7699,7 @@
       <c r="F199" s="8"/>
       <c r="G199" s="8"/>
     </row>
-    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="8" t="s">
         <v>82</v>
       </c>
@@ -7706,7 +7716,7 @@
       <c r="F200" s="8"/>
       <c r="G200" s="8"/>
     </row>
-    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
         <v>82</v>
       </c>
@@ -7723,7 +7733,7 @@
       <c r="F201" s="8"/>
       <c r="G201" s="8"/>
     </row>
-    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="8" t="s">
         <v>82</v>
       </c>
@@ -7740,7 +7750,7 @@
       <c r="F202" s="8"/>
       <c r="G202" s="8"/>
     </row>
-    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
         <v>82</v>
       </c>
@@ -7757,7 +7767,7 @@
       <c r="F203" s="8"/>
       <c r="G203" s="8"/>
     </row>
-    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="8" t="s">
         <v>82</v>
       </c>
@@ -7774,7 +7784,7 @@
       <c r="F204" s="8"/>
       <c r="G204" s="8"/>
     </row>
-    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
         <v>82</v>
       </c>
@@ -7791,7 +7801,7 @@
       <c r="F205" s="8"/>
       <c r="G205" s="8"/>
     </row>
-    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="8" t="s">
         <v>82</v>
       </c>
@@ -7808,7 +7818,7 @@
       <c r="F206" s="8"/>
       <c r="G206" s="8"/>
     </row>
-    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
         <v>82</v>
       </c>
@@ -7825,7 +7835,7 @@
       <c r="F207" s="8"/>
       <c r="G207" s="8"/>
     </row>
-    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="8" t="s">
         <v>82</v>
       </c>
@@ -7842,7 +7852,7 @@
       <c r="F208" s="8"/>
       <c r="G208" s="8"/>
     </row>
-    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
         <v>82</v>
       </c>
@@ -8309,7 +8319,7 @@
       <c r="F239" s="8"/>
       <c r="G239" s="8"/>
     </row>
-    <row r="240" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="8" t="s">
         <v>41</v>
       </c>
@@ -8328,7 +8338,7 @@
       <c r="F240" s="8"/>
       <c r="G240" s="8"/>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="8" t="s">
         <v>41</v>
       </c>
@@ -8345,7 +8355,7 @@
       <c r="F241" s="8"/>
       <c r="G241" s="8"/>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="8" t="s">
         <v>41</v>
       </c>
@@ -8362,7 +8372,7 @@
       <c r="F242" s="8"/>
       <c r="G242" s="8"/>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="8" t="s">
         <v>41</v>
       </c>
@@ -8379,7 +8389,7 @@
       <c r="F243" s="8"/>
       <c r="G243" s="8"/>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="8" t="s">
         <v>41</v>
       </c>
@@ -8396,7 +8406,7 @@
       <c r="F244" s="8"/>
       <c r="G244" s="8"/>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="8" t="s">
         <v>41</v>
       </c>
@@ -8413,7 +8423,7 @@
       <c r="F245" s="8"/>
       <c r="G245" s="8"/>
     </row>
-    <row r="246" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="8" t="s">
         <v>41</v>
       </c>
@@ -8432,7 +8442,7 @@
       <c r="F246" s="8"/>
       <c r="G246" s="8"/>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="8" t="s">
         <v>41</v>
       </c>
@@ -8449,7 +8459,7 @@
       <c r="F247" s="8"/>
       <c r="G247" s="8"/>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="8" t="s">
         <v>41</v>
       </c>
@@ -8466,7 +8476,7 @@
       <c r="F248" s="8"/>
       <c r="G248" s="8"/>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="8" t="s">
         <v>41</v>
       </c>
@@ -8483,7 +8493,7 @@
       <c r="F249" s="8"/>
       <c r="G249" s="8"/>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="8" t="s">
         <v>41</v>
       </c>
@@ -8500,7 +8510,7 @@
       <c r="F250" s="8"/>
       <c r="G250" s="8"/>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="8" t="s">
         <v>41</v>
       </c>
@@ -8517,7 +8527,7 @@
       <c r="F251" s="8"/>
       <c r="G251" s="8"/>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="8" t="s">
         <v>41</v>
       </c>
@@ -8534,7 +8544,7 @@
       <c r="F252" s="8"/>
       <c r="G252" s="8"/>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="8" t="s">
         <v>41</v>
       </c>
@@ -8551,7 +8561,7 @@
       <c r="F253" s="8"/>
       <c r="G253" s="8"/>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="8" t="s">
         <v>41</v>
       </c>
@@ -8568,7 +8578,7 @@
       <c r="F254" s="8"/>
       <c r="G254" s="8"/>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="8" t="s">
         <v>41</v>
       </c>
@@ -8585,7 +8595,7 @@
       <c r="F255" s="8"/>
       <c r="G255" s="8"/>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="8" t="s">
         <v>41</v>
       </c>
@@ -8602,7 +8612,7 @@
       <c r="F256" s="8"/>
       <c r="G256" s="8"/>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="8" t="s">
         <v>41</v>
       </c>
@@ -8619,7 +8629,7 @@
       <c r="F257" s="8"/>
       <c r="G257" s="8"/>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="8" t="s">
         <v>41</v>
       </c>
@@ -8636,7 +8646,7 @@
       <c r="F258" s="8"/>
       <c r="G258" s="8"/>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="8" t="s">
         <v>41</v>
       </c>
@@ -8653,7 +8663,7 @@
       <c r="F259" s="8"/>
       <c r="G259" s="8"/>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="8" t="s">
         <v>41</v>
       </c>
@@ -8670,7 +8680,7 @@
       <c r="F260" s="8"/>
       <c r="G260" s="8"/>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="8" t="s">
         <v>41</v>
       </c>
@@ -8687,7 +8697,7 @@
       <c r="F261" s="8"/>
       <c r="G261" s="8"/>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="8" t="s">
         <v>41</v>
       </c>
@@ -8704,7 +8714,7 @@
       <c r="F262" s="8"/>
       <c r="G262" s="8"/>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="8" t="s">
         <v>41</v>
       </c>
@@ -8721,7 +8731,7 @@
       <c r="F263" s="8"/>
       <c r="G263" s="8"/>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="8" t="s">
         <v>41</v>
       </c>
@@ -8738,7 +8748,7 @@
       <c r="F264" s="8"/>
       <c r="G264" s="8"/>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="8" t="s">
         <v>41</v>
       </c>
@@ -8755,7 +8765,7 @@
       <c r="F265" s="8"/>
       <c r="G265" s="8"/>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="8" t="s">
         <v>41</v>
       </c>
@@ -8772,7 +8782,7 @@
       <c r="F266" s="8"/>
       <c r="G266" s="8"/>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="8" t="s">
         <v>41</v>
       </c>
@@ -8789,7 +8799,7 @@
       <c r="F267" s="8"/>
       <c r="G267" s="8"/>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="8" t="s">
         <v>41</v>
       </c>
@@ -8806,7 +8816,7 @@
       <c r="F268" s="8"/>
       <c r="G268" s="8"/>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="8" t="s">
         <v>41</v>
       </c>
@@ -8823,7 +8833,7 @@
       <c r="F269" s="8"/>
       <c r="G269" s="8"/>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="8" t="s">
         <v>41</v>
       </c>
@@ -8840,7 +8850,7 @@
       <c r="F270" s="8"/>
       <c r="G270" s="8"/>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="8" t="s">
         <v>41</v>
       </c>
@@ -8857,7 +8867,7 @@
       <c r="F271" s="8"/>
       <c r="G271" s="8"/>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="8" t="s">
         <v>41</v>
       </c>
@@ -8874,7 +8884,7 @@
       <c r="F272" s="8"/>
       <c r="G272" s="8"/>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="8" t="s">
         <v>41</v>
       </c>
@@ -8891,7 +8901,7 @@
       <c r="F273" s="8"/>
       <c r="G273" s="8"/>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="8" t="s">
         <v>41</v>
       </c>
@@ -8908,7 +8918,7 @@
       <c r="F274" s="8"/>
       <c r="G274" s="8"/>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="8" t="s">
         <v>41</v>
       </c>
@@ -8925,7 +8935,7 @@
       <c r="F275" s="8"/>
       <c r="G275" s="8"/>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="8" t="s">
         <v>41</v>
       </c>
@@ -8942,7 +8952,7 @@
       <c r="F276" s="8"/>
       <c r="G276" s="8"/>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="8" t="s">
         <v>41</v>
       </c>
@@ -8959,7 +8969,7 @@
       <c r="F277" s="8"/>
       <c r="G277" s="8"/>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="8" t="s">
         <v>41</v>
       </c>
@@ -8976,7 +8986,7 @@
       <c r="F278" s="8"/>
       <c r="G278" s="8"/>
     </row>
-    <row r="279" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="8" t="s">
         <v>41</v>
       </c>
@@ -8995,7 +9005,7 @@
       <c r="F279" s="8"/>
       <c r="G279" s="8"/>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="8" t="s">
         <v>41</v>
       </c>
@@ -9012,7 +9022,7 @@
       <c r="F280" s="8"/>
       <c r="G280" s="8"/>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="8" t="s">
         <v>41</v>
       </c>
@@ -9029,7 +9039,7 @@
       <c r="F281" s="8"/>
       <c r="G281" s="8"/>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="8" t="s">
         <v>41</v>
       </c>
@@ -9046,7 +9056,7 @@
       <c r="F282" s="8"/>
       <c r="G282" s="8"/>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="8" t="s">
         <v>41</v>
       </c>
@@ -9063,7 +9073,7 @@
       <c r="F283" s="8"/>
       <c r="G283" s="8"/>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="8" t="s">
         <v>41</v>
       </c>
@@ -9080,7 +9090,7 @@
       <c r="F284" s="8"/>
       <c r="G284" s="8"/>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="8" t="s">
         <v>41</v>
       </c>
@@ -9097,7 +9107,7 @@
       <c r="F285" s="8"/>
       <c r="G285" s="8"/>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="8" t="s">
         <v>41</v>
       </c>
@@ -9114,7 +9124,7 @@
       <c r="F286" s="8"/>
       <c r="G286" s="8"/>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="8" t="s">
         <v>41</v>
       </c>
@@ -9131,7 +9141,7 @@
       <c r="F287" s="8"/>
       <c r="G287" s="8"/>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="8" t="s">
         <v>41</v>
       </c>
@@ -9148,7 +9158,7 @@
       <c r="F288" s="8"/>
       <c r="G288" s="8"/>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="8" t="s">
         <v>41</v>
       </c>
@@ -9165,7 +9175,7 @@
       <c r="F289" s="8"/>
       <c r="G289" s="8"/>
     </row>
-    <row r="290" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="8" t="s">
         <v>41</v>
       </c>
@@ -9184,7 +9194,7 @@
       <c r="F290" s="8"/>
       <c r="G290" s="8"/>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="8" t="s">
         <v>41</v>
       </c>
@@ -9201,7 +9211,7 @@
       <c r="F291" s="8"/>
       <c r="G291" s="8"/>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="8" t="s">
         <v>41</v>
       </c>
@@ -9218,7 +9228,7 @@
       <c r="F292" s="8"/>
       <c r="G292" s="8"/>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="8" t="s">
         <v>41</v>
       </c>
@@ -9235,7 +9245,7 @@
       <c r="F293" s="8"/>
       <c r="G293" s="8"/>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="8" t="s">
         <v>41</v>
       </c>
@@ -9252,7 +9262,7 @@
       <c r="F294" s="8"/>
       <c r="G294" s="8"/>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="8" t="s">
         <v>41</v>
       </c>
@@ -9269,7 +9279,7 @@
       <c r="F295" s="8"/>
       <c r="G295" s="8"/>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="8" t="s">
         <v>41</v>
       </c>
@@ -9286,7 +9296,7 @@
       <c r="F296" s="8"/>
       <c r="G296" s="8"/>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="8" t="s">
         <v>41</v>
       </c>
@@ -9303,7 +9313,7 @@
       <c r="F297" s="8"/>
       <c r="G297" s="8"/>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="8" t="s">
         <v>41</v>
       </c>
@@ -9320,7 +9330,7 @@
       <c r="F298" s="8"/>
       <c r="G298" s="8"/>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="8" t="s">
         <v>41</v>
       </c>
@@ -9337,7 +9347,7 @@
       <c r="F299" s="8"/>
       <c r="G299" s="8"/>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="8" t="s">
         <v>41</v>
       </c>
@@ -9358,14 +9368,14 @@
   <autoFilter ref="A1:G300" xr:uid="{38A162FC-7907-44C7-A909-E8E1323EC5F6}">
     <filterColumn colId="0">
       <filters>
-        <filter val="whiteleg_shrimp"/>
+        <filter val="seabream"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G300">
-      <sortCondition ref="A1:A300"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:G20">
+      <sortCondition ref="D1:D300"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="G2 F2:F300 F5:G5">
+  <conditionalFormatting sqref="G2 F5:G5 F2:F300">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"Y"</formula>
     </cfRule>

--- a/data/raw_data/feed_profiles_and_composition.xlsx
+++ b/data/raw_data/feed_profiles_and_composition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\treimer\Documents\R-temp-files\climate_risks_to_fed_mariculture\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21EC04E6-4D6D-47D8-9A7E-C69B42F88450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04F7CDA-7E3F-4F49-8F48-F42CF2E3EB7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5268" yWindow="0" windowWidth="25236" windowHeight="16656" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25260" yWindow="1836" windowWidth="15528" windowHeight="13656" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="feed_formulations" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="228">
   <si>
     <t>ingredient</t>
   </si>
@@ -1143,7 +1143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:N1097"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>49</v>
       </c>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>49</v>
       </c>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>49</v>
       </c>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>49</v>
       </c>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>49</v>
       </c>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>49</v>
       </c>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>49</v>
       </c>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>49</v>
       </c>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>49</v>
       </c>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>49</v>
       </c>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>49</v>
       </c>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>49</v>
       </c>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>49</v>
       </c>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>44</v>
       </c>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>44</v>
       </c>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>44</v>
       </c>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>44</v>
       </c>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="D25" s="2"/>
     </row>
-    <row r="26" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>44</v>
       </c>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>44</v>
       </c>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="D27" s="2"/>
     </row>
-    <row r="28" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>44</v>
       </c>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D29" s="2"/>
     </row>
-    <row r="30" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>44</v>
       </c>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>44</v>
       </c>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="D31" s="2"/>
     </row>
-    <row r="32" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>44</v>
       </c>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>44</v>
       </c>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D33" s="2"/>
     </row>
-    <row r="34" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>44</v>
       </c>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>44</v>
       </c>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D35" s="2"/>
     </row>
-    <row r="36" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>43</v>
       </c>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>43</v>
       </c>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="D37" s="2"/>
     </row>
-    <row r="38" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>43</v>
       </c>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>43</v>
       </c>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="D39" s="2"/>
     </row>
-    <row r="40" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>43</v>
       </c>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D40" s="2"/>
     </row>
-    <row r="41" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>43</v>
       </c>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="D41" s="2"/>
     </row>
-    <row r="42" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>43</v>
       </c>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="D42" s="2"/>
     </row>
-    <row r="43" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>43</v>
       </c>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="D43" s="2"/>
     </row>
-    <row r="44" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>43</v>
       </c>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>43</v>
       </c>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>43</v>
       </c>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>43</v>
       </c>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="D47" s="2"/>
     </row>
-    <row r="48" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>43</v>
       </c>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>43</v>
       </c>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="D49" s="2"/>
     </row>
-    <row r="50" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>43</v>
       </c>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>43</v>
       </c>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="D51" s="2"/>
     </row>
-    <row r="52" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>43</v>
       </c>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>48</v>
       </c>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="D53" s="2"/>
     </row>
-    <row r="54" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>48</v>
       </c>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>48</v>
       </c>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="D55" s="2"/>
     </row>
-    <row r="56" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>48</v>
       </c>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="D56" s="2"/>
     </row>
-    <row r="57" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>48</v>
       </c>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D57" s="2"/>
     </row>
-    <row r="58" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>48</v>
       </c>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="D58" s="2"/>
     </row>
-    <row r="59" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>48</v>
       </c>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="D59" s="2"/>
     </row>
-    <row r="60" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>48</v>
       </c>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="D60" s="2"/>
     </row>
-    <row r="61" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>48</v>
       </c>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="D61" s="2"/>
     </row>
-    <row r="62" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>48</v>
       </c>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D62" s="2"/>
     </row>
-    <row r="63" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>48</v>
       </c>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="D63" s="2"/>
     </row>
-    <row r="64" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>48</v>
       </c>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="D64" s="2"/>
     </row>
-    <row r="65" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>198</v>
       </c>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="D65" s="2"/>
     </row>
-    <row r="66" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>198</v>
       </c>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="D66" s="2"/>
     </row>
-    <row r="67" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>198</v>
       </c>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="D67" s="3"/>
     </row>
-    <row r="68" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>198</v>
       </c>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D68" s="2"/>
     </row>
-    <row r="69" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>198</v>
       </c>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D69" s="2"/>
     </row>
-    <row r="70" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>198</v>
       </c>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="D70" s="2"/>
     </row>
-    <row r="71" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>198</v>
       </c>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="D71" s="2"/>
     </row>
-    <row r="72" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>198</v>
       </c>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="D72" s="2"/>
     </row>
-    <row r="73" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>198</v>
       </c>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="D73" s="2"/>
     </row>
-    <row r="74" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>198</v>
       </c>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="D74" s="2"/>
     </row>
-    <row r="75" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>198</v>
       </c>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="D75" s="2"/>
     </row>
-    <row r="76" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>198</v>
       </c>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="D76" s="2"/>
     </row>
-    <row r="77" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>210</v>
       </c>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="D77" s="3"/>
     </row>
-    <row r="78" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>210</v>
       </c>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D78" s="3"/>
     </row>
-    <row r="79" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>210</v>
       </c>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D79" s="3"/>
     </row>
-    <row r="80" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>210</v>
       </c>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="D80" s="3"/>
     </row>
-    <row r="81" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>210</v>
       </c>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="D81" s="3"/>
     </row>
-    <row r="82" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>210</v>
       </c>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="D82" s="3"/>
     </row>
-    <row r="83" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>210</v>
       </c>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="D83" s="3"/>
     </row>
-    <row r="84" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>210</v>
       </c>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="D84" s="3"/>
     </row>
-    <row r="85" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>210</v>
       </c>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="D85" s="3"/>
     </row>
-    <row r="86" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>210</v>
       </c>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D86" s="3"/>
     </row>
-    <row r="87" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>210</v>
       </c>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="D87" s="3"/>
     </row>
-    <row r="88" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>30</v>
       </c>
@@ -2228,7 +2228,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>33</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>33</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>33</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>33</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>33</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>33</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>29</v>
       </c>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="D95" s="2"/>
     </row>
-    <row r="96" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>203</v>
       </c>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="D96" s="3"/>
     </row>
-    <row r="97" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>203</v>
       </c>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="D97" s="3"/>
     </row>
-    <row r="98" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>203</v>
       </c>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="D98" s="3"/>
     </row>
-    <row r="99" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>203</v>
       </c>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="D99" s="3"/>
     </row>
-    <row r="100" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>203</v>
       </c>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="D100" s="3"/>
     </row>
-    <row r="101" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>203</v>
       </c>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="D101" s="3"/>
     </row>
-    <row r="102" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>203</v>
       </c>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="D102" s="3"/>
     </row>
-    <row r="103" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>203</v>
       </c>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D103" s="3"/>
     </row>
-    <row r="104" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>203</v>
       </c>
@@ -2438,22 +2438,22 @@
       </c>
       <c r="D104" s="3"/>
     </row>
-    <row r="105" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>181</v>
       </c>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="D108" s="3"/>
     </row>
-    <row r="109" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>181</v>
       </c>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="D109" s="3"/>
     </row>
-    <row r="110" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>181</v>
       </c>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="D110" s="3"/>
     </row>
-    <row r="111" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>181</v>
       </c>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="D111" s="3"/>
     </row>
-    <row r="112" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>181</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>181</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>181</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>181</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>181</v>
       </c>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="D116" s="3"/>
     </row>
-    <row r="117" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>181</v>
       </c>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="D117" s="3"/>
     </row>
-    <row r="118" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>181</v>
       </c>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="D118" s="3"/>
     </row>
-    <row r="119" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>181</v>
       </c>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="D119" s="3"/>
     </row>
-    <row r="120" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>181</v>
       </c>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="D120" s="3"/>
     </row>
-    <row r="121" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>181</v>
       </c>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="D121" s="3"/>
     </row>
-    <row r="122" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>179</v>
       </c>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="D122" s="3"/>
     </row>
-    <row r="123" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>179</v>
       </c>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="D123" s="3"/>
     </row>
-    <row r="124" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>179</v>
       </c>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="D124" s="3"/>
     </row>
-    <row r="125" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>179</v>
       </c>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D125" s="3"/>
     </row>
-    <row r="126" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>179</v>
       </c>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="D126" s="3"/>
     </row>
-    <row r="127" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>179</v>
       </c>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="D127" s="3"/>
     </row>
-    <row r="128" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>179</v>
       </c>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="D128" s="3"/>
     </row>
-    <row r="129" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>179</v>
       </c>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="D129" s="3"/>
     </row>
-    <row r="130" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>179</v>
       </c>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="D130" s="3"/>
     </row>
-    <row r="131" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>179</v>
       </c>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="D131" s="3"/>
     </row>
-    <row r="132" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>179</v>
       </c>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="D132" s="3"/>
     </row>
-    <row r="133" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>179</v>
       </c>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="D133" s="3"/>
     </row>
-    <row r="134" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>179</v>
       </c>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="D134" s="3"/>
     </row>
-    <row r="135" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>179</v>
       </c>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="D135" s="3"/>
     </row>
-    <row r="136" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>179</v>
       </c>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="D136" s="3"/>
     </row>
-    <row r="137" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>179</v>
       </c>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="D137" s="3"/>
     </row>
-    <row r="138" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>182</v>
       </c>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="D138" s="3"/>
     </row>
-    <row r="139" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>182</v>
       </c>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="D139" s="3"/>
     </row>
-    <row r="140" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>182</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>182</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>182</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>182</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>182</v>
       </c>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="D144" s="3"/>
     </row>
-    <row r="145" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>182</v>
       </c>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="D145" s="3"/>
     </row>
-    <row r="146" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>182</v>
       </c>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="D146" s="3"/>
     </row>
-    <row r="147" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>182</v>
       </c>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="D147" s="3"/>
     </row>
-    <row r="148" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>182</v>
       </c>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D148" s="3"/>
     </row>
-    <row r="149" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>182</v>
       </c>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D149" s="3"/>
     </row>
-    <row r="150" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>195</v>
       </c>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="D150" s="2"/>
     </row>
-    <row r="151" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>195</v>
       </c>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="D151" s="2"/>
     </row>
-    <row r="152" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>195</v>
       </c>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="D152" s="2"/>
     </row>
-    <row r="153" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>195</v>
       </c>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D153" s="2"/>
     </row>
-    <row r="154" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>195</v>
       </c>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D154" s="2"/>
     </row>
-    <row r="155" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>195</v>
       </c>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="D155" s="2"/>
     </row>
-    <row r="156" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>195</v>
       </c>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="D156" s="2"/>
     </row>
-    <row r="157" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>191</v>
       </c>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="D157" s="3"/>
     </row>
-    <row r="158" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>191</v>
       </c>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="D158" s="2"/>
     </row>
-    <row r="159" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>191</v>
       </c>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="D159" s="2"/>
     </row>
-    <row r="160" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>191</v>
       </c>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="D160" s="2"/>
     </row>
-    <row r="161" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>191</v>
       </c>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D161" s="2"/>
     </row>
-    <row r="162" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>191</v>
       </c>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D162" s="2"/>
     </row>
-    <row r="163" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>191</v>
       </c>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="D163" s="2"/>
     </row>
-    <row r="164" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>191</v>
       </c>
@@ -3162,17 +3162,17 @@
       </c>
       <c r="D164" s="2"/>
     </row>
-    <row r="165" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>211</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>211</v>
       </c>
@@ -3194,7 +3194,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>211</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>211</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>2.9999999999999805E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>211</v>
       </c>
@@ -3227,7 +3227,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>211</v>
       </c>
@@ -3238,7 +3238,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>211</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>214</v>
       </c>
@@ -3260,7 +3260,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>214</v>
       </c>
@@ -3271,7 +3271,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>214</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>5.5999999999998273E-3</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>214</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>0.17500000000000002</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>214</v>
       </c>
@@ -3304,7 +3304,7 @@
         <v>0.45140000000000002</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>216</v>
       </c>
@@ -3315,7 +3315,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>216</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>216</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>0.1474</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>216</v>
       </c>
@@ -3348,7 +3348,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>216</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>3.1000000000000028E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>216</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>1.15E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>216</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>0.47010000000000002</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>222</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>222</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>222</v>
       </c>
@@ -3414,7 +3414,7 @@
         <v>9.2999999999999972E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>222</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>0.20300000000000001</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>222</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>0.21500000000000002</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>222</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>222</v>
       </c>
@@ -4366,6 +4366,11 @@
     <row r="1097" ht="13.2" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:D192" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="asian_seabass-china"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A167:D192">
       <sortCondition ref="A1:A192"/>
     </sortState>
@@ -4381,12 +4386,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A162FC-7907-44C7-A909-E8E1323EC5F6}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G300"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.5546875" style="7" customWidth="1"/>
     <col min="3" max="3" width="11.109375" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.88671875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="100.77734375" style="10" customWidth="1"/>
@@ -4418,7 +4422,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>199</v>
       </c>
@@ -4437,7 +4441,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>199</v>
       </c>
@@ -4454,7 +4458,7 @@
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>199</v>
       </c>
@@ -4471,7 +4475,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>199</v>
       </c>
@@ -4488,7 +4492,7 @@
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>128</v>
       </c>
@@ -4507,7 +4511,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>128</v>
       </c>
@@ -4524,7 +4528,7 @@
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>128</v>
       </c>
@@ -4541,7 +4545,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>128</v>
       </c>
@@ -4562,7 +4566,7 @@
       </c>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>128</v>
       </c>
@@ -4583,7 +4587,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>128</v>
       </c>
@@ -4604,7 +4608,7 @@
       </c>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>128</v>
       </c>
@@ -4623,7 +4627,7 @@
       </c>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>128</v>
       </c>
@@ -4642,7 +4646,7 @@
       </c>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>128</v>
       </c>
@@ -4661,7 +4665,7 @@
       </c>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>128</v>
       </c>
@@ -4680,7 +4684,7 @@
       </c>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>128</v>
       </c>
@@ -4699,7 +4703,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>128</v>
       </c>
@@ -4716,7 +4720,7 @@
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>128</v>
       </c>
@@ -4733,7 +4737,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>128</v>
       </c>
@@ -4750,7 +4754,7 @@
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>128</v>
       </c>
@@ -4767,7 +4771,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>119</v>
       </c>
@@ -4782,7 +4786,7 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>119</v>
       </c>
@@ -4797,7 +4801,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>119</v>
       </c>
@@ -4812,7 +4816,7 @@
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>119</v>
       </c>
@@ -4827,7 +4831,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>119</v>
       </c>
@@ -4842,7 +4846,7 @@
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>119</v>
       </c>
@@ -4857,7 +4861,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>119</v>
       </c>
@@ -4872,7 +4876,7 @@
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>119</v>
       </c>
@@ -4887,7 +4891,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>119</v>
       </c>
@@ -4902,7 +4906,7 @@
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>119</v>
       </c>
@@ -4917,7 +4921,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>119</v>
       </c>
@@ -4932,7 +4936,7 @@
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>119</v>
       </c>
@@ -4947,7 +4951,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>119</v>
       </c>
@@ -4962,7 +4966,7 @@
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>119</v>
       </c>
@@ -4977,7 +4981,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>119</v>
       </c>
@@ -4992,7 +4996,7 @@
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>119</v>
       </c>
@@ -5007,7 +5011,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="8"/>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>119</v>
       </c>
@@ -5022,7 +5026,7 @@
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>119</v>
       </c>
@@ -5037,7 +5041,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>119</v>
       </c>
@@ -5052,7 +5056,7 @@
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>119</v>
       </c>
@@ -5067,7 +5071,7 @@
       <c r="F40" s="8"/>
       <c r="G40" s="8"/>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>119</v>
       </c>
@@ -5082,7 +5086,7 @@
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>119</v>
       </c>
@@ -5097,7 +5101,7 @@
       <c r="F42" s="8"/>
       <c r="G42" s="8"/>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>119</v>
       </c>
@@ -5112,7 +5116,7 @@
       <c r="F43" s="8"/>
       <c r="G43" s="8"/>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
         <v>119</v>
       </c>
@@ -5127,7 +5131,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>119</v>
       </c>
@@ -5142,7 +5146,7 @@
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>119</v>
       </c>
@@ -5157,7 +5161,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
     </row>
-    <row r="47" spans="1:7" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>118</v>
       </c>
@@ -5176,7 +5180,7 @@
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>118</v>
       </c>
@@ -5193,7 +5197,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
         <v>118</v>
       </c>
@@ -5210,7 +5214,7 @@
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
         <v>118</v>
       </c>
@@ -5227,7 +5231,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="8"/>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
         <v>118</v>
       </c>
@@ -5244,7 +5248,7 @@
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
         <v>118</v>
       </c>
@@ -5261,7 +5265,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="8"/>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
         <v>118</v>
       </c>
@@ -5278,7 +5282,7 @@
       <c r="F53" s="8"/>
       <c r="G53" s="8"/>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
         <v>118</v>
       </c>
@@ -5295,7 +5299,7 @@
       <c r="F54" s="8"/>
       <c r="G54" s="8"/>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
         <v>118</v>
       </c>
@@ -5312,7 +5316,7 @@
       <c r="F55" s="8"/>
       <c r="G55" s="8"/>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>118</v>
       </c>
@@ -5329,7 +5333,7 @@
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
         <v>118</v>
       </c>
@@ -5346,7 +5350,7 @@
       <c r="F57" s="8"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
         <v>118</v>
       </c>
@@ -5363,7 +5367,7 @@
       <c r="F58" s="8"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
         <v>118</v>
       </c>
@@ -5380,7 +5384,7 @@
       <c r="F59" s="8"/>
       <c r="G59" s="8"/>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
         <v>118</v>
       </c>
@@ -5397,7 +5401,7 @@
       <c r="F60" s="8"/>
       <c r="G60" s="8"/>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
         <v>118</v>
       </c>
@@ -5414,7 +5418,7 @@
       <c r="F61" s="8"/>
       <c r="G61" s="8"/>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
         <v>118</v>
       </c>
@@ -5431,7 +5435,7 @@
       <c r="F62" s="8"/>
       <c r="G62" s="8"/>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
         <v>118</v>
       </c>
@@ -5448,7 +5452,7 @@
       <c r="F63" s="8"/>
       <c r="G63" s="8"/>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
         <v>118</v>
       </c>
@@ -5465,7 +5469,7 @@
       <c r="F64" s="8"/>
       <c r="G64" s="8"/>
     </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>118</v>
       </c>
@@ -5482,7 +5486,7 @@
       <c r="F65" s="8"/>
       <c r="G65" s="8"/>
     </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
         <v>118</v>
       </c>
@@ -5499,7 +5503,7 @@
       <c r="F66" s="8"/>
       <c r="G66" s="8"/>
     </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
         <v>118</v>
       </c>
@@ -5516,7 +5520,7 @@
       <c r="F67" s="8"/>
       <c r="G67" s="8"/>
     </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
         <v>118</v>
       </c>
@@ -5533,7 +5537,7 @@
       <c r="F68" s="8"/>
       <c r="G68" s="8"/>
     </row>
-    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
         <v>118</v>
       </c>
@@ -5550,7 +5554,7 @@
       <c r="F69" s="8"/>
       <c r="G69" s="8"/>
     </row>
-    <row r="70" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
         <v>117</v>
       </c>
@@ -5569,7 +5573,7 @@
       <c r="F70" s="8"/>
       <c r="G70" s="8"/>
     </row>
-    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
         <v>117</v>
       </c>
@@ -5586,7 +5590,7 @@
       <c r="F71" s="8"/>
       <c r="G71" s="8"/>
     </row>
-    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
         <v>117</v>
       </c>
@@ -5603,7 +5607,7 @@
       <c r="F72" s="8"/>
       <c r="G72" s="8"/>
     </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
         <v>117</v>
       </c>
@@ -5620,7 +5624,7 @@
       <c r="F73" s="8"/>
       <c r="G73" s="8"/>
     </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
         <v>117</v>
       </c>
@@ -5637,7 +5641,7 @@
       <c r="F74" s="8"/>
       <c r="G74" s="8"/>
     </row>
-    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
         <v>117</v>
       </c>
@@ -5654,7 +5658,7 @@
       <c r="F75" s="8"/>
       <c r="G75" s="8"/>
     </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
         <v>117</v>
       </c>
@@ -5671,7 +5675,7 @@
       <c r="F76" s="8"/>
       <c r="G76" s="8"/>
     </row>
-    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
         <v>117</v>
       </c>
@@ -5688,7 +5692,7 @@
       <c r="F77" s="8"/>
       <c r="G77" s="8"/>
     </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="8" t="s">
         <v>113</v>
       </c>
@@ -5703,7 +5707,7 @@
       <c r="F78" s="8"/>
       <c r="G78" s="8"/>
     </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
         <v>113</v>
       </c>
@@ -5718,7 +5722,7 @@
       <c r="F79" s="8"/>
       <c r="G79" s="8"/>
     </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="8" t="s">
         <v>113</v>
       </c>
@@ -5733,7 +5737,7 @@
       <c r="F80" s="8"/>
       <c r="G80" s="8"/>
     </row>
-    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
         <v>113</v>
       </c>
@@ -5748,7 +5752,7 @@
       <c r="F81" s="8"/>
       <c r="G81" s="8"/>
     </row>
-    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
         <v>113</v>
       </c>
@@ -5763,7 +5767,7 @@
       <c r="F82" s="8"/>
       <c r="G82" s="8"/>
     </row>
-    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
         <v>113</v>
       </c>
@@ -5778,7 +5782,7 @@
       <c r="F83" s="8"/>
       <c r="G83" s="8"/>
     </row>
-    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="8" t="s">
         <v>113</v>
       </c>
@@ -5793,7 +5797,7 @@
       <c r="F84" s="8"/>
       <c r="G84" s="8"/>
     </row>
-    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
         <v>113</v>
       </c>
@@ -5808,7 +5812,7 @@
       <c r="F85" s="8"/>
       <c r="G85" s="8"/>
     </row>
-    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="8" t="s">
         <v>113</v>
       </c>
@@ -5823,7 +5827,7 @@
       <c r="F86" s="8"/>
       <c r="G86" s="8"/>
     </row>
-    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
         <v>113</v>
       </c>
@@ -5838,7 +5842,7 @@
       <c r="F87" s="8"/>
       <c r="G87" s="8"/>
     </row>
-    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="8" t="s">
         <v>113</v>
       </c>
@@ -5853,7 +5857,7 @@
       <c r="F88" s="8"/>
       <c r="G88" s="8"/>
     </row>
-    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
         <v>113</v>
       </c>
@@ -5868,7 +5872,7 @@
       <c r="F89" s="8"/>
       <c r="G89" s="8"/>
     </row>
-    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="8" t="s">
         <v>113</v>
       </c>
@@ -5883,7 +5887,7 @@
       <c r="F90" s="8"/>
       <c r="G90" s="8"/>
     </row>
-    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
         <v>113</v>
       </c>
@@ -5898,7 +5902,7 @@
       <c r="F91" s="8"/>
       <c r="G91" s="8"/>
     </row>
-    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
         <v>113</v>
       </c>
@@ -5913,7 +5917,7 @@
       <c r="F92" s="8"/>
       <c r="G92" s="8"/>
     </row>
-    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
         <v>113</v>
       </c>
@@ -5928,7 +5932,7 @@
       <c r="F93" s="8"/>
       <c r="G93" s="8"/>
     </row>
-    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="8" t="s">
         <v>33</v>
       </c>
@@ -5943,7 +5947,7 @@
       <c r="F94" s="8"/>
       <c r="G94" s="8"/>
     </row>
-    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
         <v>33</v>
       </c>
@@ -5958,7 +5962,7 @@
       <c r="F95" s="8"/>
       <c r="G95" s="8"/>
     </row>
-    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="8" t="s">
         <v>33</v>
       </c>
@@ -5973,7 +5977,7 @@
       <c r="F96" s="8"/>
       <c r="G96" s="8"/>
     </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
         <v>33</v>
       </c>
@@ -5988,7 +5992,7 @@
       <c r="F97" s="8"/>
       <c r="G97" s="8"/>
     </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="8" t="s">
         <v>33</v>
       </c>
@@ -6003,7 +6007,7 @@
       <c r="F98" s="8"/>
       <c r="G98" s="8"/>
     </row>
-    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
         <v>33</v>
       </c>
@@ -6018,7 +6022,7 @@
       <c r="F99" s="8"/>
       <c r="G99" s="8"/>
     </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="8" t="s">
         <v>33</v>
       </c>
@@ -6033,7 +6037,7 @@
       <c r="F100" s="8"/>
       <c r="G100" s="8"/>
     </row>
-    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
         <v>33</v>
       </c>
@@ -6048,7 +6052,7 @@
       <c r="F101" s="8"/>
       <c r="G101" s="8"/>
     </row>
-    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="8" t="s">
         <v>33</v>
       </c>
@@ -6063,7 +6067,7 @@
       <c r="F102" s="8"/>
       <c r="G102" s="8"/>
     </row>
-    <row r="103" spans="1:7" ht="66" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
         <v>36</v>
       </c>
@@ -6082,7 +6086,7 @@
       <c r="F103" s="8"/>
       <c r="G103" s="8"/>
     </row>
-    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="8" t="s">
         <v>36</v>
       </c>
@@ -6099,7 +6103,7 @@
       <c r="F104" s="8"/>
       <c r="G104" s="8"/>
     </row>
-    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
         <v>36</v>
       </c>
@@ -6116,7 +6120,7 @@
       <c r="F105" s="8"/>
       <c r="G105" s="8"/>
     </row>
-    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="8" t="s">
         <v>36</v>
       </c>
@@ -6133,7 +6137,7 @@
       <c r="F106" s="8"/>
       <c r="G106" s="8"/>
     </row>
-    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
         <v>36</v>
       </c>
@@ -6150,7 +6154,7 @@
       <c r="F107" s="8"/>
       <c r="G107" s="8"/>
     </row>
-    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="8" t="s">
         <v>36</v>
       </c>
@@ -6167,7 +6171,7 @@
       <c r="F108" s="8"/>
       <c r="G108" s="8"/>
     </row>
-    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
         <v>36</v>
       </c>
@@ -6184,7 +6188,7 @@
       <c r="F109" s="8"/>
       <c r="G109" s="8"/>
     </row>
-    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="8" t="s">
         <v>36</v>
       </c>
@@ -6201,7 +6205,7 @@
       <c r="F110" s="8"/>
       <c r="G110" s="8"/>
     </row>
-    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
         <v>36</v>
       </c>
@@ -6218,7 +6222,7 @@
       <c r="F111" s="8"/>
       <c r="G111" s="8"/>
     </row>
-    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="8" t="s">
         <v>36</v>
       </c>
@@ -6235,7 +6239,7 @@
       <c r="F112" s="8"/>
       <c r="G112" s="8"/>
     </row>
-    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
         <v>36</v>
       </c>
@@ -6252,7 +6256,7 @@
       <c r="F113" s="8"/>
       <c r="G113" s="8"/>
     </row>
-    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
         <v>36</v>
       </c>
@@ -6269,7 +6273,7 @@
       <c r="F114" s="8"/>
       <c r="G114" s="8"/>
     </row>
-    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
         <v>36</v>
       </c>
@@ -6286,7 +6290,7 @@
       <c r="F115" s="8"/>
       <c r="G115" s="8"/>
     </row>
-    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="8" t="s">
         <v>36</v>
       </c>
@@ -6303,7 +6307,7 @@
       <c r="F116" s="8"/>
       <c r="G116" s="8"/>
     </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
         <v>36</v>
       </c>
@@ -6320,7 +6324,7 @@
       <c r="F117" s="8"/>
       <c r="G117" s="8"/>
     </row>
-    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="8" t="s">
         <v>36</v>
       </c>
@@ -6337,7 +6341,7 @@
       <c r="F118" s="8"/>
       <c r="G118" s="8"/>
     </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
         <v>36</v>
       </c>
@@ -6354,7 +6358,7 @@
       <c r="F119" s="8"/>
       <c r="G119" s="8"/>
     </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="8" t="s">
         <v>40</v>
       </c>
@@ -6369,7 +6373,7 @@
       <c r="F120" s="8"/>
       <c r="G120" s="8"/>
     </row>
-    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
         <v>40</v>
       </c>
@@ -6384,7 +6388,7 @@
       <c r="F121" s="8"/>
       <c r="G121" s="8"/>
     </row>
-    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="8" t="s">
         <v>40</v>
       </c>
@@ -6399,7 +6403,7 @@
       <c r="F122" s="8"/>
       <c r="G122" s="8"/>
     </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
         <v>40</v>
       </c>
@@ -6414,7 +6418,7 @@
       <c r="F123" s="8"/>
       <c r="G123" s="8"/>
     </row>
-    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="8" t="s">
         <v>40</v>
       </c>
@@ -6429,7 +6433,7 @@
       <c r="F124" s="8"/>
       <c r="G124" s="8"/>
     </row>
-    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
         <v>40</v>
       </c>
@@ -6444,7 +6448,7 @@
       <c r="F125" s="8"/>
       <c r="G125" s="8"/>
     </row>
-    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="8" t="s">
         <v>40</v>
       </c>
@@ -6459,7 +6463,7 @@
       <c r="F126" s="8"/>
       <c r="G126" s="8"/>
     </row>
-    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
         <v>40</v>
       </c>
@@ -6474,7 +6478,7 @@
       <c r="F127" s="8"/>
       <c r="G127" s="8"/>
     </row>
-    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="8" t="s">
         <v>40</v>
       </c>
@@ -6489,7 +6493,7 @@
       <c r="F128" s="8"/>
       <c r="G128" s="8"/>
     </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
         <v>40</v>
       </c>
@@ -6504,7 +6508,7 @@
       <c r="F129" s="8"/>
       <c r="G129" s="8"/>
     </row>
-    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="8" t="s">
         <v>40</v>
       </c>
@@ -6519,7 +6523,7 @@
       <c r="F130" s="8"/>
       <c r="G130" s="8"/>
     </row>
-    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
         <v>40</v>
       </c>
@@ -6534,7 +6538,7 @@
       <c r="F131" s="8"/>
       <c r="G131" s="8"/>
     </row>
-    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="8" t="s">
         <v>40</v>
       </c>
@@ -6549,7 +6553,7 @@
       <c r="F132" s="8"/>
       <c r="G132" s="8"/>
     </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
         <v>40</v>
       </c>
@@ -6564,7 +6568,7 @@
       <c r="F133" s="8"/>
       <c r="G133" s="8"/>
     </row>
-    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="8" t="s">
         <v>40</v>
       </c>
@@ -6579,7 +6583,7 @@
       <c r="F134" s="8"/>
       <c r="G134" s="8"/>
     </row>
-    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
         <v>40</v>
       </c>
@@ -6594,7 +6598,7 @@
       <c r="F135" s="8"/>
       <c r="G135" s="8"/>
     </row>
-    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="8" t="s">
         <v>40</v>
       </c>
@@ -6609,7 +6613,7 @@
       <c r="F136" s="8"/>
       <c r="G136" s="8"/>
     </row>
-    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
         <v>40</v>
       </c>
@@ -6624,7 +6628,7 @@
       <c r="F137" s="8"/>
       <c r="G137" s="8"/>
     </row>
-    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
         <v>40</v>
       </c>
@@ -6639,7 +6643,7 @@
       <c r="F138" s="8"/>
       <c r="G138" s="8"/>
     </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
         <v>40</v>
       </c>
@@ -6654,7 +6658,7 @@
       <c r="F139" s="8"/>
       <c r="G139" s="8"/>
     </row>
-    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="8" t="s">
         <v>40</v>
       </c>
@@ -6669,7 +6673,7 @@
       <c r="F140" s="8"/>
       <c r="G140" s="8"/>
     </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
         <v>40</v>
       </c>
@@ -6684,7 +6688,7 @@
       <c r="F141" s="8"/>
       <c r="G141" s="8"/>
     </row>
-    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="8" t="s">
         <v>40</v>
       </c>
@@ -6699,7 +6703,7 @@
       <c r="F142" s="8"/>
       <c r="G142" s="8"/>
     </row>
-    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
         <v>37</v>
       </c>
@@ -6714,7 +6718,7 @@
       <c r="F143" s="8"/>
       <c r="G143" s="8"/>
     </row>
-    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="8" t="s">
         <v>37</v>
       </c>
@@ -6729,7 +6733,7 @@
       <c r="F144" s="8"/>
       <c r="G144" s="8"/>
     </row>
-    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
         <v>37</v>
       </c>
@@ -6744,7 +6748,7 @@
       <c r="F145" s="8"/>
       <c r="G145" s="8"/>
     </row>
-    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="8" t="s">
         <v>37</v>
       </c>
@@ -6759,7 +6763,7 @@
       <c r="F146" s="8"/>
       <c r="G146" s="8"/>
     </row>
-    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
         <v>37</v>
       </c>
@@ -6774,7 +6778,7 @@
       <c r="F147" s="8"/>
       <c r="G147" s="8"/>
     </row>
-    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
         <v>37</v>
       </c>
@@ -6789,7 +6793,7 @@
       <c r="F148" s="8"/>
       <c r="G148" s="8"/>
     </row>
-    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
         <v>37</v>
       </c>
@@ -6804,7 +6808,7 @@
       <c r="F149" s="8"/>
       <c r="G149" s="8"/>
     </row>
-    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="8" t="s">
         <v>37</v>
       </c>
@@ -6819,7 +6823,7 @@
       <c r="F150" s="8"/>
       <c r="G150" s="8"/>
     </row>
-    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
         <v>37</v>
       </c>
@@ -6834,7 +6838,7 @@
       <c r="F151" s="8"/>
       <c r="G151" s="8"/>
     </row>
-    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="8" t="s">
         <v>37</v>
       </c>
@@ -6849,7 +6853,7 @@
       <c r="F152" s="8"/>
       <c r="G152" s="8"/>
     </row>
-    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
         <v>37</v>
       </c>
@@ -6864,7 +6868,7 @@
       <c r="F153" s="8"/>
       <c r="G153" s="8"/>
     </row>
-    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="8" t="s">
         <v>37</v>
       </c>
@@ -6879,7 +6883,7 @@
       <c r="F154" s="8"/>
       <c r="G154" s="8"/>
     </row>
-    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
         <v>37</v>
       </c>
@@ -6894,7 +6898,7 @@
       <c r="F155" s="8"/>
       <c r="G155" s="8"/>
     </row>
-    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="8" t="s">
         <v>37</v>
       </c>
@@ -6909,7 +6913,7 @@
       <c r="F156" s="8"/>
       <c r="G156" s="8"/>
     </row>
-    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
         <v>37</v>
       </c>
@@ -6924,7 +6928,7 @@
       <c r="F157" s="8"/>
       <c r="G157" s="8"/>
     </row>
-    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="8" t="s">
         <v>38</v>
       </c>
@@ -6939,7 +6943,7 @@
       <c r="F158" s="8"/>
       <c r="G158" s="8"/>
     </row>
-    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
         <v>38</v>
       </c>
@@ -6954,7 +6958,7 @@
       <c r="F159" s="8"/>
       <c r="G159" s="8"/>
     </row>
-    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="8" t="s">
         <v>38</v>
       </c>
@@ -6969,7 +6973,7 @@
       <c r="F160" s="8"/>
       <c r="G160" s="8"/>
     </row>
-    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
         <v>38</v>
       </c>
@@ -6984,7 +6988,7 @@
       <c r="F161" s="8"/>
       <c r="G161" s="8"/>
     </row>
-    <row r="162" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A162" s="8" t="s">
         <v>93</v>
       </c>
@@ -7005,7 +7009,7 @@
       </c>
       <c r="G162" s="8"/>
     </row>
-    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
         <v>93</v>
       </c>
@@ -7023,7 +7027,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="8" t="s">
         <v>93</v>
       </c>
@@ -7042,7 +7046,7 @@
       </c>
       <c r="G164" s="8"/>
     </row>
-    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
         <v>93</v>
       </c>
@@ -7061,7 +7065,7 @@
       </c>
       <c r="G165" s="8"/>
     </row>
-    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="8" t="s">
         <v>93</v>
       </c>
@@ -7080,7 +7084,7 @@
       </c>
       <c r="G166" s="8"/>
     </row>
-    <row r="167" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
         <v>93</v>
       </c>
@@ -7101,7 +7105,7 @@
       </c>
       <c r="G167" s="8"/>
     </row>
-    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="8" t="s">
         <v>93</v>
       </c>
@@ -7120,7 +7124,7 @@
       </c>
       <c r="G168" s="8"/>
     </row>
-    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
         <v>93</v>
       </c>
@@ -7139,7 +7143,7 @@
       </c>
       <c r="G169" s="8"/>
     </row>
-    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
         <v>93</v>
       </c>
@@ -7158,7 +7162,7 @@
       </c>
       <c r="G170" s="8"/>
     </row>
-    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
         <v>93</v>
       </c>
@@ -7177,7 +7181,7 @@
       </c>
       <c r="G171" s="8"/>
     </row>
-    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="8" t="s">
         <v>93</v>
       </c>
@@ -7196,7 +7200,7 @@
       </c>
       <c r="G172" s="8"/>
     </row>
-    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
         <v>93</v>
       </c>
@@ -7215,7 +7219,7 @@
       </c>
       <c r="G173" s="8"/>
     </row>
-    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="8" t="s">
         <v>93</v>
       </c>
@@ -7234,7 +7238,7 @@
       </c>
       <c r="G174" s="8"/>
     </row>
-    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
         <v>93</v>
       </c>
@@ -7253,7 +7257,7 @@
       </c>
       <c r="G175" s="8"/>
     </row>
-    <row r="176" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A176" s="8" t="s">
         <v>93</v>
       </c>
@@ -7274,7 +7278,7 @@
       </c>
       <c r="G176" s="8"/>
     </row>
-    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
         <v>93</v>
       </c>
@@ -7310,7 +7314,7 @@
         <v>194</v>
       </c>
       <c r="F178" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G178" s="8"/>
     </row>
@@ -7329,7 +7333,7 @@
       </c>
       <c r="E179" s="11"/>
       <c r="F179" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G179" s="8"/>
     </row>
@@ -7348,7 +7352,7 @@
       </c>
       <c r="E180" s="11"/>
       <c r="F180" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G180" s="8"/>
     </row>
@@ -7367,7 +7371,7 @@
       </c>
       <c r="E181" s="11"/>
       <c r="F181" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G181" s="8"/>
     </row>
@@ -7386,7 +7390,7 @@
       </c>
       <c r="E182" s="11"/>
       <c r="F182" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G182" s="8"/>
     </row>
@@ -7405,7 +7409,7 @@
       </c>
       <c r="E183" s="11"/>
       <c r="F183" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G183" s="8"/>
     </row>
@@ -7424,7 +7428,7 @@
       </c>
       <c r="E184" s="11"/>
       <c r="F184" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G184" s="8"/>
     </row>
@@ -7443,7 +7447,7 @@
       </c>
       <c r="E185" s="11"/>
       <c r="F185" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G185" s="8"/>
     </row>
@@ -7462,7 +7466,7 @@
       </c>
       <c r="E186" s="11"/>
       <c r="F186" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G186" s="8"/>
     </row>
@@ -7481,7 +7485,7 @@
       </c>
       <c r="E187" s="11"/>
       <c r="F187" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G187" s="8"/>
     </row>
@@ -7500,7 +7504,7 @@
       </c>
       <c r="E188" s="11"/>
       <c r="F188" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G188" s="8"/>
     </row>
@@ -7519,7 +7523,7 @@
       </c>
       <c r="E189" s="11"/>
       <c r="F189" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G189" s="8"/>
     </row>
@@ -7538,7 +7542,7 @@
       </c>
       <c r="E190" s="11"/>
       <c r="F190" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G190" s="8"/>
     </row>
@@ -7557,7 +7561,7 @@
       </c>
       <c r="E191" s="11"/>
       <c r="F191" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G191" s="8"/>
     </row>
@@ -7577,7 +7581,9 @@
       <c r="E192" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="F192" s="8"/>
+      <c r="F192" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G192" s="8"/>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -7594,7 +7600,9 @@
         <v>192</v>
       </c>
       <c r="E193" s="11"/>
-      <c r="F193" s="8"/>
+      <c r="F193" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G193" s="8"/>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -7611,7 +7619,9 @@
         <v>192</v>
       </c>
       <c r="E194" s="11"/>
-      <c r="F194" s="8"/>
+      <c r="F194" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G194" s="8"/>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -7628,7 +7638,9 @@
         <v>192</v>
       </c>
       <c r="E195" s="11"/>
-      <c r="F195" s="8"/>
+      <c r="F195" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G195" s="8"/>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -7645,7 +7657,9 @@
         <v>192</v>
       </c>
       <c r="E196" s="11"/>
-      <c r="F196" s="8"/>
+      <c r="F196" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G196" s="8"/>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -7662,7 +7676,9 @@
         <v>192</v>
       </c>
       <c r="E197" s="11"/>
-      <c r="F197" s="8"/>
+      <c r="F197" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G197" s="8"/>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -7679,7 +7695,9 @@
         <v>192</v>
       </c>
       <c r="E198" s="11"/>
-      <c r="F198" s="8"/>
+      <c r="F198" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G198" s="8"/>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -7696,7 +7714,9 @@
         <v>192</v>
       </c>
       <c r="E199" s="11"/>
-      <c r="F199" s="8"/>
+      <c r="F199" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G199" s="8"/>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -7713,7 +7733,9 @@
         <v>192</v>
       </c>
       <c r="E200" s="11"/>
-      <c r="F200" s="8"/>
+      <c r="F200" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G200" s="8"/>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -7730,7 +7752,9 @@
         <v>192</v>
       </c>
       <c r="E201" s="11"/>
-      <c r="F201" s="8"/>
+      <c r="F201" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G201" s="8"/>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -7747,7 +7771,9 @@
         <v>192</v>
       </c>
       <c r="E202" s="11"/>
-      <c r="F202" s="8"/>
+      <c r="F202" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G202" s="8"/>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -7764,7 +7790,9 @@
         <v>192</v>
       </c>
       <c r="E203" s="11"/>
-      <c r="F203" s="8"/>
+      <c r="F203" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G203" s="8"/>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -7781,7 +7809,9 @@
         <v>192</v>
       </c>
       <c r="E204" s="11"/>
-      <c r="F204" s="8"/>
+      <c r="F204" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G204" s="8"/>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -7798,7 +7828,9 @@
         <v>192</v>
       </c>
       <c r="E205" s="11"/>
-      <c r="F205" s="8"/>
+      <c r="F205" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G205" s="8"/>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -7815,7 +7847,9 @@
         <v>192</v>
       </c>
       <c r="E206" s="11"/>
-      <c r="F206" s="8"/>
+      <c r="F206" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G206" s="8"/>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -7832,7 +7866,9 @@
         <v>192</v>
       </c>
       <c r="E207" s="11"/>
-      <c r="F207" s="8"/>
+      <c r="F207" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G207" s="8"/>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -7849,7 +7885,9 @@
         <v>192</v>
       </c>
       <c r="E208" s="11"/>
-      <c r="F208" s="8"/>
+      <c r="F208" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G208" s="8"/>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -7866,10 +7904,12 @@
         <v>192</v>
       </c>
       <c r="E209" s="11"/>
-      <c r="F209" s="8"/>
+      <c r="F209" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="G209" s="8"/>
     </row>
-    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="8" t="s">
         <v>42</v>
       </c>
@@ -7884,7 +7924,7 @@
       <c r="F210" s="8"/>
       <c r="G210" s="8"/>
     </row>
-    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
         <v>42</v>
       </c>
@@ -7899,7 +7939,7 @@
       <c r="F211" s="8"/>
       <c r="G211" s="8"/>
     </row>
-    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="8" t="s">
         <v>42</v>
       </c>
@@ -7914,7 +7954,7 @@
       <c r="F212" s="8"/>
       <c r="G212" s="8"/>
     </row>
-    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
         <v>42</v>
       </c>
@@ -7929,7 +7969,7 @@
       <c r="F213" s="8"/>
       <c r="G213" s="8"/>
     </row>
-    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="8" t="s">
         <v>42</v>
       </c>
@@ -7944,7 +7984,7 @@
       <c r="F214" s="8"/>
       <c r="G214" s="8"/>
     </row>
-    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
         <v>42</v>
       </c>
@@ -7959,7 +7999,7 @@
       <c r="F215" s="8"/>
       <c r="G215" s="8"/>
     </row>
-    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="8" t="s">
         <v>42</v>
       </c>
@@ -7974,7 +8014,7 @@
       <c r="F216" s="8"/>
       <c r="G216" s="8"/>
     </row>
-    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
         <v>42</v>
       </c>
@@ -7989,7 +8029,7 @@
       <c r="F217" s="8"/>
       <c r="G217" s="8"/>
     </row>
-    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="8" t="s">
         <v>42</v>
       </c>
@@ -8004,7 +8044,7 @@
       <c r="F218" s="8"/>
       <c r="G218" s="8"/>
     </row>
-    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
         <v>42</v>
       </c>
@@ -8019,7 +8059,7 @@
       <c r="F219" s="8"/>
       <c r="G219" s="8"/>
     </row>
-    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="8" t="s">
         <v>42</v>
       </c>
@@ -8034,7 +8074,7 @@
       <c r="F220" s="8"/>
       <c r="G220" s="8"/>
     </row>
-    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
         <v>42</v>
       </c>
@@ -8049,7 +8089,7 @@
       <c r="F221" s="8"/>
       <c r="G221" s="8"/>
     </row>
-    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="8" t="s">
         <v>42</v>
       </c>
@@ -8064,7 +8104,7 @@
       <c r="F222" s="8"/>
       <c r="G222" s="8"/>
     </row>
-    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
         <v>42</v>
       </c>
@@ -8079,7 +8119,7 @@
       <c r="F223" s="8"/>
       <c r="G223" s="8"/>
     </row>
-    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="8" t="s">
         <v>42</v>
       </c>
@@ -8094,7 +8134,7 @@
       <c r="F224" s="8"/>
       <c r="G224" s="8"/>
     </row>
-    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
         <v>42</v>
       </c>
@@ -8109,7 +8149,7 @@
       <c r="F225" s="8"/>
       <c r="G225" s="8"/>
     </row>
-    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="8" t="s">
         <v>42</v>
       </c>
@@ -8124,7 +8164,7 @@
       <c r="F226" s="8"/>
       <c r="G226" s="8"/>
     </row>
-    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
         <v>42</v>
       </c>
@@ -8139,7 +8179,7 @@
       <c r="F227" s="8"/>
       <c r="G227" s="8"/>
     </row>
-    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="8" t="s">
         <v>42</v>
       </c>
@@ -8154,7 +8194,7 @@
       <c r="F228" s="8"/>
       <c r="G228" s="8"/>
     </row>
-    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
         <v>42</v>
       </c>
@@ -8169,7 +8209,7 @@
       <c r="F229" s="8"/>
       <c r="G229" s="8"/>
     </row>
-    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="8" t="s">
         <v>39</v>
       </c>
@@ -8184,7 +8224,7 @@
       <c r="F230" s="8"/>
       <c r="G230" s="8"/>
     </row>
-    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
         <v>39</v>
       </c>
@@ -8199,7 +8239,7 @@
       <c r="F231" s="8"/>
       <c r="G231" s="8"/>
     </row>
-    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" s="8" t="s">
         <v>39</v>
       </c>
@@ -8214,7 +8254,7 @@
       <c r="F232" s="8"/>
       <c r="G232" s="8"/>
     </row>
-    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
         <v>39</v>
       </c>
@@ -8229,7 +8269,7 @@
       <c r="F233" s="8"/>
       <c r="G233" s="8"/>
     </row>
-    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" s="8" t="s">
         <v>39</v>
       </c>
@@ -8244,7 +8284,7 @@
       <c r="F234" s="8"/>
       <c r="G234" s="8"/>
     </row>
-    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
         <v>39</v>
       </c>
@@ -8259,7 +8299,7 @@
       <c r="F235" s="8"/>
       <c r="G235" s="8"/>
     </row>
-    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="8" t="s">
         <v>39</v>
       </c>
@@ -8274,7 +8314,7 @@
       <c r="F236" s="8"/>
       <c r="G236" s="8"/>
     </row>
-    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
         <v>39</v>
       </c>
@@ -8289,7 +8329,7 @@
       <c r="F237" s="8"/>
       <c r="G237" s="8"/>
     </row>
-    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="8" t="s">
         <v>39</v>
       </c>
@@ -8304,7 +8344,7 @@
       <c r="F238" s="8"/>
       <c r="G238" s="8"/>
     </row>
-    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
         <v>39</v>
       </c>
@@ -8319,7 +8359,7 @@
       <c r="F239" s="8"/>
       <c r="G239" s="8"/>
     </row>
-    <row r="240" spans="1:7" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A240" s="8" t="s">
         <v>41</v>
       </c>
@@ -8338,7 +8378,7 @@
       <c r="F240" s="8"/>
       <c r="G240" s="8"/>
     </row>
-    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" s="8" t="s">
         <v>41</v>
       </c>
@@ -8355,7 +8395,7 @@
       <c r="F241" s="8"/>
       <c r="G241" s="8"/>
     </row>
-    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" s="8" t="s">
         <v>41</v>
       </c>
@@ -8372,7 +8412,7 @@
       <c r="F242" s="8"/>
       <c r="G242" s="8"/>
     </row>
-    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" s="8" t="s">
         <v>41</v>
       </c>
@@ -8389,7 +8429,7 @@
       <c r="F243" s="8"/>
       <c r="G243" s="8"/>
     </row>
-    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" s="8" t="s">
         <v>41</v>
       </c>
@@ -8406,7 +8446,7 @@
       <c r="F244" s="8"/>
       <c r="G244" s="8"/>
     </row>
-    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" s="8" t="s">
         <v>41</v>
       </c>
@@ -8423,7 +8463,7 @@
       <c r="F245" s="8"/>
       <c r="G245" s="8"/>
     </row>
-    <row r="246" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A246" s="8" t="s">
         <v>41</v>
       </c>
@@ -8442,7 +8482,7 @@
       <c r="F246" s="8"/>
       <c r="G246" s="8"/>
     </row>
-    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" s="8" t="s">
         <v>41</v>
       </c>
@@ -8459,7 +8499,7 @@
       <c r="F247" s="8"/>
       <c r="G247" s="8"/>
     </row>
-    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" s="8" t="s">
         <v>41</v>
       </c>
@@ -8476,7 +8516,7 @@
       <c r="F248" s="8"/>
       <c r="G248" s="8"/>
     </row>
-    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" s="8" t="s">
         <v>41</v>
       </c>
@@ -8493,7 +8533,7 @@
       <c r="F249" s="8"/>
       <c r="G249" s="8"/>
     </row>
-    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" s="8" t="s">
         <v>41</v>
       </c>
@@ -8510,7 +8550,7 @@
       <c r="F250" s="8"/>
       <c r="G250" s="8"/>
     </row>
-    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" s="8" t="s">
         <v>41</v>
       </c>
@@ -8527,7 +8567,7 @@
       <c r="F251" s="8"/>
       <c r="G251" s="8"/>
     </row>
-    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" s="8" t="s">
         <v>41</v>
       </c>
@@ -8544,7 +8584,7 @@
       <c r="F252" s="8"/>
       <c r="G252" s="8"/>
     </row>
-    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" s="8" t="s">
         <v>41</v>
       </c>
@@ -8561,7 +8601,7 @@
       <c r="F253" s="8"/>
       <c r="G253" s="8"/>
     </row>
-    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" s="8" t="s">
         <v>41</v>
       </c>
@@ -8578,7 +8618,7 @@
       <c r="F254" s="8"/>
       <c r="G254" s="8"/>
     </row>
-    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" s="8" t="s">
         <v>41</v>
       </c>
@@ -8595,7 +8635,7 @@
       <c r="F255" s="8"/>
       <c r="G255" s="8"/>
     </row>
-    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="8" t="s">
         <v>41</v>
       </c>
@@ -8612,7 +8652,7 @@
       <c r="F256" s="8"/>
       <c r="G256" s="8"/>
     </row>
-    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" s="8" t="s">
         <v>41</v>
       </c>
@@ -8629,7 +8669,7 @@
       <c r="F257" s="8"/>
       <c r="G257" s="8"/>
     </row>
-    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" s="8" t="s">
         <v>41</v>
       </c>
@@ -8646,7 +8686,7 @@
       <c r="F258" s="8"/>
       <c r="G258" s="8"/>
     </row>
-    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" s="8" t="s">
         <v>41</v>
       </c>
@@ -8663,7 +8703,7 @@
       <c r="F259" s="8"/>
       <c r="G259" s="8"/>
     </row>
-    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" s="8" t="s">
         <v>41</v>
       </c>
@@ -8680,7 +8720,7 @@
       <c r="F260" s="8"/>
       <c r="G260" s="8"/>
     </row>
-    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" s="8" t="s">
         <v>41</v>
       </c>
@@ -8697,7 +8737,7 @@
       <c r="F261" s="8"/>
       <c r="G261" s="8"/>
     </row>
-    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" s="8" t="s">
         <v>41</v>
       </c>
@@ -8714,7 +8754,7 @@
       <c r="F262" s="8"/>
       <c r="G262" s="8"/>
     </row>
-    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" s="8" t="s">
         <v>41</v>
       </c>
@@ -8731,7 +8771,7 @@
       <c r="F263" s="8"/>
       <c r="G263" s="8"/>
     </row>
-    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" s="8" t="s">
         <v>41</v>
       </c>
@@ -8748,7 +8788,7 @@
       <c r="F264" s="8"/>
       <c r="G264" s="8"/>
     </row>
-    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" s="8" t="s">
         <v>41</v>
       </c>
@@ -8765,7 +8805,7 @@
       <c r="F265" s="8"/>
       <c r="G265" s="8"/>
     </row>
-    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" s="8" t="s">
         <v>41</v>
       </c>
@@ -8782,7 +8822,7 @@
       <c r="F266" s="8"/>
       <c r="G266" s="8"/>
     </row>
-    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" s="8" t="s">
         <v>41</v>
       </c>
@@ -8799,7 +8839,7 @@
       <c r="F267" s="8"/>
       <c r="G267" s="8"/>
     </row>
-    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" s="8" t="s">
         <v>41</v>
       </c>
@@ -8816,7 +8856,7 @@
       <c r="F268" s="8"/>
       <c r="G268" s="8"/>
     </row>
-    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" s="8" t="s">
         <v>41</v>
       </c>
@@ -8833,7 +8873,7 @@
       <c r="F269" s="8"/>
       <c r="G269" s="8"/>
     </row>
-    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" s="8" t="s">
         <v>41</v>
       </c>
@@ -8850,7 +8890,7 @@
       <c r="F270" s="8"/>
       <c r="G270" s="8"/>
     </row>
-    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" s="8" t="s">
         <v>41</v>
       </c>
@@ -8867,7 +8907,7 @@
       <c r="F271" s="8"/>
       <c r="G271" s="8"/>
     </row>
-    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272" s="8" t="s">
         <v>41</v>
       </c>
@@ -8884,7 +8924,7 @@
       <c r="F272" s="8"/>
       <c r="G272" s="8"/>
     </row>
-    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" s="8" t="s">
         <v>41</v>
       </c>
@@ -8901,7 +8941,7 @@
       <c r="F273" s="8"/>
       <c r="G273" s="8"/>
     </row>
-    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" s="8" t="s">
         <v>41</v>
       </c>
@@ -8918,7 +8958,7 @@
       <c r="F274" s="8"/>
       <c r="G274" s="8"/>
     </row>
-    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" s="8" t="s">
         <v>41</v>
       </c>
@@ -8935,7 +8975,7 @@
       <c r="F275" s="8"/>
       <c r="G275" s="8"/>
     </row>
-    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="8" t="s">
         <v>41</v>
       </c>
@@ -8952,7 +8992,7 @@
       <c r="F276" s="8"/>
       <c r="G276" s="8"/>
     </row>
-    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" s="8" t="s">
         <v>41</v>
       </c>
@@ -8969,7 +9009,7 @@
       <c r="F277" s="8"/>
       <c r="G277" s="8"/>
     </row>
-    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" s="8" t="s">
         <v>41</v>
       </c>
@@ -8986,7 +9026,7 @@
       <c r="F278" s="8"/>
       <c r="G278" s="8"/>
     </row>
-    <row r="279" spans="1:7" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A279" s="8" t="s">
         <v>41</v>
       </c>
@@ -9005,7 +9045,7 @@
       <c r="F279" s="8"/>
       <c r="G279" s="8"/>
     </row>
-    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" s="8" t="s">
         <v>41</v>
       </c>
@@ -9022,7 +9062,7 @@
       <c r="F280" s="8"/>
       <c r="G280" s="8"/>
     </row>
-    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" s="8" t="s">
         <v>41</v>
       </c>
@@ -9039,7 +9079,7 @@
       <c r="F281" s="8"/>
       <c r="G281" s="8"/>
     </row>
-    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" s="8" t="s">
         <v>41</v>
       </c>
@@ -9056,7 +9096,7 @@
       <c r="F282" s="8"/>
       <c r="G282" s="8"/>
     </row>
-    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" s="8" t="s">
         <v>41</v>
       </c>
@@ -9073,7 +9113,7 @@
       <c r="F283" s="8"/>
       <c r="G283" s="8"/>
     </row>
-    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="8" t="s">
         <v>41</v>
       </c>
@@ -9090,7 +9130,7 @@
       <c r="F284" s="8"/>
       <c r="G284" s="8"/>
     </row>
-    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="8" t="s">
         <v>41</v>
       </c>
@@ -9107,7 +9147,7 @@
       <c r="F285" s="8"/>
       <c r="G285" s="8"/>
     </row>
-    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" s="8" t="s">
         <v>41</v>
       </c>
@@ -9124,7 +9164,7 @@
       <c r="F286" s="8"/>
       <c r="G286" s="8"/>
     </row>
-    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" s="8" t="s">
         <v>41</v>
       </c>
@@ -9141,7 +9181,7 @@
       <c r="F287" s="8"/>
       <c r="G287" s="8"/>
     </row>
-    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" s="8" t="s">
         <v>41</v>
       </c>
@@ -9158,7 +9198,7 @@
       <c r="F288" s="8"/>
       <c r="G288" s="8"/>
     </row>
-    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" s="8" t="s">
         <v>41</v>
       </c>
@@ -9175,7 +9215,7 @@
       <c r="F289" s="8"/>
       <c r="G289" s="8"/>
     </row>
-    <row r="290" spans="1:7" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A290" s="8" t="s">
         <v>41</v>
       </c>
@@ -9194,7 +9234,7 @@
       <c r="F290" s="8"/>
       <c r="G290" s="8"/>
     </row>
-    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291" s="8" t="s">
         <v>41</v>
       </c>
@@ -9211,7 +9251,7 @@
       <c r="F291" s="8"/>
       <c r="G291" s="8"/>
     </row>
-    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" s="8" t="s">
         <v>41</v>
       </c>
@@ -9228,7 +9268,7 @@
       <c r="F292" s="8"/>
       <c r="G292" s="8"/>
     </row>
-    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" s="8" t="s">
         <v>41</v>
       </c>
@@ -9245,7 +9285,7 @@
       <c r="F293" s="8"/>
       <c r="G293" s="8"/>
     </row>
-    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294" s="8" t="s">
         <v>41</v>
       </c>
@@ -9262,7 +9302,7 @@
       <c r="F294" s="8"/>
       <c r="G294" s="8"/>
     </row>
-    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" s="8" t="s">
         <v>41</v>
       </c>
@@ -9279,7 +9319,7 @@
       <c r="F295" s="8"/>
       <c r="G295" s="8"/>
     </row>
-    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" s="8" t="s">
         <v>41</v>
       </c>
@@ -9296,7 +9336,7 @@
       <c r="F296" s="8"/>
       <c r="G296" s="8"/>
     </row>
-    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" s="8" t="s">
         <v>41</v>
       </c>
@@ -9313,7 +9353,7 @@
       <c r="F297" s="8"/>
       <c r="G297" s="8"/>
     </row>
-    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" s="8" t="s">
         <v>41</v>
       </c>
@@ -9330,7 +9370,7 @@
       <c r="F298" s="8"/>
       <c r="G298" s="8"/>
     </row>
-    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" s="8" t="s">
         <v>41</v>
       </c>
@@ -9347,7 +9387,7 @@
       <c r="F299" s="8"/>
       <c r="G299" s="8"/>
     </row>
-    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" s="8" t="s">
         <v>41</v>
       </c>
@@ -9366,16 +9406,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G300" xr:uid="{38A162FC-7907-44C7-A909-E8E1323EC5F6}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="seabream"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:G20">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A240:G300">
       <sortCondition ref="D1:D300"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="G2 F5:G5 F2:F300">
+  <conditionalFormatting sqref="G2 F2:F300 F5:G5">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"Y"</formula>
     </cfRule>

--- a/data/raw_data/feed_profiles_and_composition.xlsx
+++ b/data/raw_data/feed_profiles_and_composition.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\treimer\Documents\R-temp-files\climate_risks_to_fed_mariculture\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04F7CDA-7E3F-4F49-8F48-F42CF2E3EB7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF6EBE6-1AD0-4885-9681-21050647BA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25260" yWindow="1836" windowWidth="15528" windowHeight="13656" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10368" yWindow="1692" windowWidth="23016" windowHeight="13656" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="feed_formulations" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="228">
   <si>
     <t>ingredient</t>
   </si>
@@ -731,16 +731,16 @@
     <t>Novriadi, R., Herawati, V. E., Prayitno, S. B., Windarto, S., &amp; Tan, R. (2024). Evaluation of distiller’s dried grains with solubles in diets for Pacific white shrimp, Litopenaeus vannamei, reared under pond conditions. Journal of the World Aquaculture Society, 55(1), 62–76. https://doi.org/10.1111/jwas.13033</t>
   </si>
   <si>
+    <t>Reunion</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>Democratic People’s Republic of Korea</t>
+  </si>
+  <si>
     <t>wip</t>
-  </si>
-  <si>
-    <t>Reunion</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>Democratic People’s Republic of Korea</t>
   </si>
 </sst>
 </file>
@@ -4438,7 +4438,9 @@
       <c r="E2" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="F2" s="8"/>
+      <c r="F2" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G2" s="8"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -4455,7 +4457,9 @@
         <v>193</v>
       </c>
       <c r="E3" s="11"/>
-      <c r="F3" s="8"/>
+      <c r="F3" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G3" s="8"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -4472,7 +4476,9 @@
         <v>193</v>
       </c>
       <c r="E4" s="11"/>
-      <c r="F4" s="8"/>
+      <c r="F4" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G4" s="8"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -4489,7 +4495,9 @@
         <v>193</v>
       </c>
       <c r="E5" s="11"/>
-      <c r="F5" s="8"/>
+      <c r="F5" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
@@ -4508,7 +4516,9 @@
       <c r="E6" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="F6" s="8"/>
+      <c r="F6" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G6" s="8"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -4525,7 +4535,9 @@
         <v>153</v>
       </c>
       <c r="E7" s="11"/>
-      <c r="F7" s="8"/>
+      <c r="F7" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G7" s="8"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -4542,7 +4554,9 @@
         <v>153</v>
       </c>
       <c r="E8" s="11"/>
-      <c r="F8" s="8"/>
+      <c r="F8" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G8" s="8"/>
     </row>
     <row r="9" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
@@ -4562,7 +4576,7 @@
         <v>176</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G9" s="8"/>
     </row>
@@ -4571,7 +4585,7 @@
         <v>128</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C10" s="8">
         <v>1</v>
@@ -4581,7 +4595,7 @@
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>177</v>
@@ -4604,7 +4618,7 @@
         <v>178</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G11" s="8"/>
     </row>
@@ -4623,7 +4637,7 @@
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G12" s="8"/>
     </row>
@@ -4642,7 +4656,7 @@
       </c>
       <c r="E13" s="11"/>
       <c r="F13" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G13" s="8"/>
     </row>
@@ -4661,7 +4675,7 @@
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G14" s="8"/>
     </row>
@@ -4680,7 +4694,7 @@
       </c>
       <c r="E15" s="11"/>
       <c r="F15" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G15" s="8"/>
     </row>
@@ -4700,7 +4714,9 @@
       <c r="E16" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="F16" s="8"/>
+      <c r="F16" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G16" s="8"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -4717,7 +4733,9 @@
         <v>127</v>
       </c>
       <c r="E17" s="11"/>
-      <c r="F17" s="8"/>
+      <c r="F17" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G17" s="8"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -4734,7 +4752,9 @@
         <v>127</v>
       </c>
       <c r="E18" s="11"/>
-      <c r="F18" s="8"/>
+      <c r="F18" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G18" s="8"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -4751,7 +4771,9 @@
         <v>127</v>
       </c>
       <c r="E19" s="11"/>
-      <c r="F19" s="8"/>
+      <c r="F19" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G19" s="8"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -4768,7 +4790,9 @@
         <v>127</v>
       </c>
       <c r="E20" s="11"/>
-      <c r="F20" s="8"/>
+      <c r="F20" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="G20" s="8"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5177,7 +5201,9 @@
       <c r="E47" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="F47" s="8"/>
+      <c r="F47" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G47" s="8"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -5194,7 +5220,9 @@
         <v>192</v>
       </c>
       <c r="E48" s="11"/>
-      <c r="F48" s="8"/>
+      <c r="F48" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G48" s="8"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -5211,7 +5239,9 @@
         <v>192</v>
       </c>
       <c r="E49" s="11"/>
-      <c r="F49" s="8"/>
+      <c r="F49" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G49" s="8"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -5228,7 +5258,9 @@
         <v>192</v>
       </c>
       <c r="E50" s="11"/>
-      <c r="F50" s="8"/>
+      <c r="F50" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -5245,7 +5277,9 @@
         <v>192</v>
       </c>
       <c r="E51" s="11"/>
-      <c r="F51" s="8"/>
+      <c r="F51" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G51" s="8"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -5262,7 +5296,9 @@
         <v>192</v>
       </c>
       <c r="E52" s="11"/>
-      <c r="F52" s="8"/>
+      <c r="F52" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G52" s="8"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -5279,7 +5315,9 @@
         <v>192</v>
       </c>
       <c r="E53" s="11"/>
-      <c r="F53" s="8"/>
+      <c r="F53" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -5296,7 +5334,9 @@
         <v>192</v>
       </c>
       <c r="E54" s="11"/>
-      <c r="F54" s="8"/>
+      <c r="F54" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G54" s="8"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -5313,7 +5353,9 @@
         <v>192</v>
       </c>
       <c r="E55" s="11"/>
-      <c r="F55" s="8"/>
+      <c r="F55" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G55" s="8"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -5330,7 +5372,9 @@
         <v>192</v>
       </c>
       <c r="E56" s="11"/>
-      <c r="F56" s="8"/>
+      <c r="F56" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -5347,7 +5391,9 @@
         <v>192</v>
       </c>
       <c r="E57" s="11"/>
-      <c r="F57" s="8"/>
+      <c r="F57" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G57" s="8"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -5364,7 +5410,9 @@
         <v>192</v>
       </c>
       <c r="E58" s="11"/>
-      <c r="F58" s="8"/>
+      <c r="F58" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G58" s="8"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -5381,7 +5429,9 @@
         <v>192</v>
       </c>
       <c r="E59" s="11"/>
-      <c r="F59" s="8"/>
+      <c r="F59" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G59" s="8"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -5398,7 +5448,9 @@
         <v>192</v>
       </c>
       <c r="E60" s="11"/>
-      <c r="F60" s="8"/>
+      <c r="F60" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -5415,7 +5467,9 @@
         <v>192</v>
       </c>
       <c r="E61" s="11"/>
-      <c r="F61" s="8"/>
+      <c r="F61" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -5432,7 +5486,9 @@
         <v>192</v>
       </c>
       <c r="E62" s="11"/>
-      <c r="F62" s="8"/>
+      <c r="F62" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G62" s="8"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -5449,7 +5505,9 @@
         <v>192</v>
       </c>
       <c r="E63" s="11"/>
-      <c r="F63" s="8"/>
+      <c r="F63" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G63" s="8"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -5466,7 +5524,9 @@
         <v>192</v>
       </c>
       <c r="E64" s="11"/>
-      <c r="F64" s="8"/>
+      <c r="F64" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G64" s="8"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -5483,7 +5543,9 @@
         <v>192</v>
       </c>
       <c r="E65" s="11"/>
-      <c r="F65" s="8"/>
+      <c r="F65" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G65" s="8"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -5500,7 +5562,9 @@
         <v>192</v>
       </c>
       <c r="E66" s="11"/>
-      <c r="F66" s="8"/>
+      <c r="F66" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G66" s="8"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -5517,7 +5581,9 @@
         <v>192</v>
       </c>
       <c r="E67" s="11"/>
-      <c r="F67" s="8"/>
+      <c r="F67" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G67" s="8"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -5534,7 +5600,9 @@
         <v>192</v>
       </c>
       <c r="E68" s="11"/>
-      <c r="F68" s="8"/>
+      <c r="F68" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G68" s="8"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -5551,7 +5619,9 @@
         <v>192</v>
       </c>
       <c r="E69" s="11"/>
-      <c r="F69" s="8"/>
+      <c r="F69" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G69" s="8"/>
     </row>
     <row r="70" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
@@ -6828,7 +6898,7 @@
         <v>37</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C151" s="8">
         <v>1</v>
@@ -7005,7 +7075,7 @@
         <v>185</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G162" s="8"/>
     </row>
@@ -7024,7 +7094,7 @@
       </c>
       <c r="E163" s="11"/>
       <c r="F163" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -7042,7 +7112,7 @@
       </c>
       <c r="E164" s="11"/>
       <c r="F164" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G164" s="8"/>
     </row>
@@ -7061,7 +7131,7 @@
       </c>
       <c r="E165" s="11"/>
       <c r="F165" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G165" s="8"/>
     </row>
@@ -7080,7 +7150,7 @@
       </c>
       <c r="E166" s="11"/>
       <c r="F166" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G166" s="8"/>
     </row>
@@ -7101,7 +7171,7 @@
         <v>183</v>
       </c>
       <c r="F167" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G167" s="8"/>
     </row>
@@ -7120,7 +7190,7 @@
       </c>
       <c r="E168" s="11"/>
       <c r="F168" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G168" s="8"/>
     </row>
@@ -7139,7 +7209,7 @@
       </c>
       <c r="E169" s="11"/>
       <c r="F169" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G169" s="8"/>
     </row>
@@ -7158,7 +7228,7 @@
       </c>
       <c r="E170" s="11"/>
       <c r="F170" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G170" s="8"/>
     </row>
@@ -7177,7 +7247,7 @@
       </c>
       <c r="E171" s="11"/>
       <c r="F171" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G171" s="8"/>
     </row>
@@ -7196,7 +7266,7 @@
       </c>
       <c r="E172" s="11"/>
       <c r="F172" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G172" s="8"/>
     </row>
@@ -7215,7 +7285,7 @@
       </c>
       <c r="E173" s="11"/>
       <c r="F173" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G173" s="8"/>
     </row>
@@ -7234,7 +7304,7 @@
       </c>
       <c r="E174" s="11"/>
       <c r="F174" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G174" s="8"/>
     </row>
@@ -7253,7 +7323,7 @@
       </c>
       <c r="E175" s="11"/>
       <c r="F175" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G175" s="8"/>
     </row>
@@ -7274,7 +7344,7 @@
         <v>184</v>
       </c>
       <c r="F176" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G176" s="8"/>
     </row>
@@ -7293,7 +7363,7 @@
       </c>
       <c r="E177" s="11"/>
       <c r="F177" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G177" s="8"/>
     </row>
@@ -7314,7 +7384,7 @@
         <v>194</v>
       </c>
       <c r="F178" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G178" s="8"/>
     </row>
@@ -7333,7 +7403,7 @@
       </c>
       <c r="E179" s="11"/>
       <c r="F179" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G179" s="8"/>
     </row>
@@ -7352,7 +7422,7 @@
       </c>
       <c r="E180" s="11"/>
       <c r="F180" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G180" s="8"/>
     </row>
@@ -7371,7 +7441,7 @@
       </c>
       <c r="E181" s="11"/>
       <c r="F181" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G181" s="8"/>
     </row>
@@ -7390,7 +7460,7 @@
       </c>
       <c r="E182" s="11"/>
       <c r="F182" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G182" s="8"/>
     </row>
@@ -7409,7 +7479,7 @@
       </c>
       <c r="E183" s="11"/>
       <c r="F183" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G183" s="8"/>
     </row>
@@ -7428,7 +7498,7 @@
       </c>
       <c r="E184" s="11"/>
       <c r="F184" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G184" s="8"/>
     </row>
@@ -7447,7 +7517,7 @@
       </c>
       <c r="E185" s="11"/>
       <c r="F185" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G185" s="8"/>
     </row>
@@ -7466,7 +7536,7 @@
       </c>
       <c r="E186" s="11"/>
       <c r="F186" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G186" s="8"/>
     </row>
@@ -7485,7 +7555,7 @@
       </c>
       <c r="E187" s="11"/>
       <c r="F187" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G187" s="8"/>
     </row>
@@ -7504,7 +7574,7 @@
       </c>
       <c r="E188" s="11"/>
       <c r="F188" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G188" s="8"/>
     </row>
@@ -7523,7 +7593,7 @@
       </c>
       <c r="E189" s="11"/>
       <c r="F189" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G189" s="8"/>
     </row>
@@ -7542,7 +7612,7 @@
       </c>
       <c r="E190" s="11"/>
       <c r="F190" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G190" s="8"/>
     </row>
@@ -7561,7 +7631,7 @@
       </c>
       <c r="E191" s="11"/>
       <c r="F191" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G191" s="8"/>
     </row>
@@ -7582,7 +7652,7 @@
         <v>190</v>
       </c>
       <c r="F192" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G192" s="8"/>
     </row>
@@ -7601,7 +7671,7 @@
       </c>
       <c r="E193" s="11"/>
       <c r="F193" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G193" s="8"/>
     </row>
@@ -7620,7 +7690,7 @@
       </c>
       <c r="E194" s="11"/>
       <c r="F194" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G194" s="8"/>
     </row>
@@ -7639,7 +7709,7 @@
       </c>
       <c r="E195" s="11"/>
       <c r="F195" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G195" s="8"/>
     </row>
@@ -7658,7 +7728,7 @@
       </c>
       <c r="E196" s="11"/>
       <c r="F196" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G196" s="8"/>
     </row>
@@ -7677,7 +7747,7 @@
       </c>
       <c r="E197" s="11"/>
       <c r="F197" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G197" s="8"/>
     </row>
@@ -7696,7 +7766,7 @@
       </c>
       <c r="E198" s="11"/>
       <c r="F198" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G198" s="8"/>
     </row>
@@ -7715,7 +7785,7 @@
       </c>
       <c r="E199" s="11"/>
       <c r="F199" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G199" s="8"/>
     </row>
@@ -7734,7 +7804,7 @@
       </c>
       <c r="E200" s="11"/>
       <c r="F200" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G200" s="8"/>
     </row>
@@ -7753,7 +7823,7 @@
       </c>
       <c r="E201" s="11"/>
       <c r="F201" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G201" s="8"/>
     </row>
@@ -7772,7 +7842,7 @@
       </c>
       <c r="E202" s="11"/>
       <c r="F202" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G202" s="8"/>
     </row>
@@ -7791,7 +7861,7 @@
       </c>
       <c r="E203" s="11"/>
       <c r="F203" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G203" s="8"/>
     </row>
@@ -7810,7 +7880,7 @@
       </c>
       <c r="E204" s="11"/>
       <c r="F204" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G204" s="8"/>
     </row>
@@ -7829,7 +7899,7 @@
       </c>
       <c r="E205" s="11"/>
       <c r="F205" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G205" s="8"/>
     </row>
@@ -7848,7 +7918,7 @@
       </c>
       <c r="E206" s="11"/>
       <c r="F206" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G206" s="8"/>
     </row>
@@ -7867,7 +7937,7 @@
       </c>
       <c r="E207" s="11"/>
       <c r="F207" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G207" s="8"/>
     </row>
@@ -7886,7 +7956,7 @@
       </c>
       <c r="E208" s="11"/>
       <c r="F208" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G208" s="8"/>
     </row>
@@ -7905,7 +7975,7 @@
       </c>
       <c r="E209" s="11"/>
       <c r="F209" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G209" s="8"/>
     </row>

--- a/data/raw_data/feed_profiles_and_composition.xlsx
+++ b/data/raw_data/feed_profiles_and_composition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\treimer\Documents\R-temp-files\climate_risks_to_fed_mariculture\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF6EBE6-1AD0-4885-9681-21050647BA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF71AC50-7D01-4194-A1A2-0775340BA8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10368" yWindow="1692" windowWidth="23016" windowHeight="13656" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9480" yWindow="2604" windowWidth="23016" windowHeight="13656" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="feed_formulations" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">feed_assignments!$A$1:$G$300</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">feed_formulations!$A$1:$D$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">feed_formulations!$A$1:$D$203</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="233">
   <si>
     <t>ingredient</t>
   </si>
@@ -741,6 +741,21 @@
   </si>
   <si>
     <t>wip</t>
+  </si>
+  <si>
+    <t>squid-oil</t>
+  </si>
+  <si>
+    <t>shrimp-meal</t>
+  </si>
+  <si>
+    <t>Average of diets 3-7: https://www.fao.org/fileadmin/user_upload/affris/docs/MonoT4.pdf</t>
+  </si>
+  <si>
+    <t>tiger_prawn-world</t>
+  </si>
+  <si>
+    <t>shrimp-head-meal</t>
   </si>
 </sst>
 </file>
@@ -862,7 +877,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -885,6 +900,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1143,10 +1159,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N1097"/>
+  <dimension ref="A1:N1108"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
@@ -1254,7 +1270,7 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:14" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>49</v>
       </c>
@@ -1266,7 +1282,7 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:14" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>49</v>
       </c>
@@ -1278,7 +1294,7 @@
       </c>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:14" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>49</v>
       </c>
@@ -1290,7 +1306,7 @@
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:14" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>49</v>
       </c>
@@ -1302,7 +1318,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:14" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>49</v>
       </c>
@@ -1314,7 +1330,7 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:14" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
@@ -1326,7 +1342,7 @@
       </c>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:14" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>49</v>
       </c>
@@ -1338,7 +1354,7 @@
       </c>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:14" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>49</v>
       </c>
@@ -1350,7 +1366,7 @@
       </c>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:14" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>49</v>
       </c>
@@ -1362,7 +1378,7 @@
       </c>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>49</v>
       </c>
@@ -1374,7 +1390,7 @@
       </c>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>49</v>
       </c>
@@ -1386,7 +1402,7 @@
       </c>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>49</v>
       </c>
@@ -1398,7 +1414,7 @@
       </c>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>49</v>
       </c>
@@ -1410,7 +1426,7 @@
       </c>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>49</v>
       </c>
@@ -1422,7 +1438,7 @@
       </c>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>44</v>
       </c>
@@ -1434,7 +1450,7 @@
       </c>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>44</v>
       </c>
@@ -1446,7 +1462,7 @@
       </c>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>44</v>
       </c>
@@ -1458,7 +1474,7 @@
       </c>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>44</v>
       </c>
@@ -1470,7 +1486,7 @@
       </c>
       <c r="D25" s="2"/>
     </row>
-    <row r="26" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>44</v>
       </c>
@@ -1482,7 +1498,7 @@
       </c>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>44</v>
       </c>
@@ -1494,7 +1510,7 @@
       </c>
       <c r="D27" s="2"/>
     </row>
-    <row r="28" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
@@ -1506,7 +1522,7 @@
       </c>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>44</v>
       </c>
@@ -1518,7 +1534,7 @@
       </c>
       <c r="D29" s="2"/>
     </row>
-    <row r="30" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>44</v>
       </c>
@@ -1530,7 +1546,7 @@
       </c>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>44</v>
       </c>
@@ -1542,7 +1558,7 @@
       </c>
       <c r="D31" s="2"/>
     </row>
-    <row r="32" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>44</v>
       </c>
@@ -1554,7 +1570,7 @@
       </c>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>44</v>
       </c>
@@ -1566,7 +1582,7 @@
       </c>
       <c r="D33" s="2"/>
     </row>
-    <row r="34" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>44</v>
       </c>
@@ -1578,7 +1594,7 @@
       </c>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>44</v>
       </c>
@@ -1590,7 +1606,7 @@
       </c>
       <c r="D35" s="2"/>
     </row>
-    <row r="36" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>43</v>
       </c>
@@ -1602,7 +1618,7 @@
       </c>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>43</v>
       </c>
@@ -1614,7 +1630,7 @@
       </c>
       <c r="D37" s="2"/>
     </row>
-    <row r="38" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>43</v>
       </c>
@@ -1626,7 +1642,7 @@
       </c>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>43</v>
       </c>
@@ -1638,7 +1654,7 @@
       </c>
       <c r="D39" s="2"/>
     </row>
-    <row r="40" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>43</v>
       </c>
@@ -1650,7 +1666,7 @@
       </c>
       <c r="D40" s="2"/>
     </row>
-    <row r="41" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>43</v>
       </c>
@@ -1662,7 +1678,7 @@
       </c>
       <c r="D41" s="2"/>
     </row>
-    <row r="42" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>43</v>
       </c>
@@ -1674,7 +1690,7 @@
       </c>
       <c r="D42" s="2"/>
     </row>
-    <row r="43" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>43</v>
       </c>
@@ -1686,7 +1702,7 @@
       </c>
       <c r="D43" s="2"/>
     </row>
-    <row r="44" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>43</v>
       </c>
@@ -1698,7 +1714,7 @@
       </c>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>43</v>
       </c>
@@ -1710,7 +1726,7 @@
       </c>
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>43</v>
       </c>
@@ -1722,7 +1738,7 @@
       </c>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>43</v>
       </c>
@@ -1734,7 +1750,7 @@
       </c>
       <c r="D47" s="2"/>
     </row>
-    <row r="48" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>43</v>
       </c>
@@ -1746,7 +1762,7 @@
       </c>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>43</v>
       </c>
@@ -1758,7 +1774,7 @@
       </c>
       <c r="D49" s="2"/>
     </row>
-    <row r="50" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>43</v>
       </c>
@@ -1770,7 +1786,7 @@
       </c>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>43</v>
       </c>
@@ -1782,7 +1798,7 @@
       </c>
       <c r="D51" s="2"/>
     </row>
-    <row r="52" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>43</v>
       </c>
@@ -1794,7 +1810,7 @@
       </c>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>48</v>
       </c>
@@ -1806,7 +1822,7 @@
       </c>
       <c r="D53" s="2"/>
     </row>
-    <row r="54" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>48</v>
       </c>
@@ -1818,7 +1834,7 @@
       </c>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>48</v>
       </c>
@@ -1830,7 +1846,7 @@
       </c>
       <c r="D55" s="2"/>
     </row>
-    <row r="56" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>48</v>
       </c>
@@ -1842,7 +1858,7 @@
       </c>
       <c r="D56" s="2"/>
     </row>
-    <row r="57" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>48</v>
       </c>
@@ -1854,7 +1870,7 @@
       </c>
       <c r="D57" s="2"/>
     </row>
-    <row r="58" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>48</v>
       </c>
@@ -1866,7 +1882,7 @@
       </c>
       <c r="D58" s="2"/>
     </row>
-    <row r="59" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>48</v>
       </c>
@@ -1878,7 +1894,7 @@
       </c>
       <c r="D59" s="2"/>
     </row>
-    <row r="60" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>48</v>
       </c>
@@ -1890,7 +1906,7 @@
       </c>
       <c r="D60" s="2"/>
     </row>
-    <row r="61" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>48</v>
       </c>
@@ -1902,7 +1918,7 @@
       </c>
       <c r="D61" s="2"/>
     </row>
-    <row r="62" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>48</v>
       </c>
@@ -1914,7 +1930,7 @@
       </c>
       <c r="D62" s="2"/>
     </row>
-    <row r="63" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>48</v>
       </c>
@@ -1926,7 +1942,7 @@
       </c>
       <c r="D63" s="2"/>
     </row>
-    <row r="64" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>48</v>
       </c>
@@ -1938,7 +1954,7 @@
       </c>
       <c r="D64" s="2"/>
     </row>
-    <row r="65" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>198</v>
       </c>
@@ -1950,7 +1966,7 @@
       </c>
       <c r="D65" s="2"/>
     </row>
-    <row r="66" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>198</v>
       </c>
@@ -1962,7 +1978,7 @@
       </c>
       <c r="D66" s="2"/>
     </row>
-    <row r="67" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>198</v>
       </c>
@@ -1974,7 +1990,7 @@
       </c>
       <c r="D67" s="3"/>
     </row>
-    <row r="68" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>198</v>
       </c>
@@ -1986,7 +2002,7 @@
       </c>
       <c r="D68" s="2"/>
     </row>
-    <row r="69" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>198</v>
       </c>
@@ -1998,7 +2014,7 @@
       </c>
       <c r="D69" s="2"/>
     </row>
-    <row r="70" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>198</v>
       </c>
@@ -2010,7 +2026,7 @@
       </c>
       <c r="D70" s="2"/>
     </row>
-    <row r="71" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>198</v>
       </c>
@@ -2022,7 +2038,7 @@
       </c>
       <c r="D71" s="2"/>
     </row>
-    <row r="72" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>198</v>
       </c>
@@ -2034,7 +2050,7 @@
       </c>
       <c r="D72" s="2"/>
     </row>
-    <row r="73" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>198</v>
       </c>
@@ -2046,7 +2062,7 @@
       </c>
       <c r="D73" s="2"/>
     </row>
-    <row r="74" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>198</v>
       </c>
@@ -2058,7 +2074,7 @@
       </c>
       <c r="D74" s="2"/>
     </row>
-    <row r="75" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>198</v>
       </c>
@@ -2070,7 +2086,7 @@
       </c>
       <c r="D75" s="2"/>
     </row>
-    <row r="76" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>198</v>
       </c>
@@ -2082,7 +2098,7 @@
       </c>
       <c r="D76" s="2"/>
     </row>
-    <row r="77" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>210</v>
       </c>
@@ -2094,7 +2110,7 @@
       </c>
       <c r="D77" s="3"/>
     </row>
-    <row r="78" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>210</v>
       </c>
@@ -2106,7 +2122,7 @@
       </c>
       <c r="D78" s="3"/>
     </row>
-    <row r="79" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>210</v>
       </c>
@@ -2118,7 +2134,7 @@
       </c>
       <c r="D79" s="3"/>
     </row>
-    <row r="80" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>210</v>
       </c>
@@ -2130,7 +2146,7 @@
       </c>
       <c r="D80" s="3"/>
     </row>
-    <row r="81" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>210</v>
       </c>
@@ -2142,7 +2158,7 @@
       </c>
       <c r="D81" s="3"/>
     </row>
-    <row r="82" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>210</v>
       </c>
@@ -2154,7 +2170,7 @@
       </c>
       <c r="D82" s="3"/>
     </row>
-    <row r="83" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>210</v>
       </c>
@@ -2166,7 +2182,7 @@
       </c>
       <c r="D83" s="3"/>
     </row>
-    <row r="84" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>210</v>
       </c>
@@ -2178,7 +2194,7 @@
       </c>
       <c r="D84" s="3"/>
     </row>
-    <row r="85" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>210</v>
       </c>
@@ -2190,7 +2206,7 @@
       </c>
       <c r="D85" s="3"/>
     </row>
-    <row r="86" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>210</v>
       </c>
@@ -2202,7 +2218,7 @@
       </c>
       <c r="D86" s="3"/>
     </row>
-    <row r="87" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>210</v>
       </c>
@@ -2214,7 +2230,7 @@
       </c>
       <c r="D87" s="3"/>
     </row>
-    <row r="88" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>30</v>
       </c>
@@ -2228,7 +2244,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>33</v>
       </c>
@@ -2243,7 +2259,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>33</v>
       </c>
@@ -2258,7 +2274,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>33</v>
       </c>
@@ -2273,7 +2289,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>33</v>
       </c>
@@ -2288,7 +2304,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>33</v>
       </c>
@@ -2303,7 +2319,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>33</v>
       </c>
@@ -2318,7 +2334,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>29</v>
       </c>
@@ -2330,7 +2346,7 @@
       </c>
       <c r="D95" s="2"/>
     </row>
-    <row r="96" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>203</v>
       </c>
@@ -2342,7 +2358,7 @@
       </c>
       <c r="D96" s="3"/>
     </row>
-    <row r="97" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>203</v>
       </c>
@@ -2354,7 +2370,7 @@
       </c>
       <c r="D97" s="3"/>
     </row>
-    <row r="98" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>203</v>
       </c>
@@ -2366,7 +2382,7 @@
       </c>
       <c r="D98" s="3"/>
     </row>
-    <row r="99" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>203</v>
       </c>
@@ -2378,7 +2394,7 @@
       </c>
       <c r="D99" s="3"/>
     </row>
-    <row r="100" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>203</v>
       </c>
@@ -2390,7 +2406,7 @@
       </c>
       <c r="D100" s="3"/>
     </row>
-    <row r="101" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>203</v>
       </c>
@@ -2402,7 +2418,7 @@
       </c>
       <c r="D101" s="3"/>
     </row>
-    <row r="102" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>203</v>
       </c>
@@ -2414,7 +2430,7 @@
       </c>
       <c r="D102" s="3"/>
     </row>
-    <row r="103" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>203</v>
       </c>
@@ -2426,7 +2442,7 @@
       </c>
       <c r="D103" s="3"/>
     </row>
-    <row r="104" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>203</v>
       </c>
@@ -2438,22 +2454,22 @@
       </c>
       <c r="D104" s="3"/>
     </row>
-    <row r="105" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>181</v>
       </c>
@@ -2465,7 +2481,7 @@
       </c>
       <c r="D108" s="3"/>
     </row>
-    <row r="109" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>181</v>
       </c>
@@ -2477,7 +2493,7 @@
       </c>
       <c r="D109" s="3"/>
     </row>
-    <row r="110" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>181</v>
       </c>
@@ -2489,7 +2505,7 @@
       </c>
       <c r="D110" s="3"/>
     </row>
-    <row r="111" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>181</v>
       </c>
@@ -2501,7 +2517,7 @@
       </c>
       <c r="D111" s="3"/>
     </row>
-    <row r="112" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>181</v>
       </c>
@@ -2516,7 +2532,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>181</v>
       </c>
@@ -2531,7 +2547,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>181</v>
       </c>
@@ -2546,7 +2562,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>181</v>
       </c>
@@ -2561,7 +2577,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>181</v>
       </c>
@@ -2573,7 +2589,7 @@
       </c>
       <c r="D116" s="3"/>
     </row>
-    <row r="117" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>181</v>
       </c>
@@ -2585,7 +2601,7 @@
       </c>
       <c r="D117" s="3"/>
     </row>
-    <row r="118" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>181</v>
       </c>
@@ -2597,7 +2613,7 @@
       </c>
       <c r="D118" s="3"/>
     </row>
-    <row r="119" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>181</v>
       </c>
@@ -2609,7 +2625,7 @@
       </c>
       <c r="D119" s="3"/>
     </row>
-    <row r="120" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>181</v>
       </c>
@@ -2621,7 +2637,7 @@
       </c>
       <c r="D120" s="3"/>
     </row>
-    <row r="121" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>181</v>
       </c>
@@ -2633,7 +2649,7 @@
       </c>
       <c r="D121" s="3"/>
     </row>
-    <row r="122" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>179</v>
       </c>
@@ -2645,7 +2661,7 @@
       </c>
       <c r="D122" s="3"/>
     </row>
-    <row r="123" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>179</v>
       </c>
@@ -2657,7 +2673,7 @@
       </c>
       <c r="D123" s="3"/>
     </row>
-    <row r="124" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>179</v>
       </c>
@@ -2669,7 +2685,7 @@
       </c>
       <c r="D124" s="3"/>
     </row>
-    <row r="125" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>179</v>
       </c>
@@ -2681,7 +2697,7 @@
       </c>
       <c r="D125" s="3"/>
     </row>
-    <row r="126" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>179</v>
       </c>
@@ -2693,7 +2709,7 @@
       </c>
       <c r="D126" s="3"/>
     </row>
-    <row r="127" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>179</v>
       </c>
@@ -2705,7 +2721,7 @@
       </c>
       <c r="D127" s="3"/>
     </row>
-    <row r="128" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>179</v>
       </c>
@@ -2717,7 +2733,7 @@
       </c>
       <c r="D128" s="3"/>
     </row>
-    <row r="129" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>179</v>
       </c>
@@ -2729,7 +2745,7 @@
       </c>
       <c r="D129" s="3"/>
     </row>
-    <row r="130" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>179</v>
       </c>
@@ -2741,7 +2757,7 @@
       </c>
       <c r="D130" s="3"/>
     </row>
-    <row r="131" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>179</v>
       </c>
@@ -2753,7 +2769,7 @@
       </c>
       <c r="D131" s="3"/>
     </row>
-    <row r="132" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>179</v>
       </c>
@@ -2765,7 +2781,7 @@
       </c>
       <c r="D132" s="3"/>
     </row>
-    <row r="133" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>179</v>
       </c>
@@ -2777,7 +2793,7 @@
       </c>
       <c r="D133" s="3"/>
     </row>
-    <row r="134" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>179</v>
       </c>
@@ -2789,7 +2805,7 @@
       </c>
       <c r="D134" s="3"/>
     </row>
-    <row r="135" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>179</v>
       </c>
@@ -2801,7 +2817,7 @@
       </c>
       <c r="D135" s="3"/>
     </row>
-    <row r="136" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>179</v>
       </c>
@@ -2813,7 +2829,7 @@
       </c>
       <c r="D136" s="3"/>
     </row>
-    <row r="137" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>179</v>
       </c>
@@ -2825,7 +2841,7 @@
       </c>
       <c r="D137" s="3"/>
     </row>
-    <row r="138" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>182</v>
       </c>
@@ -2837,7 +2853,7 @@
       </c>
       <c r="D138" s="3"/>
     </row>
-    <row r="139" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>182</v>
       </c>
@@ -2849,7 +2865,7 @@
       </c>
       <c r="D139" s="3"/>
     </row>
-    <row r="140" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>182</v>
       </c>
@@ -2864,7 +2880,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>182</v>
       </c>
@@ -2879,7 +2895,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>182</v>
       </c>
@@ -2894,7 +2910,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>182</v>
       </c>
@@ -2909,7 +2925,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>182</v>
       </c>
@@ -2921,7 +2937,7 @@
       </c>
       <c r="D144" s="3"/>
     </row>
-    <row r="145" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>182</v>
       </c>
@@ -2933,7 +2949,7 @@
       </c>
       <c r="D145" s="3"/>
     </row>
-    <row r="146" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>182</v>
       </c>
@@ -2945,7 +2961,7 @@
       </c>
       <c r="D146" s="3"/>
     </row>
-    <row r="147" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>182</v>
       </c>
@@ -2957,7 +2973,7 @@
       </c>
       <c r="D147" s="3"/>
     </row>
-    <row r="148" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>182</v>
       </c>
@@ -2969,7 +2985,7 @@
       </c>
       <c r="D148" s="3"/>
     </row>
-    <row r="149" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>182</v>
       </c>
@@ -2981,7 +2997,7 @@
       </c>
       <c r="D149" s="3"/>
     </row>
-    <row r="150" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>195</v>
       </c>
@@ -2993,7 +3009,7 @@
       </c>
       <c r="D150" s="2"/>
     </row>
-    <row r="151" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>195</v>
       </c>
@@ -3005,7 +3021,7 @@
       </c>
       <c r="D151" s="2"/>
     </row>
-    <row r="152" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>195</v>
       </c>
@@ -3017,7 +3033,7 @@
       </c>
       <c r="D152" s="2"/>
     </row>
-    <row r="153" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>195</v>
       </c>
@@ -3030,7 +3046,7 @@
       </c>
       <c r="D153" s="2"/>
     </row>
-    <row r="154" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>195</v>
       </c>
@@ -3042,7 +3058,7 @@
       </c>
       <c r="D154" s="2"/>
     </row>
-    <row r="155" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>195</v>
       </c>
@@ -3054,7 +3070,7 @@
       </c>
       <c r="D155" s="2"/>
     </row>
-    <row r="156" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>195</v>
       </c>
@@ -3066,7 +3082,7 @@
       </c>
       <c r="D156" s="2"/>
     </row>
-    <row r="157" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>191</v>
       </c>
@@ -3078,7 +3094,7 @@
       </c>
       <c r="D157" s="3"/>
     </row>
-    <row r="158" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>191</v>
       </c>
@@ -3090,7 +3106,7 @@
       </c>
       <c r="D158" s="2"/>
     </row>
-    <row r="159" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>191</v>
       </c>
@@ -3102,7 +3118,7 @@
       </c>
       <c r="D159" s="2"/>
     </row>
-    <row r="160" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>191</v>
       </c>
@@ -3114,7 +3130,7 @@
       </c>
       <c r="D160" s="2"/>
     </row>
-    <row r="161" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>191</v>
       </c>
@@ -3126,7 +3142,7 @@
       </c>
       <c r="D161" s="2"/>
     </row>
-    <row r="162" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>191</v>
       </c>
@@ -3138,7 +3154,7 @@
       </c>
       <c r="D162" s="2"/>
     </row>
-    <row r="163" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>191</v>
       </c>
@@ -3150,7 +3166,7 @@
       </c>
       <c r="D163" s="2"/>
     </row>
-    <row r="164" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>191</v>
       </c>
@@ -3162,319 +3178,435 @@
       </c>
       <c r="D164" s="2"/>
     </row>
-    <row r="165" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+      <c r="B165" t="s">
+        <v>1</v>
+      </c>
+      <c r="C165">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C166" s="16">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B167" t="s">
-        <v>196</v>
-      </c>
-      <c r="C167" s="14">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C167">
+        <v>0.34499999999999997</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="B168" t="s">
-        <v>1</v>
-      </c>
-      <c r="C168" s="14">
-        <v>0.56000000000000005</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+      <c r="C168">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="B169" t="s">
-        <v>3</v>
-      </c>
-      <c r="C169" s="14">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="C169">
+        <v>3.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="B170" t="s">
-        <v>34</v>
-      </c>
-      <c r="C170" s="14">
-        <v>2.9999999999999805E-2</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="C170">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="B171" t="s">
-        <v>23</v>
-      </c>
-      <c r="C171" s="14">
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+      <c r="C171">
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="B172" t="s">
         <v>12</v>
       </c>
-      <c r="C172" s="14">
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C172">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="B173" t="s">
-        <v>5</v>
-      </c>
-      <c r="C173" s="14">
-        <v>0.28000000000000003</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="C173">
+        <v>1.1000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B174" t="s">
-        <v>1</v>
-      </c>
-      <c r="C174" s="14">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="C174">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B175" t="s">
-        <v>2</v>
-      </c>
-      <c r="C175" s="14">
-        <v>2.8000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="C175">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B176" t="s">
         <v>34</v>
       </c>
-      <c r="C176" s="14">
+      <c r="C176">
+        <v>0.12300000000000001</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B178" t="s">
+        <v>196</v>
+      </c>
+      <c r="C178" s="14">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B179" t="s">
+        <v>1</v>
+      </c>
+      <c r="C179" s="14">
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B180" t="s">
+        <v>3</v>
+      </c>
+      <c r="C180" s="14">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A181" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B181" t="s">
+        <v>34</v>
+      </c>
+      <c r="C181" s="14">
+        <v>2.9999999999999805E-2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B182" t="s">
+        <v>23</v>
+      </c>
+      <c r="C182" s="14">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A183" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B183" t="s">
+        <v>12</v>
+      </c>
+      <c r="C183" s="14">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A184" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B184" t="s">
+        <v>5</v>
+      </c>
+      <c r="C184" s="14">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A185" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B185" t="s">
+        <v>1</v>
+      </c>
+      <c r="C185" s="14">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A186" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B186" t="s">
+        <v>2</v>
+      </c>
+      <c r="C186" s="14">
+        <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A187" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B187" t="s">
+        <v>34</v>
+      </c>
+      <c r="C187" s="14">
         <v>5.5999999999998273E-3</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="2" t="s">
+    <row r="188" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A188" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B188" t="s">
         <v>23</v>
       </c>
-      <c r="C177" s="14">
+      <c r="C188" s="14">
         <v>0.17500000000000002</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="2" t="s">
+    <row r="189" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A189" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B189" t="s">
         <v>5</v>
       </c>
-      <c r="C178" s="14">
+      <c r="C189" s="14">
         <v>0.45140000000000002</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="2" t="s">
+    <row r="190" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A190" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B179" s="2" t="s">
+      <c r="B190" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="C179" s="14">
+      <c r="C190" s="14">
         <v>0.12</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="2" t="s">
+    <row r="191" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A191" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B180" s="2" t="s">
+      <c r="B191" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C180" s="14">
+      <c r="C191" s="14">
         <v>0.02</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="2" t="s">
+    <row r="192" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A192" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B181" s="2" t="s">
+      <c r="B192" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C181" s="14">
+      <c r="C192" s="14">
         <v>0.1474</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="2" t="s">
+    <row r="193" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A193" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B182" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C182" s="14">
+      <c r="B193" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C193" s="14">
         <v>0.2</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="2" t="s">
+    <row r="194" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A194" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B183" s="2" t="s">
+      <c r="B194" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C183" s="14">
+      <c r="C194" s="14">
         <v>3.1000000000000028E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="2" t="s">
+    <row r="195" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A195" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B184" s="2" t="s">
+      <c r="B195" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C184" s="14">
+      <c r="C195" s="14">
         <v>1.15E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="2" t="s">
+    <row r="196" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A196" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B185" s="2" t="s">
+      <c r="B196" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C185" s="14">
+      <c r="C196" s="14">
         <v>0.47010000000000002</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="2" t="s">
+    <row r="197" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A197" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B186" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C186" s="15">
+      <c r="B197" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C197" s="15">
         <v>0.1</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="2" t="s">
+    <row r="198" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A198" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B187" s="2" t="s">
+      <c r="B198" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C187" s="15">
+      <c r="C198" s="15">
         <v>0.01</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="2" t="s">
+    <row r="199" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A199" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B188" s="2" t="s">
+      <c r="B199" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C188" s="14">
+      <c r="C199" s="14">
         <v>9.2999999999999972E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="2" t="s">
+    <row r="200" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A200" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B189" s="2" t="s">
+      <c r="B200" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C189" s="15">
+      <c r="C200" s="15">
         <v>0.20300000000000001</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="2" t="s">
+    <row r="201" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A201" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B190" s="2" t="s">
+      <c r="B201" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C190" s="15">
+      <c r="C201" s="15">
         <f>0.2+0.015</f>
         <v>0.21500000000000002</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="2" t="s">
+    <row r="202" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A202" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B191" s="2" t="s">
+      <c r="B202" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C191" s="15">
+      <c r="C202" s="15">
         <v>0.06</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="2" t="s">
+    <row r="203" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A203" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B192" s="2" t="s">
+      <c r="B203" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C192" s="15">
+      <c r="C203" s="15">
         <v>0.31900000000000001</v>
       </c>
     </row>
-    <row r="193" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="1:3" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="1:3" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="1:3" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="1:3" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="1:3" ht="13.2" x14ac:dyDescent="0.25"/>
     <row r="209" ht="13.2" x14ac:dyDescent="0.25"/>
     <row r="210" ht="13.2" x14ac:dyDescent="0.25"/>
     <row r="211" ht="13.2" x14ac:dyDescent="0.25"/>
@@ -4364,15 +4496,21 @@
     <row r="1095" ht="13.2" x14ac:dyDescent="0.25"/>
     <row r="1096" ht="13.2" x14ac:dyDescent="0.25"/>
     <row r="1097" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1098" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1099" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1100" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1101" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1102" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1103" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1104" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1105" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1106" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1107" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="1108" ht="13.2" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:D192" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="asian_seabass-china"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A167:D192">
-      <sortCondition ref="A1:A192"/>
+  <autoFilter ref="A1:D203" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A178:D203">
+      <sortCondition ref="A1:A203"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -4386,6 +4524,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A162FC-7907-44C7-A909-E8E1323EC5F6}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G300"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4422,7 +4561,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>199</v>
       </c>
@@ -4443,7 +4582,7 @@
       </c>
       <c r="G2" s="8"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>199</v>
       </c>
@@ -4462,7 +4601,7 @@
       </c>
       <c r="G3" s="8"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>199</v>
       </c>
@@ -4481,7 +4620,7 @@
       </c>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>199</v>
       </c>
@@ -4500,7 +4639,7 @@
       </c>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>128</v>
       </c>
@@ -4517,11 +4656,11 @@
         <v>176</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>128</v>
       </c>
@@ -4536,11 +4675,11 @@
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>128</v>
       </c>
@@ -4555,11 +4694,11 @@
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>128</v>
       </c>
@@ -4580,7 +4719,7 @@
       </c>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>128</v>
       </c>
@@ -4601,7 +4740,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>128</v>
       </c>
@@ -4622,7 +4761,7 @@
       </c>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>128</v>
       </c>
@@ -4641,7 +4780,7 @@
       </c>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>128</v>
       </c>
@@ -4660,7 +4799,7 @@
       </c>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>128</v>
       </c>
@@ -4679,7 +4818,7 @@
       </c>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>128</v>
       </c>
@@ -4698,7 +4837,7 @@
       </c>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>128</v>
       </c>
@@ -4719,7 +4858,7 @@
       </c>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>128</v>
       </c>
@@ -4738,7 +4877,7 @@
       </c>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>128</v>
       </c>
@@ -4757,7 +4896,7 @@
       </c>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>128</v>
       </c>
@@ -4776,7 +4915,7 @@
       </c>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>128</v>
       </c>
@@ -5185,7 +5324,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
     </row>
-    <row r="47" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>118</v>
       </c>
@@ -5202,11 +5341,11 @@
         <v>197</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G47" s="8"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>118</v>
       </c>
@@ -5221,11 +5360,11 @@
       </c>
       <c r="E48" s="11"/>
       <c r="F48" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G48" s="8"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
         <v>118</v>
       </c>
@@ -5240,11 +5379,11 @@
       </c>
       <c r="E49" s="11"/>
       <c r="F49" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G49" s="8"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
         <v>118</v>
       </c>
@@ -5259,11 +5398,11 @@
       </c>
       <c r="E50" s="11"/>
       <c r="F50" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G50" s="8"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
         <v>118</v>
       </c>
@@ -5278,11 +5417,11 @@
       </c>
       <c r="E51" s="11"/>
       <c r="F51" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G51" s="8"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
         <v>118</v>
       </c>
@@ -5297,11 +5436,11 @@
       </c>
       <c r="E52" s="11"/>
       <c r="F52" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G52" s="8"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
         <v>118</v>
       </c>
@@ -5316,11 +5455,11 @@
       </c>
       <c r="E53" s="11"/>
       <c r="F53" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G53" s="8"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
         <v>118</v>
       </c>
@@ -5335,11 +5474,11 @@
       </c>
       <c r="E54" s="11"/>
       <c r="F54" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G54" s="8"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
         <v>118</v>
       </c>
@@ -5354,11 +5493,11 @@
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G55" s="8"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>118</v>
       </c>
@@ -5373,11 +5512,11 @@
       </c>
       <c r="E56" s="11"/>
       <c r="F56" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G56" s="8"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
         <v>118</v>
       </c>
@@ -5392,11 +5531,11 @@
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
         <v>118</v>
       </c>
@@ -5411,11 +5550,11 @@
       </c>
       <c r="E58" s="11"/>
       <c r="F58" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
         <v>118</v>
       </c>
@@ -5430,11 +5569,11 @@
       </c>
       <c r="E59" s="11"/>
       <c r="F59" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G59" s="8"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
         <v>118</v>
       </c>
@@ -5449,11 +5588,11 @@
       </c>
       <c r="E60" s="11"/>
       <c r="F60" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G60" s="8"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
         <v>118</v>
       </c>
@@ -5468,11 +5607,11 @@
       </c>
       <c r="E61" s="11"/>
       <c r="F61" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G61" s="8"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
         <v>118</v>
       </c>
@@ -5487,11 +5626,11 @@
       </c>
       <c r="E62" s="11"/>
       <c r="F62" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G62" s="8"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
         <v>118</v>
       </c>
@@ -5506,11 +5645,11 @@
       </c>
       <c r="E63" s="11"/>
       <c r="F63" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G63" s="8"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
         <v>118</v>
       </c>
@@ -5525,11 +5664,11 @@
       </c>
       <c r="E64" s="11"/>
       <c r="F64" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G64" s="8"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>118</v>
       </c>
@@ -5544,11 +5683,11 @@
       </c>
       <c r="E65" s="11"/>
       <c r="F65" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G65" s="8"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
         <v>118</v>
       </c>
@@ -5563,11 +5702,11 @@
       </c>
       <c r="E66" s="11"/>
       <c r="F66" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G66" s="8"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
         <v>118</v>
       </c>
@@ -5582,11 +5721,11 @@
       </c>
       <c r="E67" s="11"/>
       <c r="F67" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G67" s="8"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
         <v>118</v>
       </c>
@@ -5601,11 +5740,11 @@
       </c>
       <c r="E68" s="11"/>
       <c r="F68" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G68" s="8"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
         <v>118</v>
       </c>
@@ -5620,7 +5759,7 @@
       </c>
       <c r="E69" s="11"/>
       <c r="F69" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G69" s="8"/>
     </row>
@@ -7058,7 +7197,7 @@
       <c r="F161" s="8"/>
       <c r="G161" s="8"/>
     </row>
-    <row r="162" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="8" t="s">
         <v>93</v>
       </c>
@@ -7079,7 +7218,7 @@
       </c>
       <c r="G162" s="8"/>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
         <v>93</v>
       </c>
@@ -7097,7 +7236,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="8" t="s">
         <v>93</v>
       </c>
@@ -7116,7 +7255,7 @@
       </c>
       <c r="G164" s="8"/>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
         <v>93</v>
       </c>
@@ -7135,7 +7274,7 @@
       </c>
       <c r="G165" s="8"/>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="8" t="s">
         <v>93</v>
       </c>
@@ -7154,7 +7293,7 @@
       </c>
       <c r="G166" s="8"/>
     </row>
-    <row r="167" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
         <v>93</v>
       </c>
@@ -7175,7 +7314,7 @@
       </c>
       <c r="G167" s="8"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="8" t="s">
         <v>93</v>
       </c>
@@ -7194,7 +7333,7 @@
       </c>
       <c r="G168" s="8"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
         <v>93</v>
       </c>
@@ -7213,7 +7352,7 @@
       </c>
       <c r="G169" s="8"/>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
         <v>93</v>
       </c>
@@ -7232,7 +7371,7 @@
       </c>
       <c r="G170" s="8"/>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
         <v>93</v>
       </c>
@@ -7251,7 +7390,7 @@
       </c>
       <c r="G171" s="8"/>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="8" t="s">
         <v>93</v>
       </c>
@@ -7270,7 +7409,7 @@
       </c>
       <c r="G172" s="8"/>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
         <v>93</v>
       </c>
@@ -7289,7 +7428,7 @@
       </c>
       <c r="G173" s="8"/>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="8" t="s">
         <v>93</v>
       </c>
@@ -7308,7 +7447,7 @@
       </c>
       <c r="G174" s="8"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
         <v>93</v>
       </c>
@@ -7327,7 +7466,7 @@
       </c>
       <c r="G175" s="8"/>
     </row>
-    <row r="176" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="8" t="s">
         <v>93</v>
       </c>
@@ -7348,7 +7487,7 @@
       </c>
       <c r="G176" s="8"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
         <v>93</v>
       </c>
@@ -7367,7 +7506,7 @@
       </c>
       <c r="G177" s="8"/>
     </row>
-    <row r="178" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="8" t="s">
         <v>82</v>
       </c>
@@ -7388,7 +7527,7 @@
       </c>
       <c r="G178" s="8"/>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
         <v>82</v>
       </c>
@@ -7407,7 +7546,7 @@
       </c>
       <c r="G179" s="8"/>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="8" t="s">
         <v>82</v>
       </c>
@@ -7426,7 +7565,7 @@
       </c>
       <c r="G180" s="8"/>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
         <v>82</v>
       </c>
@@ -7445,7 +7584,7 @@
       </c>
       <c r="G181" s="8"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="8" t="s">
         <v>82</v>
       </c>
@@ -7464,7 +7603,7 @@
       </c>
       <c r="G182" s="8"/>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
         <v>82</v>
       </c>
@@ -7483,7 +7622,7 @@
       </c>
       <c r="G183" s="8"/>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="8" t="s">
         <v>82</v>
       </c>
@@ -7502,7 +7641,7 @@
       </c>
       <c r="G184" s="8"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
         <v>82</v>
       </c>
@@ -7521,7 +7660,7 @@
       </c>
       <c r="G185" s="8"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="8" t="s">
         <v>82</v>
       </c>
@@ -7540,7 +7679,7 @@
       </c>
       <c r="G186" s="8"/>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
         <v>82</v>
       </c>
@@ -7559,7 +7698,7 @@
       </c>
       <c r="G187" s="8"/>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="8" t="s">
         <v>82</v>
       </c>
@@ -7578,7 +7717,7 @@
       </c>
       <c r="G188" s="8"/>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
         <v>82</v>
       </c>
@@ -7597,7 +7736,7 @@
       </c>
       <c r="G189" s="8"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="8" t="s">
         <v>82</v>
       </c>
@@ -7616,7 +7755,7 @@
       </c>
       <c r="G190" s="8"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
         <v>82</v>
       </c>
@@ -7635,7 +7774,7 @@
       </c>
       <c r="G191" s="8"/>
     </row>
-    <row r="192" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
         <v>82</v>
       </c>
@@ -7656,7 +7795,7 @@
       </c>
       <c r="G192" s="8"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
         <v>82</v>
       </c>
@@ -7675,7 +7814,7 @@
       </c>
       <c r="G193" s="8"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="8" t="s">
         <v>82</v>
       </c>
@@ -7694,7 +7833,7 @@
       </c>
       <c r="G194" s="8"/>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
         <v>82</v>
       </c>
@@ -7713,7 +7852,7 @@
       </c>
       <c r="G195" s="8"/>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="8" t="s">
         <v>82</v>
       </c>
@@ -7732,7 +7871,7 @@
       </c>
       <c r="G196" s="8"/>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
         <v>82</v>
       </c>
@@ -7751,7 +7890,7 @@
       </c>
       <c r="G197" s="8"/>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="8" t="s">
         <v>82</v>
       </c>
@@ -7770,7 +7909,7 @@
       </c>
       <c r="G198" s="8"/>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
         <v>82</v>
       </c>
@@ -7789,7 +7928,7 @@
       </c>
       <c r="G199" s="8"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="8" t="s">
         <v>82</v>
       </c>
@@ -7808,7 +7947,7 @@
       </c>
       <c r="G200" s="8"/>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
         <v>82</v>
       </c>
@@ -7827,7 +7966,7 @@
       </c>
       <c r="G201" s="8"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="8" t="s">
         <v>82</v>
       </c>
@@ -7846,7 +7985,7 @@
       </c>
       <c r="G202" s="8"/>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
         <v>82</v>
       </c>
@@ -7865,7 +8004,7 @@
       </c>
       <c r="G203" s="8"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="8" t="s">
         <v>82</v>
       </c>
@@ -7884,7 +8023,7 @@
       </c>
       <c r="G204" s="8"/>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
         <v>82</v>
       </c>
@@ -7903,7 +8042,7 @@
       </c>
       <c r="G205" s="8"/>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="8" t="s">
         <v>82</v>
       </c>
@@ -7922,7 +8061,7 @@
       </c>
       <c r="G206" s="8"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
         <v>82</v>
       </c>
@@ -7941,7 +8080,7 @@
       </c>
       <c r="G207" s="8"/>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="8" t="s">
         <v>82</v>
       </c>
@@ -7960,7 +8099,7 @@
       </c>
       <c r="G208" s="8"/>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
         <v>82</v>
       </c>
@@ -7989,8 +8128,12 @@
       <c r="C210" s="8">
         <v>542</v>
       </c>
-      <c r="D210" s="8"/>
-      <c r="E210" s="9"/>
+      <c r="D210" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E210" s="9" t="s">
+        <v>230</v>
+      </c>
       <c r="F210" s="8"/>
       <c r="G210" s="8"/>
     </row>
@@ -8004,8 +8147,10 @@
       <c r="C211" s="8">
         <v>418</v>
       </c>
-      <c r="D211" s="8"/>
-      <c r="E211" s="9"/>
+      <c r="D211" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E211" s="11"/>
       <c r="F211" s="8"/>
       <c r="G211" s="8"/>
     </row>
@@ -8019,8 +8164,10 @@
       <c r="C212" s="8">
         <v>292</v>
       </c>
-      <c r="D212" s="8"/>
-      <c r="E212" s="9"/>
+      <c r="D212" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E212" s="11"/>
       <c r="F212" s="8"/>
       <c r="G212" s="8"/>
     </row>
@@ -8034,8 +8181,10 @@
       <c r="C213" s="8">
         <v>203</v>
       </c>
-      <c r="D213" s="8"/>
-      <c r="E213" s="9"/>
+      <c r="D213" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E213" s="11"/>
       <c r="F213" s="8"/>
       <c r="G213" s="8"/>
     </row>
@@ -8049,8 +8198,10 @@
       <c r="C214" s="8">
         <v>151</v>
       </c>
-      <c r="D214" s="8"/>
-      <c r="E214" s="9"/>
+      <c r="D214" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E214" s="11"/>
       <c r="F214" s="8"/>
       <c r="G214" s="8"/>
     </row>
@@ -8064,8 +8215,10 @@
       <c r="C215" s="8">
         <v>116</v>
       </c>
-      <c r="D215" s="8"/>
-      <c r="E215" s="9"/>
+      <c r="D215" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E215" s="11"/>
       <c r="F215" s="8"/>
       <c r="G215" s="8"/>
     </row>
@@ -8079,8 +8232,10 @@
       <c r="C216" s="8">
         <v>96</v>
       </c>
-      <c r="D216" s="8"/>
-      <c r="E216" s="9"/>
+      <c r="D216" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E216" s="11"/>
       <c r="F216" s="8"/>
       <c r="G216" s="8"/>
     </row>
@@ -8094,8 +8249,10 @@
       <c r="C217" s="8">
         <v>54</v>
       </c>
-      <c r="D217" s="8"/>
-      <c r="E217" s="9"/>
+      <c r="D217" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E217" s="11"/>
       <c r="F217" s="8"/>
       <c r="G217" s="8"/>
     </row>
@@ -8109,8 +8266,10 @@
       <c r="C218" s="8">
         <v>51</v>
       </c>
-      <c r="D218" s="8"/>
-      <c r="E218" s="9"/>
+      <c r="D218" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E218" s="11"/>
       <c r="F218" s="8"/>
       <c r="G218" s="8"/>
     </row>
@@ -8124,8 +8283,10 @@
       <c r="C219" s="8">
         <v>23</v>
       </c>
-      <c r="D219" s="8"/>
-      <c r="E219" s="9"/>
+      <c r="D219" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E219" s="11"/>
       <c r="F219" s="8"/>
       <c r="G219" s="8"/>
     </row>
@@ -8139,8 +8300,10 @@
       <c r="C220" s="8">
         <v>6</v>
       </c>
-      <c r="D220" s="8"/>
-      <c r="E220" s="9"/>
+      <c r="D220" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E220" s="11"/>
       <c r="F220" s="8"/>
       <c r="G220" s="8"/>
     </row>
@@ -8154,8 +8317,10 @@
       <c r="C221" s="8">
         <v>2</v>
       </c>
-      <c r="D221" s="8"/>
-      <c r="E221" s="9"/>
+      <c r="D221" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E221" s="11"/>
       <c r="F221" s="8"/>
       <c r="G221" s="8"/>
     </row>
@@ -8169,8 +8334,10 @@
       <c r="C222" s="8">
         <v>1</v>
       </c>
-      <c r="D222" s="8"/>
-      <c r="E222" s="9"/>
+      <c r="D222" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E222" s="11"/>
       <c r="F222" s="8"/>
       <c r="G222" s="8"/>
     </row>
@@ -8184,8 +8351,10 @@
       <c r="C223" s="8">
         <v>1</v>
       </c>
-      <c r="D223" s="8"/>
-      <c r="E223" s="9"/>
+      <c r="D223" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E223" s="11"/>
       <c r="F223" s="8"/>
       <c r="G223" s="8"/>
     </row>
@@ -8199,8 +8368,10 @@
       <c r="C224" s="8">
         <v>1</v>
       </c>
-      <c r="D224" s="8"/>
-      <c r="E224" s="9"/>
+      <c r="D224" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E224" s="11"/>
       <c r="F224" s="8"/>
       <c r="G224" s="8"/>
     </row>
@@ -8214,8 +8385,10 @@
       <c r="C225" s="8">
         <v>1</v>
       </c>
-      <c r="D225" s="8"/>
-      <c r="E225" s="9"/>
+      <c r="D225" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E225" s="11"/>
       <c r="F225" s="8"/>
       <c r="G225" s="8"/>
     </row>
@@ -8229,8 +8402,10 @@
       <c r="C226" s="8">
         <v>1</v>
       </c>
-      <c r="D226" s="8"/>
-      <c r="E226" s="9"/>
+      <c r="D226" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E226" s="11"/>
       <c r="F226" s="8"/>
       <c r="G226" s="8"/>
     </row>
@@ -8244,8 +8419,10 @@
       <c r="C227" s="8">
         <v>1</v>
       </c>
-      <c r="D227" s="8"/>
-      <c r="E227" s="9"/>
+      <c r="D227" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E227" s="11"/>
       <c r="F227" s="8"/>
       <c r="G227" s="8"/>
     </row>
@@ -8259,8 +8436,10 @@
       <c r="C228" s="8">
         <v>1</v>
       </c>
-      <c r="D228" s="8"/>
-      <c r="E228" s="9"/>
+      <c r="D228" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E228" s="11"/>
       <c r="F228" s="8"/>
       <c r="G228" s="8"/>
     </row>
@@ -8274,8 +8453,10 @@
       <c r="C229" s="8">
         <v>1</v>
       </c>
-      <c r="D229" s="8"/>
-      <c r="E229" s="9"/>
+      <c r="D229" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E229" s="11"/>
       <c r="F229" s="8"/>
       <c r="G229" s="8"/>
     </row>
@@ -8445,7 +8626,9 @@
       <c r="E240" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="F240" s="8"/>
+      <c r="F240" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G240" s="8"/>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -8462,7 +8645,9 @@
         <v>193</v>
       </c>
       <c r="E241" s="11"/>
-      <c r="F241" s="8"/>
+      <c r="F241" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G241" s="8"/>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -8479,7 +8664,9 @@
         <v>193</v>
       </c>
       <c r="E242" s="11"/>
-      <c r="F242" s="8"/>
+      <c r="F242" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G242" s="8"/>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -8496,7 +8683,9 @@
         <v>193</v>
       </c>
       <c r="E243" s="11"/>
-      <c r="F243" s="8"/>
+      <c r="F243" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G243" s="8"/>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -8513,7 +8702,9 @@
         <v>193</v>
       </c>
       <c r="E244" s="11"/>
-      <c r="F244" s="8"/>
+      <c r="F244" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G244" s="8"/>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -8530,7 +8721,9 @@
         <v>193</v>
       </c>
       <c r="E245" s="11"/>
-      <c r="F245" s="8"/>
+      <c r="F245" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G245" s="8"/>
     </row>
     <row r="246" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
@@ -8549,7 +8742,9 @@
       <c r="E246" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="F246" s="8"/>
+      <c r="F246" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G246" s="8"/>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -8566,7 +8761,9 @@
         <v>213</v>
       </c>
       <c r="E247" s="11"/>
-      <c r="F247" s="8"/>
+      <c r="F247" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G247" s="8"/>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -8583,7 +8780,9 @@
         <v>213</v>
       </c>
       <c r="E248" s="11"/>
-      <c r="F248" s="8"/>
+      <c r="F248" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G248" s="8"/>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -8600,7 +8799,9 @@
         <v>213</v>
       </c>
       <c r="E249" s="11"/>
-      <c r="F249" s="8"/>
+      <c r="F249" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G249" s="8"/>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -8617,7 +8818,9 @@
         <v>213</v>
       </c>
       <c r="E250" s="11"/>
-      <c r="F250" s="8"/>
+      <c r="F250" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G250" s="8"/>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -8634,7 +8837,9 @@
         <v>213</v>
       </c>
       <c r="E251" s="11"/>
-      <c r="F251" s="8"/>
+      <c r="F251" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G251" s="8"/>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -8651,7 +8856,9 @@
         <v>213</v>
       </c>
       <c r="E252" s="11"/>
-      <c r="F252" s="8"/>
+      <c r="F252" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G252" s="8"/>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
@@ -8668,7 +8875,9 @@
         <v>213</v>
       </c>
       <c r="E253" s="11"/>
-      <c r="F253" s="8"/>
+      <c r="F253" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G253" s="8"/>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -8685,7 +8894,9 @@
         <v>213</v>
       </c>
       <c r="E254" s="11"/>
-      <c r="F254" s="8"/>
+      <c r="F254" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G254" s="8"/>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -8702,7 +8913,9 @@
         <v>213</v>
       </c>
       <c r="E255" s="11"/>
-      <c r="F255" s="8"/>
+      <c r="F255" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G255" s="8"/>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -8719,7 +8932,9 @@
         <v>213</v>
       </c>
       <c r="E256" s="11"/>
-      <c r="F256" s="8"/>
+      <c r="F256" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G256" s="8"/>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -8736,7 +8951,9 @@
         <v>213</v>
       </c>
       <c r="E257" s="11"/>
-      <c r="F257" s="8"/>
+      <c r="F257" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G257" s="8"/>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -8753,7 +8970,9 @@
         <v>213</v>
       </c>
       <c r="E258" s="11"/>
-      <c r="F258" s="8"/>
+      <c r="F258" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G258" s="8"/>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -8770,7 +8989,9 @@
         <v>213</v>
       </c>
       <c r="E259" s="11"/>
-      <c r="F259" s="8"/>
+      <c r="F259" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G259" s="8"/>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -8787,7 +9008,9 @@
         <v>213</v>
       </c>
       <c r="E260" s="11"/>
-      <c r="F260" s="8"/>
+      <c r="F260" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G260" s="8"/>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -8804,7 +9027,9 @@
         <v>213</v>
       </c>
       <c r="E261" s="11"/>
-      <c r="F261" s="8"/>
+      <c r="F261" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G261" s="8"/>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -8821,7 +9046,9 @@
         <v>213</v>
       </c>
       <c r="E262" s="11"/>
-      <c r="F262" s="8"/>
+      <c r="F262" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G262" s="8"/>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -8838,7 +9065,9 @@
         <v>213</v>
       </c>
       <c r="E263" s="11"/>
-      <c r="F263" s="8"/>
+      <c r="F263" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G263" s="8"/>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -8855,7 +9084,9 @@
         <v>213</v>
       </c>
       <c r="E264" s="11"/>
-      <c r="F264" s="8"/>
+      <c r="F264" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G264" s="8"/>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -8872,7 +9103,9 @@
         <v>213</v>
       </c>
       <c r="E265" s="11"/>
-      <c r="F265" s="8"/>
+      <c r="F265" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G265" s="8"/>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -8889,7 +9122,9 @@
         <v>213</v>
       </c>
       <c r="E266" s="11"/>
-      <c r="F266" s="8"/>
+      <c r="F266" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G266" s="8"/>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
@@ -8906,7 +9141,9 @@
         <v>213</v>
       </c>
       <c r="E267" s="11"/>
-      <c r="F267" s="8"/>
+      <c r="F267" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G267" s="8"/>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
@@ -8923,7 +9160,9 @@
         <v>213</v>
       </c>
       <c r="E268" s="11"/>
-      <c r="F268" s="8"/>
+      <c r="F268" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G268" s="8"/>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
@@ -8940,7 +9179,9 @@
         <v>213</v>
       </c>
       <c r="E269" s="11"/>
-      <c r="F269" s="8"/>
+      <c r="F269" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G269" s="8"/>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
@@ -8957,7 +9198,9 @@
         <v>213</v>
       </c>
       <c r="E270" s="11"/>
-      <c r="F270" s="8"/>
+      <c r="F270" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G270" s="8"/>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
@@ -8974,7 +9217,9 @@
         <v>213</v>
       </c>
       <c r="E271" s="11"/>
-      <c r="F271" s="8"/>
+      <c r="F271" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G271" s="8"/>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
@@ -8991,7 +9236,9 @@
         <v>213</v>
       </c>
       <c r="E272" s="11"/>
-      <c r="F272" s="8"/>
+      <c r="F272" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G272" s="8"/>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
@@ -9008,7 +9255,9 @@
         <v>213</v>
       </c>
       <c r="E273" s="11"/>
-      <c r="F273" s="8"/>
+      <c r="F273" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G273" s="8"/>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
@@ -9025,7 +9274,9 @@
         <v>213</v>
       </c>
       <c r="E274" s="11"/>
-      <c r="F274" s="8"/>
+      <c r="F274" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G274" s="8"/>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
@@ -9042,7 +9293,9 @@
         <v>213</v>
       </c>
       <c r="E275" s="11"/>
-      <c r="F275" s="8"/>
+      <c r="F275" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G275" s="8"/>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
@@ -9059,7 +9312,9 @@
         <v>213</v>
       </c>
       <c r="E276" s="11"/>
-      <c r="F276" s="8"/>
+      <c r="F276" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G276" s="8"/>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -9076,7 +9331,9 @@
         <v>213</v>
       </c>
       <c r="E277" s="11"/>
-      <c r="F277" s="8"/>
+      <c r="F277" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G277" s="8"/>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
@@ -9093,7 +9350,9 @@
         <v>213</v>
       </c>
       <c r="E278" s="11"/>
-      <c r="F278" s="8"/>
+      <c r="F278" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G278" s="8"/>
     </row>
     <row r="279" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
@@ -9476,6 +9735,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G300" xr:uid="{38A162FC-7907-44C7-A909-E8E1323EC5F6}">
+    <filterColumn colId="5">
+      <filters blank="1">
+        <filter val="wip"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A240:G300">
       <sortCondition ref="D1:D300"/>
     </sortState>

--- a/data/raw_data/feed_profiles_and_composition.xlsx
+++ b/data/raw_data/feed_profiles_and_composition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\treimer\Documents\R-temp-files\climate_risks_to_fed_mariculture\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF71AC50-7D01-4194-A1A2-0775340BA8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E13F016-EC12-4786-9358-1FDC0E0C4528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9480" yWindow="2604" windowWidth="23016" windowHeight="13656" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="feed_formulations" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="233">
   <si>
     <t>ingredient</t>
   </si>
@@ -1163,18 +1163,18 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:N1108"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="118.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.21875" customWidth="1"/>
-    <col min="6" max="6" width="12.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="118.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>31</v>
       </c>
@@ -1198,7 +1198,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>200</v>
       </c>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>200</v>
       </c>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>200</v>
       </c>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>200</v>
       </c>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>200</v>
       </c>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>200</v>
       </c>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>49</v>
       </c>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>49</v>
       </c>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>49</v>
       </c>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>49</v>
       </c>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>49</v>
       </c>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>49</v>
       </c>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>49</v>
       </c>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>49</v>
       </c>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>49</v>
       </c>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>49</v>
       </c>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>49</v>
       </c>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>49</v>
       </c>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>49</v>
       </c>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>44</v>
       </c>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>44</v>
       </c>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>44</v>
       </c>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>44</v>
       </c>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D25" s="2"/>
     </row>
-    <row r="26" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>44</v>
       </c>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>44</v>
       </c>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D27" s="2"/>
     </row>
-    <row r="28" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>44</v>
       </c>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D29" s="2"/>
     </row>
-    <row r="30" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>44</v>
       </c>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>44</v>
       </c>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="D31" s="2"/>
     </row>
-    <row r="32" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>44</v>
       </c>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>44</v>
       </c>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="D33" s="2"/>
     </row>
-    <row r="34" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>44</v>
       </c>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>44</v>
       </c>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D35" s="2"/>
     </row>
-    <row r="36" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>43</v>
       </c>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>43</v>
       </c>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="D37" s="2"/>
     </row>
-    <row r="38" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>43</v>
       </c>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>43</v>
       </c>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="D39" s="2"/>
     </row>
-    <row r="40" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>43</v>
       </c>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="D40" s="2"/>
     </row>
-    <row r="41" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>43</v>
       </c>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="D41" s="2"/>
     </row>
-    <row r="42" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>43</v>
       </c>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D42" s="2"/>
     </row>
-    <row r="43" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>43</v>
       </c>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="D43" s="2"/>
     </row>
-    <row r="44" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>43</v>
       </c>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>43</v>
       </c>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>43</v>
       </c>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>43</v>
       </c>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D47" s="2"/>
     </row>
-    <row r="48" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>43</v>
       </c>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>43</v>
       </c>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="D49" s="2"/>
     </row>
-    <row r="50" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>43</v>
       </c>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>43</v>
       </c>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D51" s="2"/>
     </row>
-    <row r="52" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>43</v>
       </c>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>48</v>
       </c>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="D53" s="2"/>
     </row>
-    <row r="54" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>48</v>
       </c>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>48</v>
       </c>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D55" s="2"/>
     </row>
-    <row r="56" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>48</v>
       </c>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="D56" s="2"/>
     </row>
-    <row r="57" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>48</v>
       </c>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="D57" s="2"/>
     </row>
-    <row r="58" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>48</v>
       </c>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="D58" s="2"/>
     </row>
-    <row r="59" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>48</v>
       </c>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="D59" s="2"/>
     </row>
-    <row r="60" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>48</v>
       </c>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="D60" s="2"/>
     </row>
-    <row r="61" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>48</v>
       </c>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D61" s="2"/>
     </row>
-    <row r="62" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>48</v>
       </c>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="D62" s="2"/>
     </row>
-    <row r="63" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>48</v>
       </c>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D63" s="2"/>
     </row>
-    <row r="64" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>48</v>
       </c>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="D64" s="2"/>
     </row>
-    <row r="65" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>198</v>
       </c>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="D65" s="2"/>
     </row>
-    <row r="66" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>198</v>
       </c>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D66" s="2"/>
     </row>
-    <row r="67" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>198</v>
       </c>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="D67" s="3"/>
     </row>
-    <row r="68" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>198</v>
       </c>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="D68" s="2"/>
     </row>
-    <row r="69" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>198</v>
       </c>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="D69" s="2"/>
     </row>
-    <row r="70" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>198</v>
       </c>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D70" s="2"/>
     </row>
-    <row r="71" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>198</v>
       </c>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="D71" s="2"/>
     </row>
-    <row r="72" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>198</v>
       </c>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="D72" s="2"/>
     </row>
-    <row r="73" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>198</v>
       </c>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="D73" s="2"/>
     </row>
-    <row r="74" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>198</v>
       </c>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D74" s="2"/>
     </row>
-    <row r="75" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>198</v>
       </c>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D75" s="2"/>
     </row>
-    <row r="76" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>198</v>
       </c>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="D76" s="2"/>
     </row>
-    <row r="77" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>210</v>
       </c>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="D77" s="3"/>
     </row>
-    <row r="78" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>210</v>
       </c>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="D78" s="3"/>
     </row>
-    <row r="79" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>210</v>
       </c>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="D79" s="3"/>
     </row>
-    <row r="80" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>210</v>
       </c>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="D80" s="3"/>
     </row>
-    <row r="81" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>210</v>
       </c>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="D81" s="3"/>
     </row>
-    <row r="82" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>210</v>
       </c>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D82" s="3"/>
     </row>
-    <row r="83" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>210</v>
       </c>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="D83" s="3"/>
     </row>
-    <row r="84" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>210</v>
       </c>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="D84" s="3"/>
     </row>
-    <row r="85" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>210</v>
       </c>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D85" s="3"/>
     </row>
-    <row r="86" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>210</v>
       </c>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D86" s="3"/>
     </row>
-    <row r="87" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>210</v>
       </c>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="D87" s="3"/>
     </row>
-    <row r="88" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>30</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>33</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>33</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>33</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>33</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>33</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>33</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>29</v>
       </c>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="D95" s="2"/>
     </row>
-    <row r="96" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>203</v>
       </c>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="D96" s="3"/>
     </row>
-    <row r="97" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>203</v>
       </c>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="D97" s="3"/>
     </row>
-    <row r="98" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>203</v>
       </c>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D98" s="3"/>
     </row>
-    <row r="99" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>203</v>
       </c>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D99" s="3"/>
     </row>
-    <row r="100" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>203</v>
       </c>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D100" s="3"/>
     </row>
-    <row r="101" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>203</v>
       </c>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="D101" s="3"/>
     </row>
-    <row r="102" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>203</v>
       </c>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="D102" s="3"/>
     </row>
-    <row r="103" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>203</v>
       </c>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="D103" s="3"/>
     </row>
-    <row r="104" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>203</v>
       </c>
@@ -2454,22 +2454,22 @@
       </c>
       <c r="D104" s="3"/>
     </row>
-    <row r="105" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>181</v>
       </c>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D108" s="3"/>
     </row>
-    <row r="109" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
         <v>181</v>
       </c>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="D109" s="3"/>
     </row>
-    <row r="110" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
         <v>181</v>
       </c>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="D110" s="3"/>
     </row>
-    <row r="111" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
         <v>181</v>
       </c>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="D111" s="3"/>
     </row>
-    <row r="112" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
         <v>181</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
         <v>181</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>181</v>
       </c>
@@ -2562,7 +2562,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>181</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>181</v>
       </c>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="D116" s="3"/>
     </row>
-    <row r="117" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
         <v>181</v>
       </c>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="D117" s="3"/>
     </row>
-    <row r="118" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>181</v>
       </c>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="D118" s="3"/>
     </row>
-    <row r="119" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>181</v>
       </c>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="D119" s="3"/>
     </row>
-    <row r="120" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>181</v>
       </c>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="D120" s="3"/>
     </row>
-    <row r="121" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
         <v>181</v>
       </c>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="D121" s="3"/>
     </row>
-    <row r="122" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
         <v>179</v>
       </c>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="D122" s="3"/>
     </row>
-    <row r="123" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
         <v>179</v>
       </c>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D123" s="3"/>
     </row>
-    <row r="124" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>179</v>
       </c>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D124" s="3"/>
     </row>
-    <row r="125" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
         <v>179</v>
       </c>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="D125" s="3"/>
     </row>
-    <row r="126" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
         <v>179</v>
       </c>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="D126" s="3"/>
     </row>
-    <row r="127" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
         <v>179</v>
       </c>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="D127" s="3"/>
     </row>
-    <row r="128" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
         <v>179</v>
       </c>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="D128" s="3"/>
     </row>
-    <row r="129" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
         <v>179</v>
       </c>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="D129" s="3"/>
     </row>
-    <row r="130" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
         <v>179</v>
       </c>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="D130" s="3"/>
     </row>
-    <row r="131" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
         <v>179</v>
       </c>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D131" s="3"/>
     </row>
-    <row r="132" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
         <v>179</v>
       </c>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D132" s="3"/>
     </row>
-    <row r="133" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
         <v>179</v>
       </c>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="D133" s="3"/>
     </row>
-    <row r="134" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>179</v>
       </c>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="D134" s="3"/>
     </row>
-    <row r="135" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
         <v>179</v>
       </c>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="D135" s="3"/>
     </row>
-    <row r="136" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
         <v>179</v>
       </c>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D136" s="3"/>
     </row>
-    <row r="137" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
         <v>179</v>
       </c>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="D137" s="3"/>
     </row>
-    <row r="138" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
         <v>182</v>
       </c>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="D138" s="3"/>
     </row>
-    <row r="139" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
         <v>182</v>
       </c>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="D139" s="3"/>
     </row>
-    <row r="140" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>182</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
         <v>182</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
         <v>182</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
         <v>182</v>
       </c>
@@ -2925,7 +2925,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
         <v>182</v>
       </c>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="D144" s="3"/>
     </row>
-    <row r="145" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
         <v>182</v>
       </c>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="D145" s="3"/>
     </row>
-    <row r="146" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
         <v>182</v>
       </c>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="D146" s="3"/>
     </row>
-    <row r="147" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
         <v>182</v>
       </c>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="D147" s="3"/>
     </row>
-    <row r="148" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
         <v>182</v>
       </c>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="D148" s="3"/>
     </row>
-    <row r="149" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
         <v>182</v>
       </c>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="D149" s="3"/>
     </row>
-    <row r="150" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
         <v>195</v>
       </c>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="D150" s="2"/>
     </row>
-    <row r="151" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
         <v>195</v>
       </c>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="D151" s="2"/>
     </row>
-    <row r="152" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
         <v>195</v>
       </c>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="D152" s="2"/>
     </row>
-    <row r="153" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
         <v>195</v>
       </c>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D153" s="2"/>
     </row>
-    <row r="154" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
         <v>195</v>
       </c>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="D154" s="2"/>
     </row>
-    <row r="155" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
         <v>195</v>
       </c>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="D155" s="2"/>
     </row>
-    <row r="156" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
         <v>195</v>
       </c>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="D156" s="2"/>
     </row>
-    <row r="157" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
         <v>191</v>
       </c>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="D157" s="3"/>
     </row>
-    <row r="158" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
         <v>191</v>
       </c>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D158" s="2"/>
     </row>
-    <row r="159" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
         <v>191</v>
       </c>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="D159" s="2"/>
     </row>
-    <row r="160" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
         <v>191</v>
       </c>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D160" s="2"/>
     </row>
-    <row r="161" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
         <v>191</v>
       </c>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="D161" s="2"/>
     </row>
-    <row r="162" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
         <v>191</v>
       </c>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="D162" s="2"/>
     </row>
-    <row r="163" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
         <v>191</v>
       </c>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="D163" s="2"/>
     </row>
-    <row r="164" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
         <v>191</v>
       </c>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="D164" s="2"/>
     </row>
-    <row r="165" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
         <v>231</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
         <v>231</v>
       </c>
@@ -3200,7 +3200,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
         <v>231</v>
       </c>
@@ -3211,7 +3211,7 @@
         <v>0.34499999999999997</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
         <v>231</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="2" t="s">
         <v>231</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
         <v>231</v>
       </c>
@@ -3244,7 +3244,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A171" s="2" t="s">
         <v>231</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
         <v>231</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A173" s="2" t="s">
         <v>231</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>1.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
         <v>231</v>
       </c>
@@ -3288,7 +3288,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A175" s="2" t="s">
         <v>231</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
         <v>231</v>
       </c>
@@ -3310,12 +3310,12 @@
         <v>0.12300000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A177" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
         <v>211</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
         <v>211</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
         <v>211</v>
       </c>
@@ -3348,7 +3348,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
         <v>211</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>2.9999999999999805E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
         <v>211</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A183" s="2" t="s">
         <v>211</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
         <v>211</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A185" s="2" t="s">
         <v>214</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
         <v>214</v>
       </c>
@@ -3414,7 +3414,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
         <v>214</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>5.5999999999998273E-3</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
         <v>214</v>
       </c>
@@ -3436,7 +3436,7 @@
         <v>0.17500000000000002</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A189" s="2" t="s">
         <v>214</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>0.45140000000000002</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
         <v>216</v>
       </c>
@@ -3458,7 +3458,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A191" s="2" t="s">
         <v>216</v>
       </c>
@@ -3469,7 +3469,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
         <v>216</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>0.1474</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A193" s="2" t="s">
         <v>216</v>
       </c>
@@ -3491,7 +3491,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
         <v>216</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>3.1000000000000028E-2</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
         <v>216</v>
       </c>
@@ -3513,7 +3513,7 @@
         <v>1.15E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
         <v>216</v>
       </c>
@@ -3524,7 +3524,7 @@
         <v>0.47010000000000002</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
         <v>222</v>
       </c>
@@ -3535,7 +3535,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
         <v>222</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
         <v>222</v>
       </c>
@@ -3557,7 +3557,7 @@
         <v>9.2999999999999972E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
         <v>222</v>
       </c>
@@ -3568,7 +3568,7 @@
         <v>0.20300000000000001</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A201" s="2" t="s">
         <v>222</v>
       </c>
@@ -3580,7 +3580,7 @@
         <v>0.21500000000000002</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
         <v>222</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
         <v>222</v>
       </c>
@@ -3602,911 +3602,911 @@
         <v>0.31900000000000001</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="205" spans="1:3" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="206" spans="1:3" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="207" spans="1:3" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="208" spans="1:3" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1001" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1002" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1003" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1004" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1005" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1006" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1007" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1008" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1009" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1010" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1011" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1012" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1013" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1014" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1015" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1016" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1017" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1018" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1019" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1020" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1021" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1022" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1023" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1024" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1025" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1026" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1027" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1028" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1029" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1030" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1031" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1032" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1033" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1034" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1035" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1036" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1037" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1038" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1039" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1040" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1041" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1042" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1043" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1044" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1045" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1046" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1047" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1048" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1049" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1050" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1051" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1052" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1053" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1054" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1055" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1056" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1057" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1058" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1059" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1060" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1061" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1062" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1063" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1064" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1065" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1066" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1067" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1068" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1069" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1070" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1071" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1072" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1073" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1074" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1075" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1076" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1077" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1078" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1079" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1080" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1081" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1082" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1083" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1084" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1085" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1086" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1087" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1088" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1089" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1090" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1091" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1092" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1093" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1094" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1095" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1096" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1097" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1098" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1099" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1100" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1101" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1102" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1103" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1104" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1105" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1106" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1107" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="1108" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="1:3" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="205" spans="1:3" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="206" spans="1:3" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="207" spans="1:3" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="208" spans="1:3" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1001" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1002" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1003" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1004" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1005" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1006" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1007" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1008" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1009" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1010" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1011" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1012" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1013" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1014" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1015" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1016" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1017" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1018" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1019" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1020" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1021" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1022" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1023" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1024" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1025" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1026" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1027" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1028" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1029" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1030" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1031" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1032" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1033" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1034" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1035" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1036" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1037" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1038" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1039" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1040" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1041" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1042" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1043" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1044" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1045" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1046" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1047" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1048" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1049" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1050" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1051" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1052" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1053" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1054" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1055" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1056" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1057" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1058" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1059" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1060" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1061" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1062" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1063" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1064" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1065" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1066" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1067" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1068" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1069" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1070" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1071" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1072" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1073" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1074" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1075" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1076" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1077" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1078" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1079" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1080" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1081" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1082" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1083" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1084" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1085" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1086" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1087" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1088" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1089" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1090" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1091" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1092" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1093" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1094" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1095" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1096" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1097" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1098" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1099" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1100" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1101" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1102" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1103" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1104" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1105" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1106" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1107" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="1108" ht="12.75" x14ac:dyDescent="0.2"/>
   </sheetData>
   <autoFilter ref="A1:D203" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A178:D203">
@@ -4526,19 +4526,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A162FC-7907-44C7-A909-E8E1323EC5F6}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:G300"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.5546875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="100.77734375" style="10" customWidth="1"/>
-    <col min="6" max="6" width="7.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="97.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="7"/>
+    <col min="1" max="1" width="19.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.5703125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="100.7109375" style="10" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="97.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>169</v>
       </c>
@@ -4561,7 +4561,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="38.25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>199</v>
       </c>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="G2" s="8"/>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>199</v>
       </c>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="G3" s="8"/>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>199</v>
       </c>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>199</v>
       </c>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="25.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>128</v>
       </c>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>128</v>
       </c>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>128</v>
       </c>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="25.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>128</v>
       </c>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>128</v>
       </c>
@@ -4740,7 +4740,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="25.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>128</v>
       </c>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>128</v>
       </c>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>128</v>
       </c>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>128</v>
       </c>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>128</v>
       </c>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="25.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>128</v>
       </c>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>128</v>
       </c>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>128</v>
       </c>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>128</v>
       </c>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>128</v>
       </c>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
         <v>119</v>
       </c>
@@ -4949,7 +4949,7 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>119</v>
       </c>
@@ -4964,7 +4964,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>119</v>
       </c>
@@ -4979,7 +4979,7 @@
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
         <v>119</v>
       </c>
@@ -4994,7 +4994,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>119</v>
       </c>
@@ -5009,7 +5009,7 @@
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
         <v>119</v>
       </c>
@@ -5024,7 +5024,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
         <v>119</v>
       </c>
@@ -5039,7 +5039,7 @@
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
         <v>119</v>
       </c>
@@ -5054,7 +5054,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>119</v>
       </c>
@@ -5069,7 +5069,7 @@
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>119</v>
       </c>
@@ -5084,7 +5084,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>119</v>
       </c>
@@ -5099,7 +5099,7 @@
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>119</v>
       </c>
@@ -5114,7 +5114,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>119</v>
       </c>
@@ -5129,7 +5129,7 @@
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>119</v>
       </c>
@@ -5144,7 +5144,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
         <v>119</v>
       </c>
@@ -5159,7 +5159,7 @@
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>119</v>
       </c>
@@ -5174,7 +5174,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="8"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
         <v>119</v>
       </c>
@@ -5189,7 +5189,7 @@
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
         <v>119</v>
       </c>
@@ -5204,7 +5204,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
         <v>119</v>
       </c>
@@ -5219,7 +5219,7 @@
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
         <v>119</v>
       </c>
@@ -5234,7 +5234,7 @@
       <c r="F40" s="8"/>
       <c r="G40" s="8"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
         <v>119</v>
       </c>
@@ -5249,7 +5249,7 @@
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
         <v>119</v>
       </c>
@@ -5264,7 +5264,7 @@
       <c r="F42" s="8"/>
       <c r="G42" s="8"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
         <v>119</v>
       </c>
@@ -5279,7 +5279,7 @@
       <c r="F43" s="8"/>
       <c r="G43" s="8"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>119</v>
       </c>
@@ -5294,7 +5294,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>119</v>
       </c>
@@ -5309,7 +5309,7 @@
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>119</v>
       </c>
@@ -5324,7 +5324,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
     </row>
-    <row r="47" spans="1:7" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="38.25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>118</v>
       </c>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="G47" s="8"/>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
         <v>118</v>
       </c>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="G48" s="8"/>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="8" t="s">
         <v>118</v>
       </c>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="G49" s="8"/>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>118</v>
       </c>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="G50" s="8"/>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>118</v>
       </c>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="G51" s="8"/>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
         <v>118</v>
       </c>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="G52" s="8"/>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
         <v>118</v>
       </c>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="G53" s="8"/>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
         <v>118</v>
       </c>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="G54" s="8"/>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
         <v>118</v>
       </c>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="G55" s="8"/>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
         <v>118</v>
       </c>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="G56" s="8"/>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
         <v>118</v>
       </c>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
         <v>118</v>
       </c>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
         <v>118</v>
       </c>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="G59" s="8"/>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
         <v>118</v>
       </c>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G60" s="8"/>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="8" t="s">
         <v>118</v>
       </c>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="G61" s="8"/>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="8" t="s">
         <v>118</v>
       </c>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G62" s="8"/>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="8" t="s">
         <v>118</v>
       </c>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="G63" s="8"/>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
         <v>118</v>
       </c>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="G64" s="8"/>
     </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
         <v>118</v>
       </c>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="G65" s="8"/>
     </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="8" t="s">
         <v>118</v>
       </c>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="G66" s="8"/>
     </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="8" t="s">
         <v>118</v>
       </c>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="G67" s="8"/>
     </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
         <v>118</v>
       </c>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="G68" s="8"/>
     </row>
-    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="8" t="s">
         <v>118</v>
       </c>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="G69" s="8"/>
     </row>
-    <row r="70" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
         <v>117</v>
       </c>
@@ -5782,7 +5782,7 @@
       <c r="F70" s="8"/>
       <c r="G70" s="8"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
         <v>117</v>
       </c>
@@ -5799,7 +5799,7 @@
       <c r="F71" s="8"/>
       <c r="G71" s="8"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
         <v>117</v>
       </c>
@@ -5816,7 +5816,7 @@
       <c r="F72" s="8"/>
       <c r="G72" s="8"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
         <v>117</v>
       </c>
@@ -5833,7 +5833,7 @@
       <c r="F73" s="8"/>
       <c r="G73" s="8"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
         <v>117</v>
       </c>
@@ -5850,7 +5850,7 @@
       <c r="F74" s="8"/>
       <c r="G74" s="8"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
         <v>117</v>
       </c>
@@ -5867,7 +5867,7 @@
       <c r="F75" s="8"/>
       <c r="G75" s="8"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="8" t="s">
         <v>117</v>
       </c>
@@ -5884,7 +5884,7 @@
       <c r="F76" s="8"/>
       <c r="G76" s="8"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
         <v>117</v>
       </c>
@@ -5901,7 +5901,7 @@
       <c r="F77" s="8"/>
       <c r="G77" s="8"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="8" t="s">
         <v>113</v>
       </c>
@@ -5916,7 +5916,7 @@
       <c r="F78" s="8"/>
       <c r="G78" s="8"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" s="8" t="s">
         <v>113</v>
       </c>
@@ -5931,7 +5931,7 @@
       <c r="F79" s="8"/>
       <c r="G79" s="8"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" s="8" t="s">
         <v>113</v>
       </c>
@@ -5946,7 +5946,7 @@
       <c r="F80" s="8"/>
       <c r="G80" s="8"/>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" s="8" t="s">
         <v>113</v>
       </c>
@@ -5961,7 +5961,7 @@
       <c r="F81" s="8"/>
       <c r="G81" s="8"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" s="8" t="s">
         <v>113</v>
       </c>
@@ -5976,7 +5976,7 @@
       <c r="F82" s="8"/>
       <c r="G82" s="8"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" s="8" t="s">
         <v>113</v>
       </c>
@@ -5991,7 +5991,7 @@
       <c r="F83" s="8"/>
       <c r="G83" s="8"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" s="8" t="s">
         <v>113</v>
       </c>
@@ -6006,7 +6006,7 @@
       <c r="F84" s="8"/>
       <c r="G84" s="8"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
         <v>113</v>
       </c>
@@ -6021,7 +6021,7 @@
       <c r="F85" s="8"/>
       <c r="G85" s="8"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
         <v>113</v>
       </c>
@@ -6036,7 +6036,7 @@
       <c r="F86" s="8"/>
       <c r="G86" s="8"/>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
         <v>113</v>
       </c>
@@ -6051,7 +6051,7 @@
       <c r="F87" s="8"/>
       <c r="G87" s="8"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
         <v>113</v>
       </c>
@@ -6066,7 +6066,7 @@
       <c r="F88" s="8"/>
       <c r="G88" s="8"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
         <v>113</v>
       </c>
@@ -6081,7 +6081,7 @@
       <c r="F89" s="8"/>
       <c r="G89" s="8"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="8" t="s">
         <v>113</v>
       </c>
@@ -6096,7 +6096,7 @@
       <c r="F90" s="8"/>
       <c r="G90" s="8"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="8" t="s">
         <v>113</v>
       </c>
@@ -6111,7 +6111,7 @@
       <c r="F91" s="8"/>
       <c r="G91" s="8"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="8" t="s">
         <v>113</v>
       </c>
@@ -6126,7 +6126,7 @@
       <c r="F92" s="8"/>
       <c r="G92" s="8"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="8" t="s">
         <v>113</v>
       </c>
@@ -6141,7 +6141,7 @@
       <c r="F93" s="8"/>
       <c r="G93" s="8"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="8" t="s">
         <v>33</v>
       </c>
@@ -6156,7 +6156,7 @@
       <c r="F94" s="8"/>
       <c r="G94" s="8"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="8" t="s">
         <v>33</v>
       </c>
@@ -6171,7 +6171,7 @@
       <c r="F95" s="8"/>
       <c r="G95" s="8"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="8" t="s">
         <v>33</v>
       </c>
@@ -6186,7 +6186,7 @@
       <c r="F96" s="8"/>
       <c r="G96" s="8"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="8" t="s">
         <v>33</v>
       </c>
@@ -6201,7 +6201,7 @@
       <c r="F97" s="8"/>
       <c r="G97" s="8"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="8" t="s">
         <v>33</v>
       </c>
@@ -6216,7 +6216,7 @@
       <c r="F98" s="8"/>
       <c r="G98" s="8"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="8" t="s">
         <v>33</v>
       </c>
@@ -6231,7 +6231,7 @@
       <c r="F99" s="8"/>
       <c r="G99" s="8"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="8" t="s">
         <v>33</v>
       </c>
@@ -6246,7 +6246,7 @@
       <c r="F100" s="8"/>
       <c r="G100" s="8"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="8" t="s">
         <v>33</v>
       </c>
@@ -6261,7 +6261,7 @@
       <c r="F101" s="8"/>
       <c r="G101" s="8"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="8" t="s">
         <v>33</v>
       </c>
@@ -6276,7 +6276,7 @@
       <c r="F102" s="8"/>
       <c r="G102" s="8"/>
     </row>
-    <row r="103" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A103" s="8" t="s">
         <v>36</v>
       </c>
@@ -6295,7 +6295,7 @@
       <c r="F103" s="8"/>
       <c r="G103" s="8"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
         <v>36</v>
       </c>
@@ -6312,7 +6312,7 @@
       <c r="F104" s="8"/>
       <c r="G104" s="8"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="8" t="s">
         <v>36</v>
       </c>
@@ -6329,7 +6329,7 @@
       <c r="F105" s="8"/>
       <c r="G105" s="8"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" s="8" t="s">
         <v>36</v>
       </c>
@@ -6346,7 +6346,7 @@
       <c r="F106" s="8"/>
       <c r="G106" s="8"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" s="8" t="s">
         <v>36</v>
       </c>
@@ -6363,7 +6363,7 @@
       <c r="F107" s="8"/>
       <c r="G107" s="8"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" s="8" t="s">
         <v>36</v>
       </c>
@@ -6380,7 +6380,7 @@
       <c r="F108" s="8"/>
       <c r="G108" s="8"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="8" t="s">
         <v>36</v>
       </c>
@@ -6397,7 +6397,7 @@
       <c r="F109" s="8"/>
       <c r="G109" s="8"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="8" t="s">
         <v>36</v>
       </c>
@@ -6414,7 +6414,7 @@
       <c r="F110" s="8"/>
       <c r="G110" s="8"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" s="8" t="s">
         <v>36</v>
       </c>
@@ -6431,7 +6431,7 @@
       <c r="F111" s="8"/>
       <c r="G111" s="8"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="8" t="s">
         <v>36</v>
       </c>
@@ -6448,7 +6448,7 @@
       <c r="F112" s="8"/>
       <c r="G112" s="8"/>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="8" t="s">
         <v>36</v>
       </c>
@@ -6465,7 +6465,7 @@
       <c r="F113" s="8"/>
       <c r="G113" s="8"/>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="8" t="s">
         <v>36</v>
       </c>
@@ -6482,7 +6482,7 @@
       <c r="F114" s="8"/>
       <c r="G114" s="8"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="8" t="s">
         <v>36</v>
       </c>
@@ -6499,7 +6499,7 @@
       <c r="F115" s="8"/>
       <c r="G115" s="8"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="8" t="s">
         <v>36</v>
       </c>
@@ -6516,7 +6516,7 @@
       <c r="F116" s="8"/>
       <c r="G116" s="8"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="8" t="s">
         <v>36</v>
       </c>
@@ -6533,7 +6533,7 @@
       <c r="F117" s="8"/>
       <c r="G117" s="8"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="8" t="s">
         <v>36</v>
       </c>
@@ -6550,7 +6550,7 @@
       <c r="F118" s="8"/>
       <c r="G118" s="8"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="8" t="s">
         <v>36</v>
       </c>
@@ -6567,7 +6567,7 @@
       <c r="F119" s="8"/>
       <c r="G119" s="8"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="8" t="s">
         <v>40</v>
       </c>
@@ -6582,7 +6582,7 @@
       <c r="F120" s="8"/>
       <c r="G120" s="8"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="8" t="s">
         <v>40</v>
       </c>
@@ -6597,7 +6597,7 @@
       <c r="F121" s="8"/>
       <c r="G121" s="8"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" s="8" t="s">
         <v>40</v>
       </c>
@@ -6612,7 +6612,7 @@
       <c r="F122" s="8"/>
       <c r="G122" s="8"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" s="8" t="s">
         <v>40</v>
       </c>
@@ -6627,7 +6627,7 @@
       <c r="F123" s="8"/>
       <c r="G123" s="8"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="8" t="s">
         <v>40</v>
       </c>
@@ -6642,7 +6642,7 @@
       <c r="F124" s="8"/>
       <c r="G124" s="8"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="8" t="s">
         <v>40</v>
       </c>
@@ -6657,7 +6657,7 @@
       <c r="F125" s="8"/>
       <c r="G125" s="8"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="8" t="s">
         <v>40</v>
       </c>
@@ -6672,7 +6672,7 @@
       <c r="F126" s="8"/>
       <c r="G126" s="8"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="8" t="s">
         <v>40</v>
       </c>
@@ -6687,7 +6687,7 @@
       <c r="F127" s="8"/>
       <c r="G127" s="8"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="8" t="s">
         <v>40</v>
       </c>
@@ -6702,7 +6702,7 @@
       <c r="F128" s="8"/>
       <c r="G128" s="8"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="8" t="s">
         <v>40</v>
       </c>
@@ -6717,7 +6717,7 @@
       <c r="F129" s="8"/>
       <c r="G129" s="8"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="8" t="s">
         <v>40</v>
       </c>
@@ -6732,7 +6732,7 @@
       <c r="F130" s="8"/>
       <c r="G130" s="8"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" s="8" t="s">
         <v>40</v>
       </c>
@@ -6747,7 +6747,7 @@
       <c r="F131" s="8"/>
       <c r="G131" s="8"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
         <v>40</v>
       </c>
@@ -6762,7 +6762,7 @@
       <c r="F132" s="8"/>
       <c r="G132" s="8"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="8" t="s">
         <v>40</v>
       </c>
@@ -6777,7 +6777,7 @@
       <c r="F133" s="8"/>
       <c r="G133" s="8"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="8" t="s">
         <v>40</v>
       </c>
@@ -6792,7 +6792,7 @@
       <c r="F134" s="8"/>
       <c r="G134" s="8"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="8" t="s">
         <v>40</v>
       </c>
@@ -6807,7 +6807,7 @@
       <c r="F135" s="8"/>
       <c r="G135" s="8"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="8" t="s">
         <v>40</v>
       </c>
@@ -6822,7 +6822,7 @@
       <c r="F136" s="8"/>
       <c r="G136" s="8"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="8" t="s">
         <v>40</v>
       </c>
@@ -6837,7 +6837,7 @@
       <c r="F137" s="8"/>
       <c r="G137" s="8"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="8" t="s">
         <v>40</v>
       </c>
@@ -6852,7 +6852,7 @@
       <c r="F138" s="8"/>
       <c r="G138" s="8"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="8" t="s">
         <v>40</v>
       </c>
@@ -6867,7 +6867,7 @@
       <c r="F139" s="8"/>
       <c r="G139" s="8"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="8" t="s">
         <v>40</v>
       </c>
@@ -6882,7 +6882,7 @@
       <c r="F140" s="8"/>
       <c r="G140" s="8"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="8" t="s">
         <v>40</v>
       </c>
@@ -6897,7 +6897,7 @@
       <c r="F141" s="8"/>
       <c r="G141" s="8"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="8" t="s">
         <v>40</v>
       </c>
@@ -6912,7 +6912,7 @@
       <c r="F142" s="8"/>
       <c r="G142" s="8"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
         <v>37</v>
       </c>
@@ -6927,7 +6927,7 @@
       <c r="F143" s="8"/>
       <c r="G143" s="8"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
         <v>37</v>
       </c>
@@ -6942,7 +6942,7 @@
       <c r="F144" s="8"/>
       <c r="G144" s="8"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
         <v>37</v>
       </c>
@@ -6957,7 +6957,7 @@
       <c r="F145" s="8"/>
       <c r="G145" s="8"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="8" t="s">
         <v>37</v>
       </c>
@@ -6972,7 +6972,7 @@
       <c r="F146" s="8"/>
       <c r="G146" s="8"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
         <v>37</v>
       </c>
@@ -6987,7 +6987,7 @@
       <c r="F147" s="8"/>
       <c r="G147" s="8"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="8" t="s">
         <v>37</v>
       </c>
@@ -7002,7 +7002,7 @@
       <c r="F148" s="8"/>
       <c r="G148" s="8"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
         <v>37</v>
       </c>
@@ -7017,7 +7017,7 @@
       <c r="F149" s="8"/>
       <c r="G149" s="8"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
         <v>37</v>
       </c>
@@ -7032,7 +7032,7 @@
       <c r="F150" s="8"/>
       <c r="G150" s="8"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
         <v>37</v>
       </c>
@@ -7047,7 +7047,7 @@
       <c r="F151" s="8"/>
       <c r="G151" s="8"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
         <v>37</v>
       </c>
@@ -7062,7 +7062,7 @@
       <c r="F152" s="8"/>
       <c r="G152" s="8"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="8" t="s">
         <v>37</v>
       </c>
@@ -7077,7 +7077,7 @@
       <c r="F153" s="8"/>
       <c r="G153" s="8"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" s="8" t="s">
         <v>37</v>
       </c>
@@ -7092,7 +7092,7 @@
       <c r="F154" s="8"/>
       <c r="G154" s="8"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" s="8" t="s">
         <v>37</v>
       </c>
@@ -7107,7 +7107,7 @@
       <c r="F155" s="8"/>
       <c r="G155" s="8"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" s="8" t="s">
         <v>37</v>
       </c>
@@ -7122,7 +7122,7 @@
       <c r="F156" s="8"/>
       <c r="G156" s="8"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" s="8" t="s">
         <v>37</v>
       </c>
@@ -7137,7 +7137,7 @@
       <c r="F157" s="8"/>
       <c r="G157" s="8"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" s="8" t="s">
         <v>38</v>
       </c>
@@ -7152,7 +7152,7 @@
       <c r="F158" s="8"/>
       <c r="G158" s="8"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" s="8" t="s">
         <v>38</v>
       </c>
@@ -7167,7 +7167,7 @@
       <c r="F159" s="8"/>
       <c r="G159" s="8"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" s="8" t="s">
         <v>38</v>
       </c>
@@ -7182,7 +7182,7 @@
       <c r="F160" s="8"/>
       <c r="G160" s="8"/>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" s="8" t="s">
         <v>38</v>
       </c>
@@ -7197,7 +7197,7 @@
       <c r="F161" s="8"/>
       <c r="G161" s="8"/>
     </row>
-    <row r="162" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" ht="25.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" s="8" t="s">
         <v>93</v>
       </c>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="G162" s="8"/>
     </row>
-    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" s="8" t="s">
         <v>93</v>
       </c>
@@ -7236,7 +7236,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" s="8" t="s">
         <v>93</v>
       </c>
@@ -7255,7 +7255,7 @@
       </c>
       <c r="G164" s="8"/>
     </row>
-    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" s="8" t="s">
         <v>93</v>
       </c>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="G165" s="8"/>
     </row>
-    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" s="8" t="s">
         <v>93</v>
       </c>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="G166" s="8"/>
     </row>
-    <row r="167" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" s="8" t="s">
         <v>93</v>
       </c>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="G167" s="8"/>
     </row>
-    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" s="8" t="s">
         <v>93</v>
       </c>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="G168" s="8"/>
     </row>
-    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" s="8" t="s">
         <v>93</v>
       </c>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="G169" s="8"/>
     </row>
-    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" s="8" t="s">
         <v>93</v>
       </c>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="G170" s="8"/>
     </row>
-    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" s="8" t="s">
         <v>93</v>
       </c>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="G171" s="8"/>
     </row>
-    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" s="8" t="s">
         <v>93</v>
       </c>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="G172" s="8"/>
     </row>
-    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" s="8" t="s">
         <v>93</v>
       </c>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="G173" s="8"/>
     </row>
-    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" s="8" t="s">
         <v>93</v>
       </c>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="G174" s="8"/>
     </row>
-    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" s="8" t="s">
         <v>93</v>
       </c>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="G175" s="8"/>
     </row>
-    <row r="176" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" s="8" t="s">
         <v>93</v>
       </c>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="G176" s="8"/>
     </row>
-    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" s="8" t="s">
         <v>93</v>
       </c>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="G177" s="8"/>
     </row>
-    <row r="178" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" s="8" t="s">
         <v>82</v>
       </c>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="G178" s="8"/>
     </row>
-    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" s="8" t="s">
         <v>82</v>
       </c>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="G179" s="8"/>
     </row>
-    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" s="8" t="s">
         <v>82</v>
       </c>
@@ -7565,7 +7565,7 @@
       </c>
       <c r="G180" s="8"/>
     </row>
-    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" s="8" t="s">
         <v>82</v>
       </c>
@@ -7584,7 +7584,7 @@
       </c>
       <c r="G181" s="8"/>
     </row>
-    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" s="8" t="s">
         <v>82</v>
       </c>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="G182" s="8"/>
     </row>
-    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" s="8" t="s">
         <v>82</v>
       </c>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="G183" s="8"/>
     </row>
-    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" s="8" t="s">
         <v>82</v>
       </c>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="G184" s="8"/>
     </row>
-    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" s="8" t="s">
         <v>82</v>
       </c>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="G185" s="8"/>
     </row>
-    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" s="8" t="s">
         <v>82</v>
       </c>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="G186" s="8"/>
     </row>
-    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" s="8" t="s">
         <v>82</v>
       </c>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="G187" s="8"/>
     </row>
-    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" s="8" t="s">
         <v>82</v>
       </c>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="G188" s="8"/>
     </row>
-    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" s="8" t="s">
         <v>82</v>
       </c>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="G189" s="8"/>
     </row>
-    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" s="8" t="s">
         <v>82</v>
       </c>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="G190" s="8"/>
     </row>
-    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" s="8" t="s">
         <v>82</v>
       </c>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="G191" s="8"/>
     </row>
-    <row r="192" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" s="8" t="s">
         <v>82</v>
       </c>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="G192" s="8"/>
     </row>
-    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" s="8" t="s">
         <v>82</v>
       </c>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="G193" s="8"/>
     </row>
-    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" s="8" t="s">
         <v>82</v>
       </c>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="G194" s="8"/>
     </row>
-    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" s="8" t="s">
         <v>82</v>
       </c>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="G195" s="8"/>
     </row>
-    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" s="8" t="s">
         <v>82</v>
       </c>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="G196" s="8"/>
     </row>
-    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" s="8" t="s">
         <v>82</v>
       </c>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="G197" s="8"/>
     </row>
-    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" s="8" t="s">
         <v>82</v>
       </c>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="G198" s="8"/>
     </row>
-    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" s="8" t="s">
         <v>82</v>
       </c>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="G199" s="8"/>
     </row>
-    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" s="8" t="s">
         <v>82</v>
       </c>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="G200" s="8"/>
     </row>
-    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" s="8" t="s">
         <v>82</v>
       </c>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="G201" s="8"/>
     </row>
-    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" s="8" t="s">
         <v>82</v>
       </c>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="G202" s="8"/>
     </row>
-    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8" t="s">
         <v>82</v>
       </c>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="G203" s="8"/>
     </row>
-    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" s="8" t="s">
         <v>82</v>
       </c>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="G204" s="8"/>
     </row>
-    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" s="8" t="s">
         <v>82</v>
       </c>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="G205" s="8"/>
     </row>
-    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" s="8" t="s">
         <v>82</v>
       </c>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="G206" s="8"/>
     </row>
-    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" s="8" t="s">
         <v>82</v>
       </c>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="G207" s="8"/>
     </row>
-    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" s="8" t="s">
         <v>82</v>
       </c>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="G208" s="8"/>
     </row>
-    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" s="8" t="s">
         <v>82</v>
       </c>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="G209" s="8"/>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210" s="8" t="s">
         <v>42</v>
       </c>
@@ -8137,7 +8137,7 @@
       <c r="F210" s="8"/>
       <c r="G210" s="8"/>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211" s="8" t="s">
         <v>42</v>
       </c>
@@ -8154,7 +8154,7 @@
       <c r="F211" s="8"/>
       <c r="G211" s="8"/>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212" s="8" t="s">
         <v>42</v>
       </c>
@@ -8171,7 +8171,7 @@
       <c r="F212" s="8"/>
       <c r="G212" s="8"/>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A213" s="8" t="s">
         <v>42</v>
       </c>
@@ -8188,7 +8188,7 @@
       <c r="F213" s="8"/>
       <c r="G213" s="8"/>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214" s="8" t="s">
         <v>42</v>
       </c>
@@ -8205,7 +8205,7 @@
       <c r="F214" s="8"/>
       <c r="G214" s="8"/>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A215" s="8" t="s">
         <v>42</v>
       </c>
@@ -8222,7 +8222,7 @@
       <c r="F215" s="8"/>
       <c r="G215" s="8"/>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A216" s="8" t="s">
         <v>42</v>
       </c>
@@ -8239,7 +8239,7 @@
       <c r="F216" s="8"/>
       <c r="G216" s="8"/>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A217" s="8" t="s">
         <v>42</v>
       </c>
@@ -8256,7 +8256,7 @@
       <c r="F217" s="8"/>
       <c r="G217" s="8"/>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218" s="8" t="s">
         <v>42</v>
       </c>
@@ -8273,7 +8273,7 @@
       <c r="F218" s="8"/>
       <c r="G218" s="8"/>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219" s="8" t="s">
         <v>42</v>
       </c>
@@ -8290,7 +8290,7 @@
       <c r="F219" s="8"/>
       <c r="G219" s="8"/>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220" s="8" t="s">
         <v>42</v>
       </c>
@@ -8307,7 +8307,7 @@
       <c r="F220" s="8"/>
       <c r="G220" s="8"/>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221" s="8" t="s">
         <v>42</v>
       </c>
@@ -8324,7 +8324,7 @@
       <c r="F221" s="8"/>
       <c r="G221" s="8"/>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A222" s="8" t="s">
         <v>42</v>
       </c>
@@ -8341,7 +8341,7 @@
       <c r="F222" s="8"/>
       <c r="G222" s="8"/>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A223" s="8" t="s">
         <v>42</v>
       </c>
@@ -8358,7 +8358,7 @@
       <c r="F223" s="8"/>
       <c r="G223" s="8"/>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A224" s="8" t="s">
         <v>42</v>
       </c>
@@ -8375,7 +8375,7 @@
       <c r="F224" s="8"/>
       <c r="G224" s="8"/>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A225" s="8" t="s">
         <v>42</v>
       </c>
@@ -8392,7 +8392,7 @@
       <c r="F225" s="8"/>
       <c r="G225" s="8"/>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A226" s="8" t="s">
         <v>42</v>
       </c>
@@ -8409,7 +8409,7 @@
       <c r="F226" s="8"/>
       <c r="G226" s="8"/>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A227" s="8" t="s">
         <v>42</v>
       </c>
@@ -8426,7 +8426,7 @@
       <c r="F227" s="8"/>
       <c r="G227" s="8"/>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A228" s="8" t="s">
         <v>42</v>
       </c>
@@ -8443,7 +8443,7 @@
       <c r="F228" s="8"/>
       <c r="G228" s="8"/>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A229" s="8" t="s">
         <v>42</v>
       </c>
@@ -8460,7 +8460,7 @@
       <c r="F229" s="8"/>
       <c r="G229" s="8"/>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A230" s="8" t="s">
         <v>39</v>
       </c>
@@ -8475,7 +8475,7 @@
       <c r="F230" s="8"/>
       <c r="G230" s="8"/>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A231" s="8" t="s">
         <v>39</v>
       </c>
@@ -8490,7 +8490,7 @@
       <c r="F231" s="8"/>
       <c r="G231" s="8"/>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A232" s="8" t="s">
         <v>39</v>
       </c>
@@ -8505,7 +8505,7 @@
       <c r="F232" s="8"/>
       <c r="G232" s="8"/>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A233" s="8" t="s">
         <v>39</v>
       </c>
@@ -8520,7 +8520,7 @@
       <c r="F233" s="8"/>
       <c r="G233" s="8"/>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A234" s="8" t="s">
         <v>39</v>
       </c>
@@ -8535,7 +8535,7 @@
       <c r="F234" s="8"/>
       <c r="G234" s="8"/>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A235" s="8" t="s">
         <v>39</v>
       </c>
@@ -8550,7 +8550,7 @@
       <c r="F235" s="8"/>
       <c r="G235" s="8"/>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A236" s="8" t="s">
         <v>39</v>
       </c>
@@ -8565,7 +8565,7 @@
       <c r="F236" s="8"/>
       <c r="G236" s="8"/>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A237" s="8" t="s">
         <v>39</v>
       </c>
@@ -8580,7 +8580,7 @@
       <c r="F237" s="8"/>
       <c r="G237" s="8"/>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A238" s="8" t="s">
         <v>39</v>
       </c>
@@ -8595,7 +8595,7 @@
       <c r="F238" s="8"/>
       <c r="G238" s="8"/>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A239" s="8" t="s">
         <v>39</v>
       </c>
@@ -8610,7 +8610,7 @@
       <c r="F239" s="8"/>
       <c r="G239" s="8"/>
     </row>
-    <row r="240" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A240" s="8" t="s">
         <v>41</v>
       </c>
@@ -8626,12 +8626,10 @@
       <c r="E240" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="F240" s="8" t="s">
-        <v>227</v>
-      </c>
+      <c r="F240" s="8"/>
       <c r="G240" s="8"/>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A241" s="8" t="s">
         <v>41</v>
       </c>
@@ -8645,12 +8643,10 @@
         <v>193</v>
       </c>
       <c r="E241" s="11"/>
-      <c r="F241" s="8" t="s">
-        <v>227</v>
-      </c>
+      <c r="F241" s="8"/>
       <c r="G241" s="8"/>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A242" s="8" t="s">
         <v>41</v>
       </c>
@@ -8664,12 +8660,10 @@
         <v>193</v>
       </c>
       <c r="E242" s="11"/>
-      <c r="F242" s="8" t="s">
-        <v>227</v>
-      </c>
+      <c r="F242" s="8"/>
       <c r="G242" s="8"/>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A243" s="8" t="s">
         <v>41</v>
       </c>
@@ -8683,12 +8677,10 @@
         <v>193</v>
       </c>
       <c r="E243" s="11"/>
-      <c r="F243" s="8" t="s">
-        <v>227</v>
-      </c>
+      <c r="F243" s="8"/>
       <c r="G243" s="8"/>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A244" s="8" t="s">
         <v>41</v>
       </c>
@@ -8702,12 +8694,10 @@
         <v>193</v>
       </c>
       <c r="E244" s="11"/>
-      <c r="F244" s="8" t="s">
-        <v>227</v>
-      </c>
+      <c r="F244" s="8"/>
       <c r="G244" s="8"/>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A245" s="8" t="s">
         <v>41</v>
       </c>
@@ -8721,12 +8711,10 @@
         <v>193</v>
       </c>
       <c r="E245" s="11"/>
-      <c r="F245" s="8" t="s">
-        <v>227</v>
-      </c>
+      <c r="F245" s="8"/>
       <c r="G245" s="8"/>
     </row>
-    <row r="246" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A246" s="8" t="s">
         <v>41</v>
       </c>
@@ -8747,7 +8735,7 @@
       </c>
       <c r="G246" s="8"/>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A247" s="8" t="s">
         <v>41</v>
       </c>
@@ -8766,7 +8754,7 @@
       </c>
       <c r="G247" s="8"/>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A248" s="8" t="s">
         <v>41</v>
       </c>
@@ -8785,7 +8773,7 @@
       </c>
       <c r="G248" s="8"/>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A249" s="8" t="s">
         <v>41</v>
       </c>
@@ -8804,7 +8792,7 @@
       </c>
       <c r="G249" s="8"/>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A250" s="8" t="s">
         <v>41</v>
       </c>
@@ -8823,7 +8811,7 @@
       </c>
       <c r="G250" s="8"/>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A251" s="8" t="s">
         <v>41</v>
       </c>
@@ -8842,7 +8830,7 @@
       </c>
       <c r="G251" s="8"/>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A252" s="8" t="s">
         <v>41</v>
       </c>
@@ -8861,7 +8849,7 @@
       </c>
       <c r="G252" s="8"/>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A253" s="8" t="s">
         <v>41</v>
       </c>
@@ -8880,7 +8868,7 @@
       </c>
       <c r="G253" s="8"/>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A254" s="8" t="s">
         <v>41</v>
       </c>
@@ -8899,7 +8887,7 @@
       </c>
       <c r="G254" s="8"/>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A255" s="8" t="s">
         <v>41</v>
       </c>
@@ -8918,7 +8906,7 @@
       </c>
       <c r="G255" s="8"/>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A256" s="8" t="s">
         <v>41</v>
       </c>
@@ -8937,7 +8925,7 @@
       </c>
       <c r="G256" s="8"/>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257" s="8" t="s">
         <v>41</v>
       </c>
@@ -8956,7 +8944,7 @@
       </c>
       <c r="G257" s="8"/>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258" s="8" t="s">
         <v>41</v>
       </c>
@@ -8975,7 +8963,7 @@
       </c>
       <c r="G258" s="8"/>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" s="8" t="s">
         <v>41</v>
       </c>
@@ -8994,7 +8982,7 @@
       </c>
       <c r="G259" s="8"/>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260" s="8" t="s">
         <v>41</v>
       </c>
@@ -9013,7 +9001,7 @@
       </c>
       <c r="G260" s="8"/>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261" s="8" t="s">
         <v>41</v>
       </c>
@@ -9032,7 +9020,7 @@
       </c>
       <c r="G261" s="8"/>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A262" s="8" t="s">
         <v>41</v>
       </c>
@@ -9051,7 +9039,7 @@
       </c>
       <c r="G262" s="8"/>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A263" s="8" t="s">
         <v>41</v>
       </c>
@@ -9070,7 +9058,7 @@
       </c>
       <c r="G263" s="8"/>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" s="8" t="s">
         <v>41</v>
       </c>
@@ -9089,7 +9077,7 @@
       </c>
       <c r="G264" s="8"/>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A265" s="8" t="s">
         <v>41</v>
       </c>
@@ -9108,7 +9096,7 @@
       </c>
       <c r="G265" s="8"/>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A266" s="8" t="s">
         <v>41</v>
       </c>
@@ -9127,7 +9115,7 @@
       </c>
       <c r="G266" s="8"/>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267" s="8" t="s">
         <v>41</v>
       </c>
@@ -9146,7 +9134,7 @@
       </c>
       <c r="G267" s="8"/>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A268" s="8" t="s">
         <v>41</v>
       </c>
@@ -9165,7 +9153,7 @@
       </c>
       <c r="G268" s="8"/>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269" s="8" t="s">
         <v>41</v>
       </c>
@@ -9184,7 +9172,7 @@
       </c>
       <c r="G269" s="8"/>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" s="8" t="s">
         <v>41</v>
       </c>
@@ -9203,7 +9191,7 @@
       </c>
       <c r="G270" s="8"/>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A271" s="8" t="s">
         <v>41</v>
       </c>
@@ -9222,7 +9210,7 @@
       </c>
       <c r="G271" s="8"/>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A272" s="8" t="s">
         <v>41</v>
       </c>
@@ -9241,7 +9229,7 @@
       </c>
       <c r="G272" s="8"/>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A273" s="8" t="s">
         <v>41</v>
       </c>
@@ -9260,7 +9248,7 @@
       </c>
       <c r="G273" s="8"/>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A274" s="8" t="s">
         <v>41</v>
       </c>
@@ -9279,7 +9267,7 @@
       </c>
       <c r="G274" s="8"/>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A275" s="8" t="s">
         <v>41</v>
       </c>
@@ -9298,7 +9286,7 @@
       </c>
       <c r="G275" s="8"/>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A276" s="8" t="s">
         <v>41</v>
       </c>
@@ -9317,7 +9305,7 @@
       </c>
       <c r="G276" s="8"/>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A277" s="8" t="s">
         <v>41</v>
       </c>
@@ -9336,7 +9324,7 @@
       </c>
       <c r="G277" s="8"/>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A278" s="8" t="s">
         <v>41</v>
       </c>
@@ -9355,7 +9343,7 @@
       </c>
       <c r="G278" s="8"/>
     </row>
-    <row r="279" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A279" s="8" t="s">
         <v>41</v>
       </c>
@@ -9374,7 +9362,7 @@
       <c r="F279" s="8"/>
       <c r="G279" s="8"/>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A280" s="8" t="s">
         <v>41</v>
       </c>
@@ -9391,7 +9379,7 @@
       <c r="F280" s="8"/>
       <c r="G280" s="8"/>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A281" s="8" t="s">
         <v>41</v>
       </c>
@@ -9408,7 +9396,7 @@
       <c r="F281" s="8"/>
       <c r="G281" s="8"/>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A282" s="8" t="s">
         <v>41</v>
       </c>
@@ -9425,7 +9413,7 @@
       <c r="F282" s="8"/>
       <c r="G282" s="8"/>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A283" s="8" t="s">
         <v>41</v>
       </c>
@@ -9442,7 +9430,7 @@
       <c r="F283" s="8"/>
       <c r="G283" s="8"/>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A284" s="8" t="s">
         <v>41</v>
       </c>
@@ -9459,7 +9447,7 @@
       <c r="F284" s="8"/>
       <c r="G284" s="8"/>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A285" s="8" t="s">
         <v>41</v>
       </c>
@@ -9476,7 +9464,7 @@
       <c r="F285" s="8"/>
       <c r="G285" s="8"/>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A286" s="8" t="s">
         <v>41</v>
       </c>
@@ -9493,7 +9481,7 @@
       <c r="F286" s="8"/>
       <c r="G286" s="8"/>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A287" s="8" t="s">
         <v>41</v>
       </c>
@@ -9510,7 +9498,7 @@
       <c r="F287" s="8"/>
       <c r="G287" s="8"/>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A288" s="8" t="s">
         <v>41</v>
       </c>
@@ -9527,7 +9515,7 @@
       <c r="F288" s="8"/>
       <c r="G288" s="8"/>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A289" s="8" t="s">
         <v>41</v>
       </c>
@@ -9544,7 +9532,7 @@
       <c r="F289" s="8"/>
       <c r="G289" s="8"/>
     </row>
-    <row r="290" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A290" s="8" t="s">
         <v>41</v>
       </c>
@@ -9563,7 +9551,7 @@
       <c r="F290" s="8"/>
       <c r="G290" s="8"/>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A291" s="8" t="s">
         <v>41</v>
       </c>
@@ -9580,7 +9568,7 @@
       <c r="F291" s="8"/>
       <c r="G291" s="8"/>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A292" s="8" t="s">
         <v>41</v>
       </c>
@@ -9597,7 +9585,7 @@
       <c r="F292" s="8"/>
       <c r="G292" s="8"/>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A293" s="8" t="s">
         <v>41</v>
       </c>
@@ -9614,7 +9602,7 @@
       <c r="F293" s="8"/>
       <c r="G293" s="8"/>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A294" s="8" t="s">
         <v>41</v>
       </c>
@@ -9631,7 +9619,7 @@
       <c r="F294" s="8"/>
       <c r="G294" s="8"/>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A295" s="8" t="s">
         <v>41</v>
       </c>
@@ -9648,7 +9636,7 @@
       <c r="F295" s="8"/>
       <c r="G295" s="8"/>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A296" s="8" t="s">
         <v>41</v>
       </c>
@@ -9665,7 +9653,7 @@
       <c r="F296" s="8"/>
       <c r="G296" s="8"/>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A297" s="8" t="s">
         <v>41</v>
       </c>
@@ -9682,7 +9670,7 @@
       <c r="F297" s="8"/>
       <c r="G297" s="8"/>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A298" s="8" t="s">
         <v>41</v>
       </c>
@@ -9699,7 +9687,7 @@
       <c r="F298" s="8"/>
       <c r="G298" s="8"/>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A299" s="8" t="s">
         <v>41</v>
       </c>
@@ -9716,7 +9704,7 @@
       <c r="F299" s="8"/>
       <c r="G299" s="8"/>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A300" s="8" t="s">
         <v>41</v>
       </c>

--- a/data/raw_data/feed_profiles_and_composition.xlsx
+++ b/data/raw_data/feed_profiles_and_composition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\treimer\Documents\R-temp-files\climate_risks_to_fed_mariculture\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E13F016-EC12-4786-9358-1FDC0E0C4528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01085C50-8AC8-4132-AA47-5C7A9F6E1B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="0" windowWidth="27360" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="feed_formulations" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="233">
   <si>
     <t>ingredient</t>
   </si>
@@ -9359,7 +9359,9 @@
       <c r="E279" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="F279" s="8"/>
+      <c r="F279" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G279" s="8"/>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.2">
@@ -9376,7 +9378,9 @@
         <v>219</v>
       </c>
       <c r="E280" s="11"/>
-      <c r="F280" s="8"/>
+      <c r="F280" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G280" s="8"/>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.2">
@@ -9393,7 +9397,9 @@
         <v>219</v>
       </c>
       <c r="E281" s="11"/>
-      <c r="F281" s="8"/>
+      <c r="F281" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G281" s="8"/>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.2">
@@ -9410,7 +9416,9 @@
         <v>219</v>
       </c>
       <c r="E282" s="11"/>
-      <c r="F282" s="8"/>
+      <c r="F282" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G282" s="8"/>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.2">
@@ -9427,7 +9435,9 @@
         <v>219</v>
       </c>
       <c r="E283" s="11"/>
-      <c r="F283" s="8"/>
+      <c r="F283" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G283" s="8"/>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.2">
@@ -9444,7 +9454,9 @@
         <v>219</v>
       </c>
       <c r="E284" s="11"/>
-      <c r="F284" s="8"/>
+      <c r="F284" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G284" s="8"/>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.2">
@@ -9461,7 +9473,9 @@
         <v>219</v>
       </c>
       <c r="E285" s="11"/>
-      <c r="F285" s="8"/>
+      <c r="F285" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G285" s="8"/>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.2">
@@ -9478,7 +9492,9 @@
         <v>219</v>
       </c>
       <c r="E286" s="11"/>
-      <c r="F286" s="8"/>
+      <c r="F286" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G286" s="8"/>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.2">
@@ -9495,7 +9511,9 @@
         <v>219</v>
       </c>
       <c r="E287" s="11"/>
-      <c r="F287" s="8"/>
+      <c r="F287" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G287" s="8"/>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.2">
@@ -9512,7 +9530,9 @@
         <v>219</v>
       </c>
       <c r="E288" s="11"/>
-      <c r="F288" s="8"/>
+      <c r="F288" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G288" s="8"/>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.2">
@@ -9529,7 +9549,9 @@
         <v>219</v>
       </c>
       <c r="E289" s="11"/>
-      <c r="F289" s="8"/>
+      <c r="F289" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="G289" s="8"/>
     </row>
     <row r="290" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
